--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="59">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -545,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J351"/>
+  <dimension ref="A1:J376"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -585,16 +588,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -617,16 +620,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>9</v>
@@ -649,16 +652,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -681,16 +684,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -713,16 +716,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -745,16 +748,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -777,16 +780,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>14</v>
@@ -809,16 +812,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -841,16 +844,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>11</v>
@@ -873,16 +876,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -905,16 +908,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -937,16 +940,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>7</v>
@@ -969,16 +972,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -1001,16 +1004,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1033,16 +1036,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1065,16 +1068,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -1097,16 +1100,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>8</v>
@@ -1129,16 +1132,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -1161,16 +1164,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20">
         <v>14</v>
@@ -1193,16 +1196,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -1225,16 +1228,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <v>11</v>
@@ -1257,16 +1260,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <v>13</v>
@@ -1289,16 +1292,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -1321,16 +1324,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25">
         <v>14</v>
@@ -1353,16 +1356,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -1385,16 +1388,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F27">
         <v>7</v>
@@ -1417,16 +1420,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>6</v>
@@ -1449,16 +1452,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -1481,16 +1484,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -1513,16 +1516,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -1545,16 +1548,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F32">
         <v>13</v>
@@ -1577,16 +1580,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>16</v>
@@ -1609,16 +1612,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F34">
         <v>13</v>
@@ -1641,16 +1644,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>9</v>
@@ -1673,16 +1676,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1705,16 +1708,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1737,16 +1740,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -1769,16 +1772,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1801,16 +1804,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F40">
         <v>13</v>
@@ -1833,16 +1836,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41">
         <v>6</v>
@@ -1865,16 +1868,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1897,16 +1900,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1929,16 +1932,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1961,16 +1964,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -1993,16 +1996,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2025,16 +2028,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F47">
         <v>11</v>
@@ -2057,16 +2060,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F48">
         <v>12</v>
@@ -2089,16 +2092,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2121,16 +2124,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2153,16 +2156,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2185,16 +2188,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52">
         <v>9</v>
@@ -2217,16 +2220,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F53">
         <v>10</v>
@@ -2249,16 +2252,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F54">
         <v>10</v>
@@ -2281,16 +2284,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55">
         <v>11</v>
@@ -2313,16 +2316,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56">
         <v>6</v>
@@ -2345,16 +2348,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F57">
         <v>14</v>
@@ -2377,16 +2380,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F58">
         <v>20</v>
@@ -2409,16 +2412,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F59">
         <v>16</v>
@@ -2441,16 +2444,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F60">
         <v>8</v>
@@ -2473,16 +2476,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61">
         <v>4</v>
@@ -2505,16 +2508,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -2537,16 +2540,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F63">
         <v>9</v>
@@ -2569,16 +2572,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2601,16 +2604,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F65">
         <v>13</v>
@@ -2633,16 +2636,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2665,16 +2668,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -2697,16 +2700,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2729,16 +2732,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2761,16 +2764,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2793,16 +2796,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2825,16 +2828,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F72">
         <v>15</v>
@@ -2857,16 +2860,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F73">
         <v>13</v>
@@ -2889,16 +2892,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2921,16 +2924,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -2953,16 +2956,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -2985,16 +2988,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F77">
         <v>9</v>
@@ -3017,16 +3020,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F78">
         <v>16</v>
@@ -3049,16 +3052,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F79">
         <v>11</v>
@@ -3081,16 +3084,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F80">
         <v>13</v>
@@ -3113,16 +3116,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81">
         <v>10</v>
@@ -3145,16 +3148,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F82">
         <v>15</v>
@@ -3177,16 +3180,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F83">
         <v>24</v>
@@ -3209,16 +3212,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F84">
         <v>15</v>
@@ -3241,16 +3244,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F85">
         <v>8</v>
@@ -3273,16 +3276,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F86">
         <v>5</v>
@@ -3305,16 +3308,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F87">
         <v>10</v>
@@ -3337,16 +3340,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F88">
         <v>9</v>
@@ -3369,16 +3372,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3401,16 +3404,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F90">
         <v>12</v>
@@ -3433,16 +3436,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3465,16 +3468,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3497,16 +3500,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3529,16 +3532,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -3561,16 +3564,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -3593,16 +3596,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -3625,16 +3628,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F97">
         <v>19</v>
@@ -3657,16 +3660,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F98">
         <v>15</v>
@@ -3689,16 +3692,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -3721,16 +3724,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -3753,16 +3756,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -3785,16 +3788,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F102">
         <v>11</v>
@@ -3817,16 +3820,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F103">
         <v>22</v>
@@ -3849,16 +3852,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F104">
         <v>14</v>
@@ -3881,16 +3884,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F105">
         <v>18</v>
@@ -3913,16 +3916,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F106">
         <v>16</v>
@@ -3945,16 +3948,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F107">
         <v>15</v>
@@ -3977,16 +3980,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F108">
         <v>34</v>
@@ -4009,16 +4012,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F109">
         <v>21</v>
@@ -4041,16 +4044,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110">
         <v>6</v>
@@ -4073,16 +4076,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F111">
         <v>8</v>
@@ -4105,16 +4108,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F112">
         <v>11</v>
@@ -4137,16 +4140,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F113">
         <v>9</v>
@@ -4169,16 +4172,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -4201,16 +4204,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C115" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F115">
         <v>14</v>
@@ -4233,16 +4236,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -4265,16 +4268,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4297,16 +4300,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -4329,16 +4332,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -4361,16 +4364,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -4393,16 +4396,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -4425,16 +4428,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F122">
         <v>21</v>
@@ -4457,16 +4460,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F123">
         <v>16</v>
@@ -4489,16 +4492,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -4521,16 +4524,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -4553,16 +4556,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -4585,16 +4588,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F127">
         <v>13</v>
@@ -4617,16 +4620,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F128">
         <v>27</v>
@@ -4649,16 +4652,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F129">
         <v>21</v>
@@ -4681,16 +4684,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F130">
         <v>24</v>
@@ -4713,16 +4716,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F131">
         <v>19</v>
@@ -4745,16 +4748,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F132">
         <v>21</v>
@@ -4777,16 +4780,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F133">
         <v>38</v>
@@ -4809,16 +4812,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F134">
         <v>25</v>
@@ -4841,16 +4844,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F135">
         <v>5</v>
@@ -4873,16 +4876,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F136">
         <v>8</v>
@@ -4905,16 +4908,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F137">
         <v>17</v>
@@ -4937,16 +4940,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F138">
         <v>18</v>
@@ -4969,16 +4972,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -5001,16 +5004,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F140">
         <v>15</v>
@@ -5033,16 +5036,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C141" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -5065,16 +5068,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -5097,16 +5100,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -5129,16 +5132,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -5161,16 +5164,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -5193,16 +5196,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -5225,16 +5228,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F147">
         <v>25</v>
@@ -5257,16 +5260,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F148">
         <v>16</v>
@@ -5289,16 +5292,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -5321,16 +5324,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -5353,16 +5356,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -5385,16 +5388,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F152">
         <v>23</v>
@@ -5417,16 +5420,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5449,16 +5452,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F154">
         <v>31</v>
@@ -5481,16 +5484,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F155">
         <v>29</v>
@@ -5513,16 +5516,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F156">
         <v>26</v>
@@ -5545,16 +5548,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F157">
         <v>24</v>
@@ -5577,16 +5580,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F158">
         <v>47</v>
@@ -5609,16 +5612,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F159">
         <v>29</v>
@@ -5641,16 +5644,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F160">
         <v>3</v>
@@ -5673,16 +5676,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161">
         <v>9</v>
@@ -5705,16 +5708,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F162">
         <v>20</v>
@@ -5737,16 +5740,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C163" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F163">
         <v>26</v>
@@ -5769,16 +5772,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C164" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -5801,16 +5804,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C165" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F165">
         <v>14</v>
@@ -5833,16 +5836,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C166" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -5865,16 +5868,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -5897,16 +5900,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -5929,16 +5932,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -5961,16 +5964,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -5993,16 +5996,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -6025,16 +6028,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C172" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F172">
         <v>31</v>
@@ -6057,16 +6060,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C173" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F173">
         <v>17</v>
@@ -6089,16 +6092,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C174" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -6121,16 +6124,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C175" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6153,16 +6156,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -6185,16 +6188,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C177" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F177">
         <v>34</v>
@@ -6217,16 +6220,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C178" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F178">
         <v>39</v>
@@ -6249,16 +6252,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F179">
         <v>40</v>
@@ -6281,16 +6284,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F180">
         <v>38</v>
@@ -6313,16 +6316,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C181" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F181">
         <v>36</v>
@@ -6345,16 +6348,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F182">
         <v>31</v>
@@ -6377,16 +6380,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C183" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F183">
         <v>54</v>
@@ -6409,16 +6412,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F184">
         <v>37</v>
@@ -6441,16 +6444,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F185">
         <v>2</v>
@@ -6473,16 +6476,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F186">
         <v>9</v>
@@ -6505,16 +6508,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F187">
         <v>30</v>
@@ -6537,16 +6540,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C188" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F188">
         <v>37</v>
@@ -6569,16 +6572,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C189" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -6601,16 +6604,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F190">
         <v>15</v>
@@ -6633,16 +6636,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C191" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -6665,16 +6668,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C192" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -6697,16 +6700,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -6729,16 +6732,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C194" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -6761,16 +6764,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C195" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -6793,16 +6796,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C196" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -6825,16 +6828,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C197" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F197">
         <v>35</v>
@@ -6857,16 +6860,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C198" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F198">
         <v>19</v>
@@ -6889,16 +6892,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C199" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -6921,16 +6924,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C200" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -6953,16 +6956,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C201" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -6985,16 +6988,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C202" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F202">
         <v>44</v>
@@ -7017,16 +7020,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C203" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F203">
         <v>46</v>
@@ -7049,16 +7052,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C204" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F204">
         <v>49</v>
@@ -7081,16 +7084,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C205" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F205">
         <v>51</v>
@@ -7113,16 +7116,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C206" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F206">
         <v>49</v>
@@ -7145,16 +7148,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F207">
         <v>43</v>
@@ -7177,16 +7180,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C208" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F208">
         <v>63</v>
@@ -7209,16 +7212,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C209" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F209">
         <v>48</v>
@@ -7241,16 +7244,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -7273,16 +7276,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F211">
         <v>14</v>
@@ -7305,16 +7308,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C212" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F212">
         <v>43</v>
@@ -7337,16 +7340,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C213" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F213">
         <v>46</v>
@@ -7369,16 +7372,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C214" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -7401,16 +7404,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C215" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F215">
         <v>16</v>
@@ -7433,16 +7436,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C216" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -7465,16 +7468,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C217" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -7497,16 +7500,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C218" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -7529,16 +7532,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C219" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -7561,16 +7564,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C220" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -7593,16 +7596,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C221" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -7625,16 +7628,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C222" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F222">
         <v>41</v>
@@ -7657,16 +7660,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C223" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F223">
         <v>20</v>
@@ -7689,16 +7692,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C224" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -7721,16 +7724,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C225" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -7753,16 +7756,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C226" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -7785,16 +7788,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C227" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F227">
         <v>57</v>
@@ -7817,16 +7820,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C228" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F228">
         <v>59</v>
@@ -7849,16 +7852,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C229" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F229">
         <v>56</v>
@@ -7881,16 +7884,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C230" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F230">
         <v>60</v>
@@ -7913,16 +7916,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C231" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F231">
         <v>62</v>
@@ -7945,16 +7948,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C232" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F232">
         <v>48</v>
@@ -7977,16 +7980,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C233" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F233">
         <v>74</v>
@@ -8009,16 +8012,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C234" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F234">
         <v>65</v>
@@ -8041,16 +8044,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C235" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -8073,16 +8076,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C236" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F236">
         <v>17</v>
@@ -8105,16 +8108,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C237" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F237">
         <v>48</v>
@@ -8137,16 +8140,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C238" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F238">
         <v>62</v>
@@ -8169,16 +8172,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C239" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F239">
         <v>0</v>
@@ -8201,16 +8204,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C240" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F240">
         <v>18</v>
@@ -8233,16 +8236,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C241" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -8265,16 +8268,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C242" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -8297,16 +8300,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C243" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -8329,16 +8332,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C244" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F244">
         <v>0</v>
@@ -8361,16 +8364,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C245" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -8393,16 +8396,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C246" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F246">
         <v>0</v>
@@ -8425,16 +8428,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C247" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F247">
         <v>46</v>
@@ -8457,16 +8460,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C248" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F248">
         <v>22</v>
@@ -8489,16 +8492,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C249" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -8521,16 +8524,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C250" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F250">
         <v>0</v>
@@ -8553,16 +8556,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C251" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -8585,16 +8588,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C252" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F252">
         <v>70</v>
@@ -8617,16 +8620,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C253" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F253">
         <v>71</v>
@@ -8649,16 +8652,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C254" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F254">
         <v>63</v>
@@ -8681,16 +8684,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C255" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F255">
         <v>67</v>
@@ -8713,16 +8716,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C256" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F256">
         <v>68</v>
@@ -8745,16 +8748,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C257" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F257">
         <v>57</v>
@@ -8777,16 +8780,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C258" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F258">
         <v>82</v>
@@ -8809,16 +8812,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C259" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F259">
         <v>77</v>
@@ -8841,16 +8844,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C260" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -8873,16 +8876,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F261">
         <v>23</v>
@@ -8905,16 +8908,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F262">
         <v>58</v>
@@ -8937,16 +8940,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C263" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F263">
         <v>67</v>
@@ -8969,16 +8972,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C264" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F264">
         <v>0</v>
@@ -9001,16 +9004,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C265" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F265">
         <v>18</v>
@@ -9033,16 +9036,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C266" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -9065,16 +9068,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C267" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -9097,16 +9100,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C268" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F268">
         <v>0</v>
@@ -9129,16 +9132,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C269" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F269">
         <v>0</v>
@@ -9161,16 +9164,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C270" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -9193,16 +9196,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C271" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F271">
         <v>0</v>
@@ -9225,16 +9228,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C272" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F272">
         <v>54</v>
@@ -9257,16 +9260,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C273" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F273">
         <v>24</v>
@@ -9289,16 +9292,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C274" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F274">
         <v>0</v>
@@ -9321,16 +9324,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C275" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F275">
         <v>0</v>
@@ -9353,16 +9356,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C276" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F276">
         <v>0</v>
@@ -9385,16 +9388,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C277" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F277">
         <v>77</v>
@@ -9417,16 +9420,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C278" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F278">
         <v>88</v>
@@ -9449,16 +9452,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C279" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F279">
         <v>70</v>
@@ -9481,16 +9484,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C280" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F280">
         <v>84</v>
@@ -9513,16 +9516,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C281" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F281">
         <v>77</v>
@@ -9545,16 +9548,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C282" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F282">
         <v>72</v>
@@ -9577,16 +9580,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C283" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F283">
         <v>98</v>
@@ -9609,16 +9612,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C284" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F284">
         <v>96</v>
@@ -9641,16 +9644,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C285" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -9673,16 +9676,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C286" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F286">
         <v>28</v>
@@ -9705,16 +9708,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C287" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F287">
         <v>67</v>
@@ -9737,16 +9740,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C288" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F288">
         <v>82</v>
@@ -9769,16 +9772,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C289" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F289">
         <v>0</v>
@@ -9801,16 +9804,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C290" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F290">
         <v>18</v>
@@ -9833,16 +9836,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C291" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -9865,16 +9868,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C292" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F292">
         <v>0</v>
@@ -9897,16 +9900,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C293" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -9929,16 +9932,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C294" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -9961,16 +9964,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C295" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -9993,16 +9996,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C296" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F296">
         <v>0</v>
@@ -10025,16 +10028,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C297" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F297">
         <v>66</v>
@@ -10057,16 +10060,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C298" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F298">
         <v>27</v>
@@ -10089,16 +10092,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C299" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -10121,16 +10124,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C300" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -10153,16 +10156,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C301" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F301">
         <v>0</v>
@@ -10185,16 +10188,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C302" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F302">
         <v>75</v>
@@ -10217,16 +10220,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C303" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F303">
         <v>75</v>
@@ -10249,16 +10252,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C304" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F304">
         <v>75</v>
@@ -10281,16 +10284,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C305" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F305">
         <v>75</v>
@@ -10313,16 +10316,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F306">
         <v>75</v>
@@ -10345,16 +10348,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C307" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F307">
         <v>75</v>
@@ -10377,16 +10380,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C308" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F308">
         <v>75</v>
@@ -10409,16 +10412,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C309" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F309">
         <v>75</v>
@@ -10441,16 +10444,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C310" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F310">
         <v>75</v>
@@ -10473,16 +10476,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C311" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F311">
         <v>2</v>
@@ -10505,16 +10508,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C312" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F312">
         <v>2</v>
@@ -10537,16 +10540,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C313" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F313">
         <v>2</v>
@@ -10569,16 +10572,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C314" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F314">
         <v>2</v>
@@ -10601,16 +10604,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C315" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F315">
         <v>2</v>
@@ -10633,16 +10636,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C316" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F316">
         <v>2</v>
@@ -10665,16 +10668,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C317" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F317">
         <v>2</v>
@@ -10697,16 +10700,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C318" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F318">
         <v>2</v>
@@ -10729,16 +10732,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C319" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F319">
         <v>2</v>
@@ -10761,16 +10764,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C320" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F320">
         <v>2</v>
@@ -10793,16 +10796,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C321" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F321">
         <v>2</v>
@@ -10825,16 +10828,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C322" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F322">
         <v>2</v>
@@ -10857,16 +10860,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C323" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F323">
         <v>2</v>
@@ -10889,16 +10892,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C324" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F324">
         <v>2</v>
@@ -10921,16 +10924,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C325" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F325">
         <v>2</v>
@@ -10953,16 +10956,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C326" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F326">
         <v>2</v>
@@ -10985,16 +10988,16 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C327" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D327">
         <v>7381125</v>
       </c>
       <c r="E327" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F327">
         <v>75</v>
@@ -11017,16 +11020,16 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C328" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D328">
         <v>2207663</v>
       </c>
       <c r="E328" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F328">
         <v>75</v>
@@ -11049,16 +11052,16 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C329" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D329">
         <v>7397528</v>
       </c>
       <c r="E329" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F329">
         <v>75</v>
@@ -11081,16 +11084,16 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C330" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D330">
         <v>5931712</v>
       </c>
       <c r="E330" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F330">
         <v>75</v>
@@ -11113,16 +11116,16 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C331" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D331">
         <v>7325488</v>
       </c>
       <c r="E331" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F331">
         <v>75</v>
@@ -11145,16 +11148,16 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C332" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D332">
         <v>3368175</v>
       </c>
       <c r="E332" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F332">
         <v>75</v>
@@ -11177,16 +11180,16 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C333" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D333">
         <v>3864716</v>
       </c>
       <c r="E333" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F333">
         <v>75</v>
@@ -11209,16 +11212,16 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C334" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D334">
         <v>3367403</v>
       </c>
       <c r="E334" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F334">
         <v>75</v>
@@ -11241,16 +11244,16 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D335">
         <v>7381124</v>
       </c>
       <c r="E335" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F335">
         <v>75</v>
@@ -11273,16 +11276,16 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C336" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D336">
         <v>7079978</v>
       </c>
       <c r="E336" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F336">
         <v>2</v>
@@ -11305,16 +11308,16 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C337" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D337">
         <v>3367739</v>
       </c>
       <c r="E337" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F337">
         <v>2</v>
@@ -11337,16 +11340,16 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C338" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D338">
         <v>7072286</v>
       </c>
       <c r="E338" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F338">
         <v>2</v>
@@ -11369,16 +11372,16 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C339" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D339">
         <v>3367743</v>
       </c>
       <c r="E339" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F339">
         <v>2</v>
@@ -11401,16 +11404,16 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C340" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D340">
         <v>4214024</v>
       </c>
       <c r="E340" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F340">
         <v>2</v>
@@ -11433,16 +11436,16 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C341" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D341">
         <v>7357843</v>
       </c>
       <c r="E341" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F341">
         <v>2</v>
@@ -11465,16 +11468,16 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C342" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D342">
         <v>7077448</v>
       </c>
       <c r="E342" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F342">
         <v>2</v>
@@ -11497,16 +11500,16 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C343" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D343">
         <v>2278099</v>
       </c>
       <c r="E343" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F343">
         <v>2</v>
@@ -11529,16 +11532,16 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C344" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D344">
         <v>7077738</v>
       </c>
       <c r="E344" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F344">
         <v>2</v>
@@ -11561,16 +11564,16 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C345" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D345">
         <v>4493936</v>
       </c>
       <c r="E345" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F345">
         <v>2</v>
@@ -11593,16 +11596,16 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C346" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D346">
         <v>5284531</v>
       </c>
       <c r="E346" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F346">
         <v>2</v>
@@ -11625,16 +11628,16 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C347" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D347">
         <v>5954007</v>
       </c>
       <c r="E347" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F347">
         <v>2</v>
@@ -11657,16 +11660,16 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C348" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D348">
         <v>7081903</v>
       </c>
       <c r="E348" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F348">
         <v>2</v>
@@ -11689,16 +11692,16 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C349" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D349">
         <v>9366541</v>
       </c>
       <c r="E349" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F349">
         <v>2</v>
@@ -11721,16 +11724,16 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C350" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D350">
         <v>6435172</v>
       </c>
       <c r="E350" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F350">
         <v>2</v>
@@ -11753,30 +11756,830 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C351" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D351">
         <v>7077736</v>
       </c>
       <c r="E351" t="s">
+        <v>58</v>
+      </c>
+      <c r="F351">
+        <v>2</v>
+      </c>
+      <c r="G351">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>2</v>
+      </c>
+      <c r="J351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="A352" t="s">
+        <v>24</v>
+      </c>
+      <c r="B352" t="s">
+        <v>25</v>
+      </c>
+      <c r="C352" t="s">
+        <v>25</v>
+      </c>
+      <c r="D352">
+        <v>7381125</v>
+      </c>
+      <c r="E352" t="s">
+        <v>34</v>
+      </c>
+      <c r="F352">
+        <v>75</v>
+      </c>
+      <c r="G352">
+        <v>20</v>
+      </c>
+      <c r="H352">
+        <v>0</v>
+      </c>
+      <c r="I352">
+        <v>5</v>
+      </c>
+      <c r="J352">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10">
+      <c r="A353" t="s">
+        <v>24</v>
+      </c>
+      <c r="B353" t="s">
+        <v>25</v>
+      </c>
+      <c r="C353" t="s">
+        <v>25</v>
+      </c>
+      <c r="D353">
+        <v>2207663</v>
+      </c>
+      <c r="E353" t="s">
+        <v>35</v>
+      </c>
+      <c r="F353">
+        <v>75</v>
+      </c>
+      <c r="G353">
+        <v>20</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+      <c r="I353">
+        <v>5</v>
+      </c>
+      <c r="J353">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10">
+      <c r="A354" t="s">
+        <v>24</v>
+      </c>
+      <c r="B354" t="s">
+        <v>25</v>
+      </c>
+      <c r="C354" t="s">
+        <v>25</v>
+      </c>
+      <c r="D354">
+        <v>7397528</v>
+      </c>
+      <c r="E354" t="s">
+        <v>36</v>
+      </c>
+      <c r="F354">
+        <v>75</v>
+      </c>
+      <c r="G354">
+        <v>20</v>
+      </c>
+      <c r="H354">
+        <v>0</v>
+      </c>
+      <c r="I354">
+        <v>5</v>
+      </c>
+      <c r="J354">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="A355" t="s">
+        <v>24</v>
+      </c>
+      <c r="B355" t="s">
+        <v>25</v>
+      </c>
+      <c r="C355" t="s">
+        <v>25</v>
+      </c>
+      <c r="D355">
+        <v>5931712</v>
+      </c>
+      <c r="E355" t="s">
+        <v>37</v>
+      </c>
+      <c r="F355">
+        <v>75</v>
+      </c>
+      <c r="G355">
+        <v>20</v>
+      </c>
+      <c r="H355">
+        <v>0</v>
+      </c>
+      <c r="I355">
+        <v>5</v>
+      </c>
+      <c r="J355">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="A356" t="s">
+        <v>24</v>
+      </c>
+      <c r="B356" t="s">
+        <v>25</v>
+      </c>
+      <c r="C356" t="s">
+        <v>25</v>
+      </c>
+      <c r="D356">
+        <v>7325488</v>
+      </c>
+      <c r="E356" t="s">
+        <v>38</v>
+      </c>
+      <c r="F356">
+        <v>75</v>
+      </c>
+      <c r="G356">
+        <v>20</v>
+      </c>
+      <c r="H356">
+        <v>0</v>
+      </c>
+      <c r="I356">
+        <v>5</v>
+      </c>
+      <c r="J356">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="A357" t="s">
+        <v>24</v>
+      </c>
+      <c r="B357" t="s">
+        <v>25</v>
+      </c>
+      <c r="C357" t="s">
+        <v>25</v>
+      </c>
+      <c r="D357">
+        <v>3368175</v>
+      </c>
+      <c r="E357" t="s">
+        <v>39</v>
+      </c>
+      <c r="F357">
+        <v>75</v>
+      </c>
+      <c r="G357">
+        <v>20</v>
+      </c>
+      <c r="H357">
+        <v>0</v>
+      </c>
+      <c r="I357">
+        <v>5</v>
+      </c>
+      <c r="J357">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="A358" t="s">
+        <v>24</v>
+      </c>
+      <c r="B358" t="s">
+        <v>25</v>
+      </c>
+      <c r="C358" t="s">
+        <v>25</v>
+      </c>
+      <c r="D358">
+        <v>3864716</v>
+      </c>
+      <c r="E358" t="s">
+        <v>40</v>
+      </c>
+      <c r="F358">
+        <v>75</v>
+      </c>
+      <c r="G358">
+        <v>20</v>
+      </c>
+      <c r="H358">
+        <v>0</v>
+      </c>
+      <c r="I358">
+        <v>5</v>
+      </c>
+      <c r="J358">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="A359" t="s">
+        <v>24</v>
+      </c>
+      <c r="B359" t="s">
+        <v>25</v>
+      </c>
+      <c r="C359" t="s">
+        <v>25</v>
+      </c>
+      <c r="D359">
+        <v>3367403</v>
+      </c>
+      <c r="E359" t="s">
+        <v>41</v>
+      </c>
+      <c r="F359">
+        <v>75</v>
+      </c>
+      <c r="G359">
+        <v>20</v>
+      </c>
+      <c r="H359">
+        <v>0</v>
+      </c>
+      <c r="I359">
+        <v>5</v>
+      </c>
+      <c r="J359">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="A360" t="s">
+        <v>24</v>
+      </c>
+      <c r="B360" t="s">
+        <v>25</v>
+      </c>
+      <c r="C360" t="s">
+        <v>25</v>
+      </c>
+      <c r="D360">
+        <v>7381124</v>
+      </c>
+      <c r="E360" t="s">
+        <v>42</v>
+      </c>
+      <c r="F360">
+        <v>75</v>
+      </c>
+      <c r="G360">
+        <v>20</v>
+      </c>
+      <c r="H360">
+        <v>0</v>
+      </c>
+      <c r="I360">
+        <v>5</v>
+      </c>
+      <c r="J360">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="A361" t="s">
+        <v>24</v>
+      </c>
+      <c r="B361" t="s">
+        <v>25</v>
+      </c>
+      <c r="C361" t="s">
+        <v>26</v>
+      </c>
+      <c r="D361">
+        <v>7079978</v>
+      </c>
+      <c r="E361" t="s">
+        <v>43</v>
+      </c>
+      <c r="F361">
+        <v>2</v>
+      </c>
+      <c r="G361">
+        <v>1</v>
+      </c>
+      <c r="H361">
+        <v>0</v>
+      </c>
+      <c r="I361">
+        <v>2</v>
+      </c>
+      <c r="J361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="A362" t="s">
+        <v>24</v>
+      </c>
+      <c r="B362" t="s">
+        <v>25</v>
+      </c>
+      <c r="C362" t="s">
+        <v>26</v>
+      </c>
+      <c r="D362">
+        <v>3367739</v>
+      </c>
+      <c r="E362" t="s">
+        <v>44</v>
+      </c>
+      <c r="F362">
+        <v>2</v>
+      </c>
+      <c r="G362">
+        <v>1</v>
+      </c>
+      <c r="H362">
+        <v>0</v>
+      </c>
+      <c r="I362">
+        <v>2</v>
+      </c>
+      <c r="J362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="A363" t="s">
+        <v>24</v>
+      </c>
+      <c r="B363" t="s">
+        <v>25</v>
+      </c>
+      <c r="C363" t="s">
+        <v>27</v>
+      </c>
+      <c r="D363">
+        <v>7072286</v>
+      </c>
+      <c r="E363" t="s">
+        <v>45</v>
+      </c>
+      <c r="F363">
+        <v>2</v>
+      </c>
+      <c r="G363">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>0</v>
+      </c>
+      <c r="I363">
+        <v>2</v>
+      </c>
+      <c r="J363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10">
+      <c r="A364" t="s">
+        <v>24</v>
+      </c>
+      <c r="B364" t="s">
+        <v>25</v>
+      </c>
+      <c r="C364" t="s">
+        <v>28</v>
+      </c>
+      <c r="D364">
+        <v>3367743</v>
+      </c>
+      <c r="E364" t="s">
+        <v>46</v>
+      </c>
+      <c r="F364">
+        <v>2</v>
+      </c>
+      <c r="G364">
+        <v>1</v>
+      </c>
+      <c r="H364">
+        <v>0</v>
+      </c>
+      <c r="I364">
+        <v>2</v>
+      </c>
+      <c r="J364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="A365" t="s">
+        <v>24</v>
+      </c>
+      <c r="B365" t="s">
+        <v>25</v>
+      </c>
+      <c r="C365" t="s">
+        <v>27</v>
+      </c>
+      <c r="D365">
+        <v>4214024</v>
+      </c>
+      <c r="E365" t="s">
+        <v>47</v>
+      </c>
+      <c r="F365">
+        <v>2</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+      <c r="I365">
+        <v>2</v>
+      </c>
+      <c r="J365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="A366" t="s">
+        <v>24</v>
+      </c>
+      <c r="B366" t="s">
+        <v>25</v>
+      </c>
+      <c r="C366" t="s">
+        <v>28</v>
+      </c>
+      <c r="D366">
+        <v>7357843</v>
+      </c>
+      <c r="E366" t="s">
+        <v>48</v>
+      </c>
+      <c r="F366">
+        <v>2</v>
+      </c>
+      <c r="G366">
+        <v>1</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+      <c r="I366">
+        <v>2</v>
+      </c>
+      <c r="J366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="A367" t="s">
+        <v>24</v>
+      </c>
+      <c r="B367" t="s">
+        <v>25</v>
+      </c>
+      <c r="C367" t="s">
+        <v>28</v>
+      </c>
+      <c r="D367">
+        <v>7077448</v>
+      </c>
+      <c r="E367" t="s">
+        <v>49</v>
+      </c>
+      <c r="F367">
+        <v>2</v>
+      </c>
+      <c r="G367">
+        <v>1</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+      <c r="I367">
+        <v>2</v>
+      </c>
+      <c r="J367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="A368" t="s">
+        <v>24</v>
+      </c>
+      <c r="B368" t="s">
+        <v>25</v>
+      </c>
+      <c r="C368" t="s">
+        <v>29</v>
+      </c>
+      <c r="D368">
+        <v>2278099</v>
+      </c>
+      <c r="E368" t="s">
+        <v>50</v>
+      </c>
+      <c r="F368">
+        <v>2</v>
+      </c>
+      <c r="G368">
+        <v>1</v>
+      </c>
+      <c r="H368">
+        <v>0</v>
+      </c>
+      <c r="I368">
+        <v>2</v>
+      </c>
+      <c r="J368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="A369" t="s">
+        <v>24</v>
+      </c>
+      <c r="B369" t="s">
+        <v>25</v>
+      </c>
+      <c r="C369" t="s">
+        <v>29</v>
+      </c>
+      <c r="D369">
+        <v>7077738</v>
+      </c>
+      <c r="E369" t="s">
+        <v>51</v>
+      </c>
+      <c r="F369">
+        <v>2</v>
+      </c>
+      <c r="G369">
+        <v>1</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+      <c r="I369">
+        <v>2</v>
+      </c>
+      <c r="J369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="A370" t="s">
+        <v>24</v>
+      </c>
+      <c r="B370" t="s">
+        <v>25</v>
+      </c>
+      <c r="C370" t="s">
+        <v>29</v>
+      </c>
+      <c r="D370">
+        <v>4493936</v>
+      </c>
+      <c r="E370" t="s">
+        <v>52</v>
+      </c>
+      <c r="F370">
+        <v>2</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>2</v>
+      </c>
+      <c r="J370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="A371" t="s">
+        <v>24</v>
+      </c>
+      <c r="B371" t="s">
+        <v>25</v>
+      </c>
+      <c r="C371" t="s">
+        <v>29</v>
+      </c>
+      <c r="D371">
+        <v>5284531</v>
+      </c>
+      <c r="E371" t="s">
+        <v>53</v>
+      </c>
+      <c r="F371">
+        <v>2</v>
+      </c>
+      <c r="G371">
+        <v>1</v>
+      </c>
+      <c r="H371">
+        <v>0</v>
+      </c>
+      <c r="I371">
+        <v>2</v>
+      </c>
+      <c r="J371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="A372" t="s">
+        <v>24</v>
+      </c>
+      <c r="B372" t="s">
+        <v>25</v>
+      </c>
+      <c r="C372" t="s">
+        <v>30</v>
+      </c>
+      <c r="D372">
+        <v>5954007</v>
+      </c>
+      <c r="E372" t="s">
+        <v>54</v>
+      </c>
+      <c r="F372">
+        <v>2</v>
+      </c>
+      <c r="G372">
+        <v>1</v>
+      </c>
+      <c r="H372">
+        <v>0</v>
+      </c>
+      <c r="I372">
+        <v>2</v>
+      </c>
+      <c r="J372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="A373" t="s">
+        <v>24</v>
+      </c>
+      <c r="B373" t="s">
+        <v>25</v>
+      </c>
+      <c r="C373" t="s">
+        <v>30</v>
+      </c>
+      <c r="D373">
+        <v>7081903</v>
+      </c>
+      <c r="E373" t="s">
+        <v>55</v>
+      </c>
+      <c r="F373">
+        <v>2</v>
+      </c>
+      <c r="G373">
+        <v>1</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>2</v>
+      </c>
+      <c r="J373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374" t="s">
+        <v>24</v>
+      </c>
+      <c r="B374" t="s">
+        <v>25</v>
+      </c>
+      <c r="C374" t="s">
+        <v>31</v>
+      </c>
+      <c r="D374">
+        <v>9366541</v>
+      </c>
+      <c r="E374" t="s">
+        <v>56</v>
+      </c>
+      <c r="F374">
+        <v>2</v>
+      </c>
+      <c r="G374">
+        <v>1</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+      <c r="I374">
+        <v>2</v>
+      </c>
+      <c r="J374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="A375" t="s">
+        <v>24</v>
+      </c>
+      <c r="B375" t="s">
+        <v>25</v>
+      </c>
+      <c r="C375" t="s">
+        <v>32</v>
+      </c>
+      <c r="D375">
+        <v>6435172</v>
+      </c>
+      <c r="E375" t="s">
         <v>57</v>
       </c>
-      <c r="F351">
-        <v>2</v>
-      </c>
-      <c r="G351">
-        <v>1</v>
-      </c>
-      <c r="H351">
-        <v>0</v>
-      </c>
-      <c r="I351">
-        <v>2</v>
-      </c>
-      <c r="J351">
+      <c r="F375">
+        <v>2</v>
+      </c>
+      <c r="G375">
+        <v>1</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+      <c r="I375">
+        <v>2</v>
+      </c>
+      <c r="J375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376" t="s">
+        <v>24</v>
+      </c>
+      <c r="B376" t="s">
+        <v>25</v>
+      </c>
+      <c r="C376" t="s">
+        <v>33</v>
+      </c>
+      <c r="D376">
+        <v>7077736</v>
+      </c>
+      <c r="E376" t="s">
+        <v>58</v>
+      </c>
+      <c r="F376">
+        <v>2</v>
+      </c>
+      <c r="G376">
+        <v>1</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>2</v>
+      </c>
+      <c r="J376">
         <v>1</v>
       </c>
     </row>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -12603,19 +12603,19 @@
         <v>35</v>
       </c>
       <c r="F377">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G377">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H377">
         <v>3</v>
       </c>
       <c r="I377">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J377">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -12635,19 +12635,19 @@
         <v>36</v>
       </c>
       <c r="F378">
+        <v>15</v>
+      </c>
+      <c r="G378">
+        <v>8</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>9</v>
+      </c>
+      <c r="J378">
         <v>14</v>
-      </c>
-      <c r="G378">
-        <v>4</v>
-      </c>
-      <c r="H378">
-        <v>0</v>
-      </c>
-      <c r="I378">
-        <v>2</v>
-      </c>
-      <c r="J378">
-        <v>16</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -12667,19 +12667,19 @@
         <v>37</v>
       </c>
       <c r="F379">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G379">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H379">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I379">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J379">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -12699,19 +12699,19 @@
         <v>38</v>
       </c>
       <c r="F380">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G380">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H380">
         <v>2</v>
       </c>
       <c r="I380">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J380">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -12731,19 +12731,19 @@
         <v>39</v>
       </c>
       <c r="F381">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G381">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H381">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I381">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J381">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -12763,19 +12763,19 @@
         <v>40</v>
       </c>
       <c r="F382">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G382">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H382">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I382">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J382">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -12795,19 +12795,19 @@
         <v>41</v>
       </c>
       <c r="F383">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G383">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I383">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J383">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -12827,19 +12827,19 @@
         <v>42</v>
       </c>
       <c r="F384">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G384">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H384">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I384">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J384">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -12859,19 +12859,19 @@
         <v>43</v>
       </c>
       <c r="F385">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G385">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H385">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I385">
         <v>0</v>
       </c>
       <c r="J385">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -12891,19 +12891,19 @@
         <v>44</v>
       </c>
       <c r="F386">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G386">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H386">
         <v>0</v>
       </c>
       <c r="I386">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J386">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -12923,16 +12923,16 @@
         <v>45</v>
       </c>
       <c r="F387">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G387">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H387">
         <v>0</v>
       </c>
       <c r="I387">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J387">
         <v>0</v>
@@ -12955,19 +12955,19 @@
         <v>46</v>
       </c>
       <c r="F388">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G388">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H388">
         <v>0</v>
       </c>
       <c r="I388">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J388">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -12987,16 +12987,16 @@
         <v>47</v>
       </c>
       <c r="F389">
+        <v>0</v>
+      </c>
+      <c r="G389">
+        <v>0</v>
+      </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
+      <c r="I389">
         <v>2</v>
-      </c>
-      <c r="G389">
-        <v>0</v>
-      </c>
-      <c r="H389">
-        <v>2</v>
-      </c>
-      <c r="I389">
-        <v>0</v>
       </c>
       <c r="J389">
         <v>0</v>
@@ -13019,10 +13019,10 @@
         <v>48</v>
       </c>
       <c r="F390">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G390">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H390">
         <v>0</v>
@@ -13031,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="J390">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -13051,19 +13051,19 @@
         <v>49</v>
       </c>
       <c r="F391">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G391">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H391">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I391">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J391">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -13083,10 +13083,10 @@
         <v>50</v>
       </c>
       <c r="F392">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G392">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H392">
         <v>0</v>
@@ -13095,7 +13095,7 @@
         <v>0</v>
       </c>
       <c r="J392">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -13115,19 +13115,19 @@
         <v>51</v>
       </c>
       <c r="F393">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G393">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H393">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I393">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J393">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -13150,16 +13150,16 @@
         <v>2</v>
       </c>
       <c r="G394">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H394">
         <v>0</v>
       </c>
       <c r="I394">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J394">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -13179,19 +13179,19 @@
         <v>53</v>
       </c>
       <c r="F395">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G395">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H395">
         <v>0</v>
       </c>
       <c r="I395">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J395">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -13214,7 +13214,7 @@
         <v>4</v>
       </c>
       <c r="G396">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -13223,7 +13223,7 @@
         <v>2</v>
       </c>
       <c r="J396">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -13243,19 +13243,19 @@
         <v>55</v>
       </c>
       <c r="F397">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G397">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H397">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I397">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J397">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -13275,19 +13275,19 @@
         <v>56</v>
       </c>
       <c r="F398">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G398">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H398">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I398">
         <v>0</v>
       </c>
       <c r="J398">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -13307,19 +13307,19 @@
         <v>57</v>
       </c>
       <c r="F399">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G399">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H399">
         <v>0</v>
       </c>
       <c r="I399">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J399">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -13342,16 +13342,16 @@
         <v>0</v>
       </c>
       <c r="G400">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H400">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I400">
         <v>0</v>
       </c>
       <c r="J400">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -13371,7 +13371,7 @@
         <v>59</v>
       </c>
       <c r="F401">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G401">
         <v>2</v>
@@ -13383,7 +13383,7 @@
         <v>0</v>
       </c>
       <c r="J401">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="47">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -509,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -549,16 +552,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -581,16 +584,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -613,16 +616,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -645,16 +648,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -677,16 +680,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -709,16 +712,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -741,16 +744,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -773,16 +776,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -805,16 +808,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -837,16 +840,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -869,16 +872,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -901,16 +904,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -933,16 +936,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -965,16 +968,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -997,16 +1000,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1029,16 +1032,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1061,16 +1064,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1093,16 +1096,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1125,16 +1128,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1157,16 +1160,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1189,16 +1192,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1221,16 +1224,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1253,16 +1256,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1285,16 +1288,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1320,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1349,16 +1352,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1381,16 +1384,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1413,16 +1416,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1445,16 +1448,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1477,16 +1480,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1509,16 +1512,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1541,16 +1544,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1573,16 +1576,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1605,16 +1608,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1637,16 +1640,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1669,16 +1672,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1701,16 +1704,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1733,16 +1736,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1765,16 +1768,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1797,16 +1800,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1829,16 +1832,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1861,16 +1864,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1893,16 +1896,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1925,16 +1928,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1957,16 +1960,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -1989,16 +1992,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2021,16 +2024,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2053,16 +2056,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2085,16 +2088,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2117,16 +2120,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2142,6 +2145,806 @@
       </c>
       <c r="J51">
         <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52">
+        <v>7381125</v>
+      </c>
+      <c r="E52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52">
+        <v>27</v>
+      </c>
+      <c r="G52">
+        <v>25</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>7</v>
+      </c>
+      <c r="J52">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53">
+        <v>2207663</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53">
+        <v>19</v>
+      </c>
+      <c r="G53">
+        <v>15</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+      <c r="I53">
+        <v>6</v>
+      </c>
+      <c r="J53">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54">
+        <v>7397528</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54">
+        <v>28</v>
+      </c>
+      <c r="G54">
+        <v>22</v>
+      </c>
+      <c r="H54">
+        <v>6</v>
+      </c>
+      <c r="I54">
+        <v>25</v>
+      </c>
+      <c r="J54">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55">
+        <v>5931712</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55">
+        <v>13</v>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>16</v>
+      </c>
+      <c r="J55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56">
+        <v>7325488</v>
+      </c>
+      <c r="E56" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56">
+        <v>28</v>
+      </c>
+      <c r="G56">
+        <v>40</v>
+      </c>
+      <c r="H56">
+        <v>8</v>
+      </c>
+      <c r="I56">
+        <v>15</v>
+      </c>
+      <c r="J56">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57">
+        <v>3368175</v>
+      </c>
+      <c r="E57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57">
+        <v>29</v>
+      </c>
+      <c r="G57">
+        <v>23</v>
+      </c>
+      <c r="H57">
+        <v>5</v>
+      </c>
+      <c r="I57">
+        <v>13</v>
+      </c>
+      <c r="J57">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58">
+        <v>3864716</v>
+      </c>
+      <c r="E58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58">
+        <v>41</v>
+      </c>
+      <c r="G58">
+        <v>19</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>9</v>
+      </c>
+      <c r="J58">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59">
+        <v>3367403</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>6</v>
+      </c>
+      <c r="G59">
+        <v>9</v>
+      </c>
+      <c r="H59">
+        <v>6</v>
+      </c>
+      <c r="I59">
+        <v>8</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60">
+        <v>7381124</v>
+      </c>
+      <c r="E60" t="s">
+        <v>30</v>
+      </c>
+      <c r="F60">
+        <v>34</v>
+      </c>
+      <c r="G60">
+        <v>28</v>
+      </c>
+      <c r="H60">
+        <v>7</v>
+      </c>
+      <c r="I60">
+        <v>11</v>
+      </c>
+      <c r="J60">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61">
+        <v>7079978</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61">
+        <v>7</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>6</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62">
+        <v>3367739</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62">
+        <v>4</v>
+      </c>
+      <c r="G62">
+        <v>3</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>7</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63">
+        <v>7072286</v>
+      </c>
+      <c r="E63" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64">
+        <v>3367743</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>4214024</v>
+      </c>
+      <c r="E65" t="s">
+        <v>35</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>4</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66">
+        <v>7357843</v>
+      </c>
+      <c r="E66" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66">
+        <v>17</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66">
+        <v>4</v>
+      </c>
+      <c r="J66">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67">
+        <v>7077448</v>
+      </c>
+      <c r="E67" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68">
+        <v>2278099</v>
+      </c>
+      <c r="E68" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68">
+        <v>27</v>
+      </c>
+      <c r="G68">
+        <v>17</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>35</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69">
+        <v>7077738</v>
+      </c>
+      <c r="E69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+      <c r="J69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70">
+        <v>4493936</v>
+      </c>
+      <c r="E70" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>4</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>7</v>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71">
+        <v>5284531</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71">
+        <v>3</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72">
+        <v>5954007</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72">
+        <v>20</v>
+      </c>
+      <c r="G72">
+        <v>27</v>
+      </c>
+      <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <v>10</v>
+      </c>
+      <c r="J72">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73">
+        <v>7081903</v>
+      </c>
+      <c r="E73" t="s">
+        <v>43</v>
+      </c>
+      <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>20</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74">
+        <v>9366541</v>
+      </c>
+      <c r="E74" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74">
+        <v>29</v>
+      </c>
+      <c r="G74">
+        <v>10</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74">
+        <v>10</v>
+      </c>
+      <c r="J74">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <v>6435172</v>
+      </c>
+      <c r="E75" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>5</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
+      </c>
+      <c r="J75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76">
+        <v>7077736</v>
+      </c>
+      <c r="E76" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="54">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -527,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -567,16 +573,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -599,16 +605,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -631,16 +637,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -663,16 +669,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -695,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -727,16 +733,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -759,16 +765,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -791,16 +797,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -823,16 +829,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -855,16 +861,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -887,16 +893,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -919,16 +925,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -951,16 +957,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -983,16 +989,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1015,16 +1021,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1047,16 +1053,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1079,16 +1085,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1111,16 +1117,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1143,16 +1149,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1175,16 +1181,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1207,16 +1213,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1239,16 +1245,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1271,16 +1277,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1303,16 +1309,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1335,16 +1341,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1367,16 +1373,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1399,16 +1405,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1431,16 +1437,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1463,16 +1469,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1495,16 +1501,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1527,16 +1533,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1559,16 +1565,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1591,16 +1597,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1623,16 +1629,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1655,16 +1661,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1687,16 +1693,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1719,16 +1725,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1751,16 +1757,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1783,16 +1789,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1815,16 +1821,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1847,16 +1853,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1879,16 +1885,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1911,16 +1917,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1943,16 +1949,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1975,16 +1981,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2007,16 +2013,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2039,16 +2045,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2071,16 +2077,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2103,16 +2109,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2135,16 +2141,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2167,16 +2173,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2199,16 +2205,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2231,16 +2237,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2263,16 +2269,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2295,16 +2301,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2327,16 +2333,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2359,16 +2365,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2391,16 +2397,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2423,16 +2429,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2455,16 +2461,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2487,16 +2493,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2519,16 +2525,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2551,16 +2557,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2583,16 +2589,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2615,16 +2621,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2647,16 +2653,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2679,16 +2685,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2711,16 +2717,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2743,16 +2749,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2775,16 +2781,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2807,16 +2813,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2839,16 +2845,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2871,16 +2877,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2903,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2935,16 +2941,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2967,16 +2973,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -2999,16 +3005,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3031,16 +3037,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3063,16 +3069,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3095,16 +3101,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3127,16 +3133,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3159,16 +3165,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3191,16 +3197,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3223,16 +3229,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3255,16 +3261,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3287,16 +3293,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3319,16 +3325,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3351,16 +3357,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3383,16 +3389,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3415,16 +3421,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3447,16 +3453,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3479,16 +3485,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3511,16 +3517,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C94" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3543,16 +3549,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3575,16 +3581,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3607,16 +3613,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3639,16 +3645,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3671,16 +3677,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3703,16 +3709,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3735,16 +3741,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3767,16 +3773,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3799,16 +3805,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3831,16 +3837,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3863,16 +3869,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C105" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3895,16 +3901,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3927,16 +3933,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C107" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3959,16 +3965,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -3991,16 +3997,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C109" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4023,16 +4029,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4055,16 +4061,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C111" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4087,16 +4093,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4119,16 +4125,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4151,16 +4157,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4183,16 +4189,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4215,16 +4221,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4247,16 +4253,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4279,16 +4285,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C118" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4311,16 +4317,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C119" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4343,16 +4349,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C120" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4375,16 +4381,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4407,16 +4413,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C122" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4439,16 +4445,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C123" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4471,16 +4477,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C124" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4503,16 +4509,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4535,16 +4541,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C126" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4567,16 +4573,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C127" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4599,16 +4605,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4631,16 +4637,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4663,16 +4669,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4695,16 +4701,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4727,16 +4733,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4759,16 +4765,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4791,16 +4797,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4823,16 +4829,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C135" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4855,16 +4861,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C136" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4887,16 +4893,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4919,16 +4925,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4951,16 +4957,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -4983,16 +4989,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5015,16 +5021,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5047,16 +5053,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C142" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5079,16 +5085,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C143" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5111,16 +5117,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C144" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5143,16 +5149,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5175,16 +5181,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C146" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5207,16 +5213,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5239,16 +5245,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5271,16 +5277,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C149" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5303,16 +5309,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5335,16 +5341,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C151" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5367,16 +5373,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C152" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5399,16 +5405,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5431,16 +5437,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C154" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5463,16 +5469,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5495,16 +5501,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5527,16 +5533,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5559,16 +5565,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C158" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5591,16 +5597,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C159" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5623,16 +5629,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C160" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5655,16 +5661,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C161" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5687,16 +5693,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C162" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5719,16 +5725,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C163" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5751,16 +5757,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C164" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5783,16 +5789,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C165" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5815,16 +5821,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C166" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5847,16 +5853,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C167" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5879,16 +5885,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5911,16 +5917,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5943,16 +5949,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C170" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5975,16 +5981,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C171" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6007,16 +6013,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C172" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6039,16 +6045,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C173" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6071,16 +6077,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6103,16 +6109,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C175" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6135,16 +6141,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C176" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6167,16 +6173,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6199,16 +6205,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6231,16 +6237,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6263,16 +6269,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6295,16 +6301,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C181" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6327,16 +6333,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C182" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6359,16 +6365,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6391,16 +6397,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C184" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6423,16 +6429,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C185" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6455,16 +6461,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C186" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6487,16 +6493,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6519,16 +6525,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C188" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6551,16 +6557,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C189" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6583,16 +6589,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C190" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6615,16 +6621,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6647,16 +6653,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6679,16 +6685,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C193" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6711,16 +6717,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6743,16 +6749,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6775,16 +6781,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6807,16 +6813,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6839,16 +6845,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C198" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6871,16 +6877,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C199" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6903,16 +6909,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6935,16 +6941,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C201" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6960,6 +6966,1606 @@
       </c>
       <c r="J201">
         <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" t="s">
+        <v>18</v>
+      </c>
+      <c r="B202" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202">
+        <v>7381125</v>
+      </c>
+      <c r="E202" t="s">
+        <v>29</v>
+      </c>
+      <c r="F202">
+        <v>50</v>
+      </c>
+      <c r="G202">
+        <v>22</v>
+      </c>
+      <c r="H202">
+        <v>13</v>
+      </c>
+      <c r="I202">
+        <v>23</v>
+      </c>
+      <c r="J202">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203" t="s">
+        <v>20</v>
+      </c>
+      <c r="C203" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203">
+        <v>2207663</v>
+      </c>
+      <c r="E203" t="s">
+        <v>30</v>
+      </c>
+      <c r="F203">
+        <v>15</v>
+      </c>
+      <c r="G203">
+        <v>19</v>
+      </c>
+      <c r="H203">
+        <v>7</v>
+      </c>
+      <c r="I203">
+        <v>23</v>
+      </c>
+      <c r="J203">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204" t="s">
+        <v>18</v>
+      </c>
+      <c r="B204" t="s">
+        <v>20</v>
+      </c>
+      <c r="C204" t="s">
+        <v>20</v>
+      </c>
+      <c r="D204">
+        <v>7397528</v>
+      </c>
+      <c r="E204" t="s">
+        <v>31</v>
+      </c>
+      <c r="F204">
+        <v>39</v>
+      </c>
+      <c r="G204">
+        <v>49</v>
+      </c>
+      <c r="H204">
+        <v>14</v>
+      </c>
+      <c r="I204">
+        <v>46</v>
+      </c>
+      <c r="J204">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205" t="s">
+        <v>18</v>
+      </c>
+      <c r="B205" t="s">
+        <v>20</v>
+      </c>
+      <c r="C205" t="s">
+        <v>20</v>
+      </c>
+      <c r="D205">
+        <v>5931712</v>
+      </c>
+      <c r="E205" t="s">
+        <v>32</v>
+      </c>
+      <c r="F205">
+        <v>49</v>
+      </c>
+      <c r="G205">
+        <v>30</v>
+      </c>
+      <c r="H205">
+        <v>3</v>
+      </c>
+      <c r="I205">
+        <v>27</v>
+      </c>
+      <c r="J205">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206" t="s">
+        <v>18</v>
+      </c>
+      <c r="B206" t="s">
+        <v>20</v>
+      </c>
+      <c r="C206" t="s">
+        <v>20</v>
+      </c>
+      <c r="D206">
+        <v>7325488</v>
+      </c>
+      <c r="E206" t="s">
+        <v>33</v>
+      </c>
+      <c r="F206">
+        <v>84</v>
+      </c>
+      <c r="G206">
+        <v>55</v>
+      </c>
+      <c r="H206">
+        <v>20</v>
+      </c>
+      <c r="I206">
+        <v>51</v>
+      </c>
+      <c r="J206">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" t="s">
+        <v>18</v>
+      </c>
+      <c r="B207" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" t="s">
+        <v>20</v>
+      </c>
+      <c r="D207">
+        <v>3368175</v>
+      </c>
+      <c r="E207" t="s">
+        <v>34</v>
+      </c>
+      <c r="F207">
+        <v>51</v>
+      </c>
+      <c r="G207">
+        <v>32</v>
+      </c>
+      <c r="H207">
+        <v>5</v>
+      </c>
+      <c r="I207">
+        <v>26</v>
+      </c>
+      <c r="J207">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" t="s">
+        <v>18</v>
+      </c>
+      <c r="B208" t="s">
+        <v>20</v>
+      </c>
+      <c r="C208" t="s">
+        <v>20</v>
+      </c>
+      <c r="D208">
+        <v>3864716</v>
+      </c>
+      <c r="E208" t="s">
+        <v>35</v>
+      </c>
+      <c r="F208">
+        <v>99</v>
+      </c>
+      <c r="G208">
+        <v>45</v>
+      </c>
+      <c r="H208">
+        <v>7</v>
+      </c>
+      <c r="I208">
+        <v>22</v>
+      </c>
+      <c r="J208">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" t="s">
+        <v>18</v>
+      </c>
+      <c r="B209" t="s">
+        <v>20</v>
+      </c>
+      <c r="C209" t="s">
+        <v>20</v>
+      </c>
+      <c r="D209">
+        <v>3367403</v>
+      </c>
+      <c r="E209" t="s">
+        <v>36</v>
+      </c>
+      <c r="F209">
+        <v>12</v>
+      </c>
+      <c r="G209">
+        <v>15</v>
+      </c>
+      <c r="H209">
+        <v>4</v>
+      </c>
+      <c r="I209">
+        <v>12</v>
+      </c>
+      <c r="J209">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" t="s">
+        <v>18</v>
+      </c>
+      <c r="B210" t="s">
+        <v>20</v>
+      </c>
+      <c r="C210" t="s">
+        <v>20</v>
+      </c>
+      <c r="D210">
+        <v>7381124</v>
+      </c>
+      <c r="E210" t="s">
+        <v>37</v>
+      </c>
+      <c r="F210">
+        <v>65</v>
+      </c>
+      <c r="G210">
+        <v>35</v>
+      </c>
+      <c r="H210">
+        <v>8</v>
+      </c>
+      <c r="I210">
+        <v>17</v>
+      </c>
+      <c r="J210">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" t="s">
+        <v>18</v>
+      </c>
+      <c r="B211" t="s">
+        <v>20</v>
+      </c>
+      <c r="C211" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211">
+        <v>7079978</v>
+      </c>
+      <c r="E211" t="s">
+        <v>38</v>
+      </c>
+      <c r="F211">
+        <v>7</v>
+      </c>
+      <c r="G211">
+        <v>14</v>
+      </c>
+      <c r="H211">
+        <v>3</v>
+      </c>
+      <c r="I211">
+        <v>11</v>
+      </c>
+      <c r="J211">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" t="s">
+        <v>18</v>
+      </c>
+      <c r="B212" t="s">
+        <v>20</v>
+      </c>
+      <c r="C212" t="s">
+        <v>21</v>
+      </c>
+      <c r="D212">
+        <v>3367739</v>
+      </c>
+      <c r="E212" t="s">
+        <v>39</v>
+      </c>
+      <c r="F212">
+        <v>7</v>
+      </c>
+      <c r="G212">
+        <v>7</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>6</v>
+      </c>
+      <c r="J212">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" t="s">
+        <v>18</v>
+      </c>
+      <c r="B213" t="s">
+        <v>20</v>
+      </c>
+      <c r="C213" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213">
+        <v>7072286</v>
+      </c>
+      <c r="E213" t="s">
+        <v>40</v>
+      </c>
+      <c r="F213">
+        <v>3</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" t="s">
+        <v>18</v>
+      </c>
+      <c r="B214" t="s">
+        <v>20</v>
+      </c>
+      <c r="C214" t="s">
+        <v>23</v>
+      </c>
+      <c r="D214">
+        <v>3367743</v>
+      </c>
+      <c r="E214" t="s">
+        <v>41</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>2</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215" t="s">
+        <v>18</v>
+      </c>
+      <c r="B215" t="s">
+        <v>20</v>
+      </c>
+      <c r="C215" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215">
+        <v>4214024</v>
+      </c>
+      <c r="E215" t="s">
+        <v>42</v>
+      </c>
+      <c r="F215">
+        <v>7</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>2</v>
+      </c>
+      <c r="J215">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" t="s">
+        <v>18</v>
+      </c>
+      <c r="B216" t="s">
+        <v>20</v>
+      </c>
+      <c r="C216" t="s">
+        <v>23</v>
+      </c>
+      <c r="D216">
+        <v>7357843</v>
+      </c>
+      <c r="E216" t="s">
+        <v>43</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216">
+        <v>22</v>
+      </c>
+      <c r="H216">
+        <v>6</v>
+      </c>
+      <c r="I216">
+        <v>4</v>
+      </c>
+      <c r="J216">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" t="s">
+        <v>18</v>
+      </c>
+      <c r="B217" t="s">
+        <v>20</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217">
+        <v>7077448</v>
+      </c>
+      <c r="E217" t="s">
+        <v>44</v>
+      </c>
+      <c r="F217">
+        <v>2</v>
+      </c>
+      <c r="G217">
+        <v>2</v>
+      </c>
+      <c r="H217">
+        <v>1</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218" t="s">
+        <v>18</v>
+      </c>
+      <c r="B218" t="s">
+        <v>20</v>
+      </c>
+      <c r="C218" t="s">
+        <v>24</v>
+      </c>
+      <c r="D218">
+        <v>2278099</v>
+      </c>
+      <c r="E218" t="s">
+        <v>45</v>
+      </c>
+      <c r="F218">
+        <v>27</v>
+      </c>
+      <c r="G218">
+        <v>34</v>
+      </c>
+      <c r="H218">
+        <v>10</v>
+      </c>
+      <c r="I218">
+        <v>39</v>
+      </c>
+      <c r="J218">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" t="s">
+        <v>18</v>
+      </c>
+      <c r="B219" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" t="s">
+        <v>24</v>
+      </c>
+      <c r="D219">
+        <v>7077738</v>
+      </c>
+      <c r="E219" t="s">
+        <v>46</v>
+      </c>
+      <c r="F219">
+        <v>7</v>
+      </c>
+      <c r="G219">
+        <v>9</v>
+      </c>
+      <c r="H219">
+        <v>1</v>
+      </c>
+      <c r="I219">
+        <v>4</v>
+      </c>
+      <c r="J219">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" t="s">
+        <v>18</v>
+      </c>
+      <c r="B220" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" t="s">
+        <v>24</v>
+      </c>
+      <c r="D220">
+        <v>4493936</v>
+      </c>
+      <c r="E220" t="s">
+        <v>47</v>
+      </c>
+      <c r="F220">
+        <v>14</v>
+      </c>
+      <c r="G220">
+        <v>8</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>5</v>
+      </c>
+      <c r="J220">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" t="s">
+        <v>18</v>
+      </c>
+      <c r="B221" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" t="s">
+        <v>24</v>
+      </c>
+      <c r="D221">
+        <v>5284531</v>
+      </c>
+      <c r="E221" t="s">
+        <v>48</v>
+      </c>
+      <c r="F221">
+        <v>4</v>
+      </c>
+      <c r="G221">
+        <v>6</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>6</v>
+      </c>
+      <c r="J221">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" t="s">
+        <v>18</v>
+      </c>
+      <c r="B222" t="s">
+        <v>20</v>
+      </c>
+      <c r="C222" t="s">
+        <v>25</v>
+      </c>
+      <c r="D222">
+        <v>5954007</v>
+      </c>
+      <c r="E222" t="s">
+        <v>49</v>
+      </c>
+      <c r="F222">
+        <v>94</v>
+      </c>
+      <c r="G222">
+        <v>43</v>
+      </c>
+      <c r="H222">
+        <v>10</v>
+      </c>
+      <c r="I222">
+        <v>29</v>
+      </c>
+      <c r="J222">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" t="s">
+        <v>18</v>
+      </c>
+      <c r="B223" t="s">
+        <v>20</v>
+      </c>
+      <c r="C223" t="s">
+        <v>25</v>
+      </c>
+      <c r="D223">
+        <v>7081903</v>
+      </c>
+      <c r="E223" t="s">
+        <v>50</v>
+      </c>
+      <c r="F223">
+        <v>53</v>
+      </c>
+      <c r="G223">
+        <v>25</v>
+      </c>
+      <c r="H223">
+        <v>3</v>
+      </c>
+      <c r="I223">
+        <v>20</v>
+      </c>
+      <c r="J223">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" t="s">
+        <v>18</v>
+      </c>
+      <c r="B224" t="s">
+        <v>20</v>
+      </c>
+      <c r="C224" t="s">
+        <v>26</v>
+      </c>
+      <c r="D224">
+        <v>9366541</v>
+      </c>
+      <c r="E224" t="s">
+        <v>51</v>
+      </c>
+      <c r="F224">
+        <v>30</v>
+      </c>
+      <c r="G224">
+        <v>24</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>11</v>
+      </c>
+      <c r="J224">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225" t="s">
+        <v>18</v>
+      </c>
+      <c r="B225" t="s">
+        <v>20</v>
+      </c>
+      <c r="C225" t="s">
+        <v>27</v>
+      </c>
+      <c r="D225">
+        <v>6435172</v>
+      </c>
+      <c r="E225" t="s">
+        <v>52</v>
+      </c>
+      <c r="F225">
+        <v>16</v>
+      </c>
+      <c r="G225">
+        <v>14</v>
+      </c>
+      <c r="H225">
+        <v>4</v>
+      </c>
+      <c r="I225">
+        <v>12</v>
+      </c>
+      <c r="J225">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" t="s">
+        <v>18</v>
+      </c>
+      <c r="B226" t="s">
+        <v>20</v>
+      </c>
+      <c r="C226" t="s">
+        <v>28</v>
+      </c>
+      <c r="D226">
+        <v>7077736</v>
+      </c>
+      <c r="E226" t="s">
+        <v>53</v>
+      </c>
+      <c r="F226">
+        <v>7</v>
+      </c>
+      <c r="G226">
+        <v>4</v>
+      </c>
+      <c r="H226">
+        <v>2</v>
+      </c>
+      <c r="I226">
+        <v>2</v>
+      </c>
+      <c r="J226">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227" t="s">
+        <v>19</v>
+      </c>
+      <c r="B227" t="s">
+        <v>20</v>
+      </c>
+      <c r="C227" t="s">
+        <v>20</v>
+      </c>
+      <c r="D227">
+        <v>7381125</v>
+      </c>
+      <c r="E227" t="s">
+        <v>29</v>
+      </c>
+      <c r="F227">
+        <v>46</v>
+      </c>
+      <c r="G227">
+        <v>28</v>
+      </c>
+      <c r="H227">
+        <v>5</v>
+      </c>
+      <c r="I227">
+        <v>28</v>
+      </c>
+      <c r="J227">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228" t="s">
+        <v>19</v>
+      </c>
+      <c r="B228" t="s">
+        <v>20</v>
+      </c>
+      <c r="C228" t="s">
+        <v>20</v>
+      </c>
+      <c r="D228">
+        <v>2207663</v>
+      </c>
+      <c r="E228" t="s">
+        <v>30</v>
+      </c>
+      <c r="F228">
+        <v>20</v>
+      </c>
+      <c r="G228">
+        <v>25</v>
+      </c>
+      <c r="H228">
+        <v>8</v>
+      </c>
+      <c r="I228">
+        <v>17</v>
+      </c>
+      <c r="J228">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229" t="s">
+        <v>19</v>
+      </c>
+      <c r="B229" t="s">
+        <v>20</v>
+      </c>
+      <c r="C229" t="s">
+        <v>20</v>
+      </c>
+      <c r="D229">
+        <v>7397528</v>
+      </c>
+      <c r="E229" t="s">
+        <v>31</v>
+      </c>
+      <c r="F229">
+        <v>31</v>
+      </c>
+      <c r="G229">
+        <v>32</v>
+      </c>
+      <c r="H229">
+        <v>9</v>
+      </c>
+      <c r="I229">
+        <v>65</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230" t="s">
+        <v>19</v>
+      </c>
+      <c r="B230" t="s">
+        <v>20</v>
+      </c>
+      <c r="C230" t="s">
+        <v>20</v>
+      </c>
+      <c r="D230">
+        <v>5931712</v>
+      </c>
+      <c r="E230" t="s">
+        <v>32</v>
+      </c>
+      <c r="F230">
+        <v>48</v>
+      </c>
+      <c r="G230">
+        <v>25</v>
+      </c>
+      <c r="H230">
+        <v>4</v>
+      </c>
+      <c r="I230">
+        <v>30</v>
+      </c>
+      <c r="J230">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231" t="s">
+        <v>19</v>
+      </c>
+      <c r="B231" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" t="s">
+        <v>20</v>
+      </c>
+      <c r="D231">
+        <v>7325488</v>
+      </c>
+      <c r="E231" t="s">
+        <v>33</v>
+      </c>
+      <c r="F231">
+        <v>88</v>
+      </c>
+      <c r="G231">
+        <v>57</v>
+      </c>
+      <c r="H231">
+        <v>21</v>
+      </c>
+      <c r="I231">
+        <v>55</v>
+      </c>
+      <c r="J231">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232" t="s">
+        <v>19</v>
+      </c>
+      <c r="B232" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" t="s">
+        <v>20</v>
+      </c>
+      <c r="D232">
+        <v>3368175</v>
+      </c>
+      <c r="E232" t="s">
+        <v>34</v>
+      </c>
+      <c r="F232">
+        <v>44</v>
+      </c>
+      <c r="G232">
+        <v>31</v>
+      </c>
+      <c r="H232">
+        <v>10</v>
+      </c>
+      <c r="I232">
+        <v>31</v>
+      </c>
+      <c r="J232">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233" t="s">
+        <v>19</v>
+      </c>
+      <c r="B233" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" t="s">
+        <v>20</v>
+      </c>
+      <c r="D233">
+        <v>3864716</v>
+      </c>
+      <c r="E233" t="s">
+        <v>35</v>
+      </c>
+      <c r="F233">
+        <v>104</v>
+      </c>
+      <c r="G233">
+        <v>48</v>
+      </c>
+      <c r="H233">
+        <v>15</v>
+      </c>
+      <c r="I233">
+        <v>36</v>
+      </c>
+      <c r="J233">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234" t="s">
+        <v>19</v>
+      </c>
+      <c r="B234" t="s">
+        <v>20</v>
+      </c>
+      <c r="C234" t="s">
+        <v>20</v>
+      </c>
+      <c r="D234">
+        <v>3367403</v>
+      </c>
+      <c r="E234" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234">
+        <v>13</v>
+      </c>
+      <c r="G234">
+        <v>4</v>
+      </c>
+      <c r="H234">
+        <v>8</v>
+      </c>
+      <c r="I234">
+        <v>12</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235" t="s">
+        <v>19</v>
+      </c>
+      <c r="B235" t="s">
+        <v>20</v>
+      </c>
+      <c r="C235" t="s">
+        <v>20</v>
+      </c>
+      <c r="D235">
+        <v>7381124</v>
+      </c>
+      <c r="E235" t="s">
+        <v>37</v>
+      </c>
+      <c r="F235">
+        <v>65</v>
+      </c>
+      <c r="G235">
+        <v>32</v>
+      </c>
+      <c r="H235">
+        <v>8</v>
+      </c>
+      <c r="I235">
+        <v>32</v>
+      </c>
+      <c r="J235">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236" t="s">
+        <v>19</v>
+      </c>
+      <c r="B236" t="s">
+        <v>20</v>
+      </c>
+      <c r="C236" t="s">
+        <v>21</v>
+      </c>
+      <c r="D236">
+        <v>7079978</v>
+      </c>
+      <c r="E236" t="s">
+        <v>38</v>
+      </c>
+      <c r="F236">
+        <v>8</v>
+      </c>
+      <c r="G236">
+        <v>4</v>
+      </c>
+      <c r="H236">
+        <v>1</v>
+      </c>
+      <c r="I236">
+        <v>13</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237" t="s">
+        <v>19</v>
+      </c>
+      <c r="B237" t="s">
+        <v>20</v>
+      </c>
+      <c r="C237" t="s">
+        <v>21</v>
+      </c>
+      <c r="D237">
+        <v>3367739</v>
+      </c>
+      <c r="E237" t="s">
+        <v>39</v>
+      </c>
+      <c r="F237">
+        <v>12</v>
+      </c>
+      <c r="G237">
+        <v>3</v>
+      </c>
+      <c r="H237">
+        <v>1</v>
+      </c>
+      <c r="I237">
+        <v>6</v>
+      </c>
+      <c r="J237">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238" t="s">
+        <v>19</v>
+      </c>
+      <c r="B238" t="s">
+        <v>20</v>
+      </c>
+      <c r="C238" t="s">
+        <v>22</v>
+      </c>
+      <c r="D238">
+        <v>7072286</v>
+      </c>
+      <c r="E238" t="s">
+        <v>40</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239" t="s">
+        <v>19</v>
+      </c>
+      <c r="B239" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" t="s">
+        <v>23</v>
+      </c>
+      <c r="D239">
+        <v>3367743</v>
+      </c>
+      <c r="E239" t="s">
+        <v>41</v>
+      </c>
+      <c r="F239">
+        <v>2</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240" t="s">
+        <v>19</v>
+      </c>
+      <c r="B240" t="s">
+        <v>20</v>
+      </c>
+      <c r="C240" t="s">
+        <v>22</v>
+      </c>
+      <c r="D240">
+        <v>4214024</v>
+      </c>
+      <c r="E240" t="s">
+        <v>42</v>
+      </c>
+      <c r="F240">
+        <v>6</v>
+      </c>
+      <c r="G240">
+        <v>2</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>2</v>
+      </c>
+      <c r="J240">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241" t="s">
+        <v>19</v>
+      </c>
+      <c r="B241" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" t="s">
+        <v>23</v>
+      </c>
+      <c r="D241">
+        <v>7357843</v>
+      </c>
+      <c r="E241" t="s">
+        <v>43</v>
+      </c>
+      <c r="F241">
+        <v>41</v>
+      </c>
+      <c r="G241">
+        <v>14</v>
+      </c>
+      <c r="H241">
+        <v>3</v>
+      </c>
+      <c r="I241">
+        <v>5</v>
+      </c>
+      <c r="J241">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242" t="s">
+        <v>19</v>
+      </c>
+      <c r="B242" t="s">
+        <v>20</v>
+      </c>
+      <c r="C242" t="s">
+        <v>23</v>
+      </c>
+      <c r="D242">
+        <v>7077448</v>
+      </c>
+      <c r="E242" t="s">
+        <v>44</v>
+      </c>
+      <c r="F242">
+        <v>3</v>
+      </c>
+      <c r="G242">
+        <v>0</v>
+      </c>
+      <c r="H242">
+        <v>2</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243" t="s">
+        <v>19</v>
+      </c>
+      <c r="B243" t="s">
+        <v>20</v>
+      </c>
+      <c r="C243" t="s">
+        <v>24</v>
+      </c>
+      <c r="D243">
+        <v>2278099</v>
+      </c>
+      <c r="E243" t="s">
+        <v>45</v>
+      </c>
+      <c r="F243">
+        <v>30</v>
+      </c>
+      <c r="G243">
+        <v>36</v>
+      </c>
+      <c r="H243">
+        <v>5</v>
+      </c>
+      <c r="I243">
+        <v>36</v>
+      </c>
+      <c r="J243">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244" t="s">
+        <v>19</v>
+      </c>
+      <c r="B244" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" t="s">
+        <v>24</v>
+      </c>
+      <c r="D244">
+        <v>7077738</v>
+      </c>
+      <c r="E244" t="s">
+        <v>46</v>
+      </c>
+      <c r="F244">
+        <v>9</v>
+      </c>
+      <c r="G244">
+        <v>10</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>5</v>
+      </c>
+      <c r="J244">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245" t="s">
+        <v>19</v>
+      </c>
+      <c r="B245" t="s">
+        <v>20</v>
+      </c>
+      <c r="C245" t="s">
+        <v>24</v>
+      </c>
+      <c r="D245">
+        <v>4493936</v>
+      </c>
+      <c r="E245" t="s">
+        <v>47</v>
+      </c>
+      <c r="F245">
+        <v>16</v>
+      </c>
+      <c r="G245">
+        <v>9</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>7</v>
+      </c>
+      <c r="J245">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246" t="s">
+        <v>19</v>
+      </c>
+      <c r="B246" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246" t="s">
+        <v>24</v>
+      </c>
+      <c r="D246">
+        <v>5284531</v>
+      </c>
+      <c r="E246" t="s">
+        <v>48</v>
+      </c>
+      <c r="F246">
+        <v>8</v>
+      </c>
+      <c r="G246">
+        <v>4</v>
+      </c>
+      <c r="H246">
+        <v>1</v>
+      </c>
+      <c r="I246">
+        <v>2</v>
+      </c>
+      <c r="J246">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="A247" t="s">
+        <v>19</v>
+      </c>
+      <c r="B247" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" t="s">
+        <v>25</v>
+      </c>
+      <c r="D247">
+        <v>5954007</v>
+      </c>
+      <c r="E247" t="s">
+        <v>49</v>
+      </c>
+      <c r="F247">
+        <v>108</v>
+      </c>
+      <c r="G247">
+        <v>30</v>
+      </c>
+      <c r="H247">
+        <v>5</v>
+      </c>
+      <c r="I247">
+        <v>33</v>
+      </c>
+      <c r="J247">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248" t="s">
+        <v>19</v>
+      </c>
+      <c r="B248" t="s">
+        <v>20</v>
+      </c>
+      <c r="C248" t="s">
+        <v>25</v>
+      </c>
+      <c r="D248">
+        <v>7081903</v>
+      </c>
+      <c r="E248" t="s">
+        <v>50</v>
+      </c>
+      <c r="F248">
+        <v>57</v>
+      </c>
+      <c r="G248">
+        <v>21</v>
+      </c>
+      <c r="H248">
+        <v>1</v>
+      </c>
+      <c r="I248">
+        <v>22</v>
+      </c>
+      <c r="J248">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249" t="s">
+        <v>19</v>
+      </c>
+      <c r="B249" t="s">
+        <v>20</v>
+      </c>
+      <c r="C249" t="s">
+        <v>26</v>
+      </c>
+      <c r="D249">
+        <v>9366541</v>
+      </c>
+      <c r="E249" t="s">
+        <v>51</v>
+      </c>
+      <c r="F249">
+        <v>38</v>
+      </c>
+      <c r="G249">
+        <v>20</v>
+      </c>
+      <c r="H249">
+        <v>1</v>
+      </c>
+      <c r="I249">
+        <v>17</v>
+      </c>
+      <c r="J249">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250" t="s">
+        <v>19</v>
+      </c>
+      <c r="B250" t="s">
+        <v>20</v>
+      </c>
+      <c r="C250" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250">
+        <v>6435172</v>
+      </c>
+      <c r="E250" t="s">
+        <v>52</v>
+      </c>
+      <c r="F250">
+        <v>19</v>
+      </c>
+      <c r="G250">
+        <v>6</v>
+      </c>
+      <c r="H250">
+        <v>4</v>
+      </c>
+      <c r="I250">
+        <v>14</v>
+      </c>
+      <c r="J250">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251" t="s">
+        <v>19</v>
+      </c>
+      <c r="B251" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" t="s">
+        <v>28</v>
+      </c>
+      <c r="D251">
+        <v>7077736</v>
+      </c>
+      <c r="E251" t="s">
+        <v>53</v>
+      </c>
+      <c r="F251">
+        <v>7</v>
+      </c>
+      <c r="G251">
+        <v>2</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>6</v>
+      </c>
+      <c r="J251">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="55">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -533,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -573,16 +576,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -605,16 +608,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -637,16 +640,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -669,16 +672,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -701,16 +704,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -733,16 +736,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -765,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -797,16 +800,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -829,16 +832,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -861,16 +864,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -893,16 +896,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -925,16 +928,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -957,16 +960,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -989,16 +992,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1021,16 +1024,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1053,16 +1056,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1085,16 +1088,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1117,16 +1120,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1149,16 +1152,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1181,16 +1184,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1213,16 +1216,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1245,16 +1248,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1277,16 +1280,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1309,16 +1312,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1341,16 +1344,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1373,16 +1376,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1405,16 +1408,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1437,16 +1440,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1469,16 +1472,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1501,16 +1504,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1533,16 +1536,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1565,16 +1568,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1597,16 +1600,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1629,16 +1632,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1661,16 +1664,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1693,16 +1696,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1725,16 +1728,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1757,16 +1760,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1789,16 +1792,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1821,16 +1824,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1853,16 +1856,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1885,16 +1888,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1917,16 +1920,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1949,16 +1952,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1981,16 +1984,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2013,16 +2016,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2045,16 +2048,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2077,16 +2080,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2109,16 +2112,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2141,16 +2144,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2173,16 +2176,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2205,16 +2208,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2237,16 +2240,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2269,16 +2272,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2301,16 +2304,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2333,16 +2336,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2365,16 +2368,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2397,16 +2400,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2429,16 +2432,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2461,16 +2464,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2493,16 +2496,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2525,16 +2528,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2557,16 +2560,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2589,16 +2592,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2621,16 +2624,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2653,16 +2656,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2685,16 +2688,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2717,16 +2720,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2749,16 +2752,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2781,16 +2784,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2813,16 +2816,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2845,16 +2848,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2877,16 +2880,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2909,16 +2912,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2941,16 +2944,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2973,16 +2976,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3005,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3037,16 +3040,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3069,16 +3072,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3101,16 +3104,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3133,16 +3136,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3165,16 +3168,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3197,16 +3200,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3229,16 +3232,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3261,16 +3264,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3293,16 +3296,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3325,16 +3328,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3357,16 +3360,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3389,16 +3392,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3421,16 +3424,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3453,16 +3456,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3485,16 +3488,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3517,16 +3520,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3549,16 +3552,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3581,16 +3584,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3613,16 +3616,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3645,16 +3648,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3677,16 +3680,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3709,16 +3712,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3741,16 +3744,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3773,16 +3776,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3805,16 +3808,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3837,16 +3840,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3869,16 +3872,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3901,16 +3904,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3933,16 +3936,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3965,16 +3968,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -3997,16 +4000,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4029,16 +4032,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4061,16 +4064,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4093,16 +4096,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4125,16 +4128,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4157,16 +4160,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4189,16 +4192,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4221,16 +4224,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4253,16 +4256,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4285,16 +4288,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C118" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4317,16 +4320,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C119" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4349,16 +4352,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C120" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4381,16 +4384,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C121" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4413,16 +4416,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4445,16 +4448,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4477,16 +4480,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C124" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4509,16 +4512,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C125" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4541,16 +4544,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C126" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4573,16 +4576,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4605,16 +4608,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C128" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4637,16 +4640,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4669,16 +4672,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4701,16 +4704,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4733,16 +4736,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4765,16 +4768,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4797,16 +4800,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4829,16 +4832,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4861,16 +4864,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C136" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4893,16 +4896,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4925,16 +4928,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4957,16 +4960,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -4989,16 +4992,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5021,16 +5024,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5053,16 +5056,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5085,16 +5088,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5117,16 +5120,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5149,16 +5152,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5181,16 +5184,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5213,16 +5216,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5245,16 +5248,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5277,16 +5280,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C149" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5309,16 +5312,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5341,16 +5344,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5373,16 +5376,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C152" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5405,16 +5408,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5437,16 +5440,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5469,16 +5472,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5501,16 +5504,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5533,16 +5536,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5565,16 +5568,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5597,16 +5600,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5629,16 +5632,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5661,16 +5664,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C161" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5693,16 +5696,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C162" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5725,16 +5728,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C163" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5757,16 +5760,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C164" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5789,16 +5792,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C165" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5821,16 +5824,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C166" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5853,16 +5856,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C167" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5885,16 +5888,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C168" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5917,16 +5920,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5949,16 +5952,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C170" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5981,16 +5984,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6013,16 +6016,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6045,16 +6048,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C173" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6077,16 +6080,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C174" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6109,16 +6112,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6141,16 +6144,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6173,16 +6176,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C177" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6205,16 +6208,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C178" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6237,16 +6240,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6269,16 +6272,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6301,16 +6304,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C181" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6333,16 +6336,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C182" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6365,16 +6368,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C183" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6397,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6429,16 +6432,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6461,16 +6464,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6493,16 +6496,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C187" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6525,16 +6528,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C188" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6557,16 +6560,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C189" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6589,16 +6592,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C190" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6621,16 +6624,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C191" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6653,16 +6656,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C192" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6685,16 +6688,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6717,16 +6720,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C194" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6749,16 +6752,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C195" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6781,16 +6784,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C196" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6813,16 +6816,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C197" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6845,16 +6848,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C198" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6877,16 +6880,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C199" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6909,16 +6912,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C200" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6941,16 +6944,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C201" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6973,16 +6976,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C202" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7005,16 +7008,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7037,16 +7040,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C204" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7069,16 +7072,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C205" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7101,16 +7104,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C206" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7133,16 +7136,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C207" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7165,16 +7168,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C208" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7197,16 +7200,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C209" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7229,16 +7232,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C210" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7261,16 +7264,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C211" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7293,16 +7296,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C212" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7325,16 +7328,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7357,16 +7360,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C214" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7389,16 +7392,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C215" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7421,16 +7424,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C216" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7453,16 +7456,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7485,16 +7488,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C218" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7517,16 +7520,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C219" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7549,16 +7552,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C220" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7581,16 +7584,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C221" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7613,16 +7616,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C222" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7645,16 +7648,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C223" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7677,16 +7680,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7709,16 +7712,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7741,16 +7744,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C226" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7773,16 +7776,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C227" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7805,16 +7808,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C228" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7837,16 +7840,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C229" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7869,16 +7872,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7901,16 +7904,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C231" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7933,16 +7936,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C232" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7965,16 +7968,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C233" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -7997,16 +8000,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C234" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8029,16 +8032,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C235" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8061,16 +8064,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C236" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8093,16 +8096,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C237" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8125,16 +8128,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C238" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8157,16 +8160,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8189,16 +8192,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C240" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8221,16 +8224,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C241" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8253,16 +8256,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8285,16 +8288,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C243" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8317,16 +8320,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C244" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8349,16 +8352,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C245" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8381,16 +8384,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C246" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8413,16 +8416,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C247" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8445,16 +8448,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C248" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8477,16 +8480,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C249" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8509,16 +8512,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C250" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8541,16 +8544,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C251" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8566,6 +8569,806 @@
       </c>
       <c r="J251">
         <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252" t="s">
+        <v>20</v>
+      </c>
+      <c r="B252" t="s">
+        <v>21</v>
+      </c>
+      <c r="C252" t="s">
+        <v>21</v>
+      </c>
+      <c r="D252">
+        <v>7381125</v>
+      </c>
+      <c r="E252" t="s">
+        <v>30</v>
+      </c>
+      <c r="F252">
+        <v>40</v>
+      </c>
+      <c r="G252">
+        <v>29</v>
+      </c>
+      <c r="H252">
+        <v>11</v>
+      </c>
+      <c r="I252">
+        <v>30</v>
+      </c>
+      <c r="J252">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" t="s">
+        <v>20</v>
+      </c>
+      <c r="B253" t="s">
+        <v>21</v>
+      </c>
+      <c r="C253" t="s">
+        <v>21</v>
+      </c>
+      <c r="D253">
+        <v>2207663</v>
+      </c>
+      <c r="E253" t="s">
+        <v>31</v>
+      </c>
+      <c r="F253">
+        <v>22</v>
+      </c>
+      <c r="G253">
+        <v>18</v>
+      </c>
+      <c r="H253">
+        <v>8</v>
+      </c>
+      <c r="I253">
+        <v>19</v>
+      </c>
+      <c r="J253">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" t="s">
+        <v>20</v>
+      </c>
+      <c r="B254" t="s">
+        <v>21</v>
+      </c>
+      <c r="C254" t="s">
+        <v>21</v>
+      </c>
+      <c r="D254">
+        <v>7397528</v>
+      </c>
+      <c r="E254" t="s">
+        <v>32</v>
+      </c>
+      <c r="F254">
+        <v>36</v>
+      </c>
+      <c r="G254">
+        <v>32</v>
+      </c>
+      <c r="H254">
+        <v>14</v>
+      </c>
+      <c r="I254">
+        <v>37</v>
+      </c>
+      <c r="J254">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" t="s">
+        <v>20</v>
+      </c>
+      <c r="B255" t="s">
+        <v>21</v>
+      </c>
+      <c r="C255" t="s">
+        <v>21</v>
+      </c>
+      <c r="D255">
+        <v>5931712</v>
+      </c>
+      <c r="E255" t="s">
+        <v>33</v>
+      </c>
+      <c r="F255">
+        <v>44</v>
+      </c>
+      <c r="G255">
+        <v>32</v>
+      </c>
+      <c r="H255">
+        <v>17</v>
+      </c>
+      <c r="I255">
+        <v>29</v>
+      </c>
+      <c r="J255">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" t="s">
+        <v>20</v>
+      </c>
+      <c r="B256" t="s">
+        <v>21</v>
+      </c>
+      <c r="C256" t="s">
+        <v>21</v>
+      </c>
+      <c r="D256">
+        <v>7325488</v>
+      </c>
+      <c r="E256" t="s">
+        <v>34</v>
+      </c>
+      <c r="F256">
+        <v>92</v>
+      </c>
+      <c r="G256">
+        <v>43</v>
+      </c>
+      <c r="H256">
+        <v>17</v>
+      </c>
+      <c r="I256">
+        <v>52</v>
+      </c>
+      <c r="J256">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" t="s">
+        <v>20</v>
+      </c>
+      <c r="B257" t="s">
+        <v>21</v>
+      </c>
+      <c r="C257" t="s">
+        <v>21</v>
+      </c>
+      <c r="D257">
+        <v>3368175</v>
+      </c>
+      <c r="E257" t="s">
+        <v>35</v>
+      </c>
+      <c r="F257">
+        <v>37</v>
+      </c>
+      <c r="G257">
+        <v>22</v>
+      </c>
+      <c r="H257">
+        <v>9</v>
+      </c>
+      <c r="I257">
+        <v>41</v>
+      </c>
+      <c r="J257">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" t="s">
+        <v>20</v>
+      </c>
+      <c r="B258" t="s">
+        <v>21</v>
+      </c>
+      <c r="C258" t="s">
+        <v>21</v>
+      </c>
+      <c r="D258">
+        <v>3864716</v>
+      </c>
+      <c r="E258" t="s">
+        <v>36</v>
+      </c>
+      <c r="F258">
+        <v>75</v>
+      </c>
+      <c r="G258">
+        <v>47</v>
+      </c>
+      <c r="H258">
+        <v>15</v>
+      </c>
+      <c r="I258">
+        <v>67</v>
+      </c>
+      <c r="J258">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259" t="s">
+        <v>20</v>
+      </c>
+      <c r="B259" t="s">
+        <v>21</v>
+      </c>
+      <c r="C259" t="s">
+        <v>21</v>
+      </c>
+      <c r="D259">
+        <v>3367403</v>
+      </c>
+      <c r="E259" t="s">
+        <v>37</v>
+      </c>
+      <c r="F259">
+        <v>8</v>
+      </c>
+      <c r="G259">
+        <v>15</v>
+      </c>
+      <c r="H259">
+        <v>10</v>
+      </c>
+      <c r="I259">
+        <v>6</v>
+      </c>
+      <c r="J259">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260" t="s">
+        <v>20</v>
+      </c>
+      <c r="B260" t="s">
+        <v>21</v>
+      </c>
+      <c r="C260" t="s">
+        <v>21</v>
+      </c>
+      <c r="D260">
+        <v>7381124</v>
+      </c>
+      <c r="E260" t="s">
+        <v>38</v>
+      </c>
+      <c r="F260">
+        <v>62</v>
+      </c>
+      <c r="G260">
+        <v>28</v>
+      </c>
+      <c r="H260">
+        <v>11</v>
+      </c>
+      <c r="I260">
+        <v>30</v>
+      </c>
+      <c r="J260">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" t="s">
+        <v>20</v>
+      </c>
+      <c r="B261" t="s">
+        <v>21</v>
+      </c>
+      <c r="C261" t="s">
+        <v>22</v>
+      </c>
+      <c r="D261">
+        <v>7079978</v>
+      </c>
+      <c r="E261" t="s">
+        <v>39</v>
+      </c>
+      <c r="F261">
+        <v>5</v>
+      </c>
+      <c r="G261">
+        <v>18</v>
+      </c>
+      <c r="H261">
+        <v>2</v>
+      </c>
+      <c r="I261">
+        <v>9</v>
+      </c>
+      <c r="J261">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" t="s">
+        <v>20</v>
+      </c>
+      <c r="B262" t="s">
+        <v>21</v>
+      </c>
+      <c r="C262" t="s">
+        <v>22</v>
+      </c>
+      <c r="D262">
+        <v>3367739</v>
+      </c>
+      <c r="E262" t="s">
+        <v>40</v>
+      </c>
+      <c r="F262">
+        <v>9</v>
+      </c>
+      <c r="G262">
+        <v>11</v>
+      </c>
+      <c r="H262">
+        <v>4</v>
+      </c>
+      <c r="I262">
+        <v>8</v>
+      </c>
+      <c r="J262">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263" t="s">
+        <v>20</v>
+      </c>
+      <c r="B263" t="s">
+        <v>21</v>
+      </c>
+      <c r="C263" t="s">
+        <v>23</v>
+      </c>
+      <c r="D263">
+        <v>7072286</v>
+      </c>
+      <c r="E263" t="s">
+        <v>41</v>
+      </c>
+      <c r="F263">
+        <v>1</v>
+      </c>
+      <c r="G263">
+        <v>1</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>2</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264" t="s">
+        <v>20</v>
+      </c>
+      <c r="B264" t="s">
+        <v>21</v>
+      </c>
+      <c r="C264" t="s">
+        <v>24</v>
+      </c>
+      <c r="D264">
+        <v>3367743</v>
+      </c>
+      <c r="E264" t="s">
+        <v>42</v>
+      </c>
+      <c r="F264">
+        <v>3</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265" t="s">
+        <v>20</v>
+      </c>
+      <c r="B265" t="s">
+        <v>21</v>
+      </c>
+      <c r="C265" t="s">
+        <v>23</v>
+      </c>
+      <c r="D265">
+        <v>4214024</v>
+      </c>
+      <c r="E265" t="s">
+        <v>43</v>
+      </c>
+      <c r="F265">
+        <v>4</v>
+      </c>
+      <c r="G265">
+        <v>3</v>
+      </c>
+      <c r="H265">
+        <v>3</v>
+      </c>
+      <c r="I265">
+        <v>9</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" t="s">
+        <v>20</v>
+      </c>
+      <c r="B266" t="s">
+        <v>21</v>
+      </c>
+      <c r="C266" t="s">
+        <v>24</v>
+      </c>
+      <c r="D266">
+        <v>7357843</v>
+      </c>
+      <c r="E266" t="s">
+        <v>44</v>
+      </c>
+      <c r="F266">
+        <v>46</v>
+      </c>
+      <c r="G266">
+        <v>10</v>
+      </c>
+      <c r="H266">
+        <v>3</v>
+      </c>
+      <c r="I266">
+        <v>9</v>
+      </c>
+      <c r="J266">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" t="s">
+        <v>20</v>
+      </c>
+      <c r="B267" t="s">
+        <v>21</v>
+      </c>
+      <c r="C267" t="s">
+        <v>24</v>
+      </c>
+      <c r="D267">
+        <v>7077448</v>
+      </c>
+      <c r="E267" t="s">
+        <v>45</v>
+      </c>
+      <c r="F267">
+        <v>3</v>
+      </c>
+      <c r="G267">
+        <v>1</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268" t="s">
+        <v>20</v>
+      </c>
+      <c r="B268" t="s">
+        <v>21</v>
+      </c>
+      <c r="C268" t="s">
+        <v>25</v>
+      </c>
+      <c r="D268">
+        <v>2278099</v>
+      </c>
+      <c r="E268" t="s">
+        <v>46</v>
+      </c>
+      <c r="F268">
+        <v>38</v>
+      </c>
+      <c r="G268">
+        <v>45</v>
+      </c>
+      <c r="H268">
+        <v>7</v>
+      </c>
+      <c r="I268">
+        <v>30</v>
+      </c>
+      <c r="J268">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269" t="s">
+        <v>20</v>
+      </c>
+      <c r="B269" t="s">
+        <v>21</v>
+      </c>
+      <c r="C269" t="s">
+        <v>25</v>
+      </c>
+      <c r="D269">
+        <v>7077738</v>
+      </c>
+      <c r="E269" t="s">
+        <v>47</v>
+      </c>
+      <c r="F269">
+        <v>14</v>
+      </c>
+      <c r="G269">
+        <v>3</v>
+      </c>
+      <c r="H269">
+        <v>1</v>
+      </c>
+      <c r="I269">
+        <v>6</v>
+      </c>
+      <c r="J269">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270" t="s">
+        <v>20</v>
+      </c>
+      <c r="B270" t="s">
+        <v>21</v>
+      </c>
+      <c r="C270" t="s">
+        <v>25</v>
+      </c>
+      <c r="D270">
+        <v>4493936</v>
+      </c>
+      <c r="E270" t="s">
+        <v>48</v>
+      </c>
+      <c r="F270">
+        <v>17</v>
+      </c>
+      <c r="G270">
+        <v>8</v>
+      </c>
+      <c r="H270">
+        <v>2</v>
+      </c>
+      <c r="I270">
+        <v>6</v>
+      </c>
+      <c r="J270">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271" t="s">
+        <v>20</v>
+      </c>
+      <c r="B271" t="s">
+        <v>21</v>
+      </c>
+      <c r="C271" t="s">
+        <v>25</v>
+      </c>
+      <c r="D271">
+        <v>5284531</v>
+      </c>
+      <c r="E271" t="s">
+        <v>49</v>
+      </c>
+      <c r="F271">
+        <v>7</v>
+      </c>
+      <c r="G271">
+        <v>3</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>5</v>
+      </c>
+      <c r="J271">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272" t="s">
+        <v>20</v>
+      </c>
+      <c r="B272" t="s">
+        <v>21</v>
+      </c>
+      <c r="C272" t="s">
+        <v>26</v>
+      </c>
+      <c r="D272">
+        <v>5954007</v>
+      </c>
+      <c r="E272" t="s">
+        <v>50</v>
+      </c>
+      <c r="F272">
+        <v>116</v>
+      </c>
+      <c r="G272">
+        <v>19</v>
+      </c>
+      <c r="H272">
+        <v>6</v>
+      </c>
+      <c r="I272">
+        <v>17</v>
+      </c>
+      <c r="J272">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273" t="s">
+        <v>20</v>
+      </c>
+      <c r="B273" t="s">
+        <v>21</v>
+      </c>
+      <c r="C273" t="s">
+        <v>26</v>
+      </c>
+      <c r="D273">
+        <v>7081903</v>
+      </c>
+      <c r="E273" t="s">
+        <v>51</v>
+      </c>
+      <c r="F273">
+        <v>58</v>
+      </c>
+      <c r="G273">
+        <v>19</v>
+      </c>
+      <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273">
+        <v>24</v>
+      </c>
+      <c r="J273">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274" t="s">
+        <v>20</v>
+      </c>
+      <c r="B274" t="s">
+        <v>21</v>
+      </c>
+      <c r="C274" t="s">
+        <v>27</v>
+      </c>
+      <c r="D274">
+        <v>9366541</v>
+      </c>
+      <c r="E274" t="s">
+        <v>52</v>
+      </c>
+      <c r="F274">
+        <v>43</v>
+      </c>
+      <c r="G274">
+        <v>16</v>
+      </c>
+      <c r="H274">
+        <v>1</v>
+      </c>
+      <c r="I274">
+        <v>17</v>
+      </c>
+      <c r="J274">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="A275" t="s">
+        <v>20</v>
+      </c>
+      <c r="B275" t="s">
+        <v>21</v>
+      </c>
+      <c r="C275" t="s">
+        <v>28</v>
+      </c>
+      <c r="D275">
+        <v>6435172</v>
+      </c>
+      <c r="E275" t="s">
+        <v>53</v>
+      </c>
+      <c r="F275">
+        <v>12</v>
+      </c>
+      <c r="G275">
+        <v>10</v>
+      </c>
+      <c r="H275">
+        <v>6</v>
+      </c>
+      <c r="I275">
+        <v>8</v>
+      </c>
+      <c r="J275">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="A276" t="s">
+        <v>20</v>
+      </c>
+      <c r="B276" t="s">
+        <v>21</v>
+      </c>
+      <c r="C276" t="s">
+        <v>29</v>
+      </c>
+      <c r="D276">
+        <v>7077736</v>
+      </c>
+      <c r="E276" t="s">
+        <v>54</v>
+      </c>
+      <c r="F276">
+        <v>5</v>
+      </c>
+      <c r="G276">
+        <v>4</v>
+      </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
+      <c r="I276">
+        <v>6</v>
+      </c>
+      <c r="J276">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="57">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -536,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -576,16 +582,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -608,16 +614,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -640,16 +646,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -672,16 +678,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -704,16 +710,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -736,16 +742,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -768,16 +774,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -800,16 +806,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -832,16 +838,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -864,16 +870,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -896,16 +902,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -928,16 +934,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -960,16 +966,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -992,16 +998,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1024,16 +1030,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1056,16 +1062,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1088,16 +1094,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1120,16 +1126,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1152,16 +1158,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1184,16 +1190,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1216,16 +1222,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1248,16 +1254,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1280,16 +1286,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1312,16 +1318,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1344,16 +1350,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1376,16 +1382,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1408,16 +1414,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1440,16 +1446,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1472,16 +1478,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1504,16 +1510,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1536,16 +1542,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1568,16 +1574,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1600,16 +1606,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1632,16 +1638,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1664,16 +1670,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1696,16 +1702,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1728,16 +1734,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1760,16 +1766,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1792,16 +1798,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1824,16 +1830,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1856,16 +1862,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1888,16 +1894,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1920,16 +1926,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1952,16 +1958,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1984,16 +1990,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2016,16 +2022,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2048,16 +2054,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2080,16 +2086,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2112,16 +2118,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2144,16 +2150,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2176,16 +2182,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2208,16 +2214,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2240,16 +2246,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2272,16 +2278,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2304,16 +2310,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2336,16 +2342,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2368,16 +2374,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2400,16 +2406,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2432,16 +2438,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2464,16 +2470,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2496,16 +2502,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2528,16 +2534,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2560,16 +2566,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2592,16 +2598,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2624,16 +2630,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2656,16 +2662,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2688,16 +2694,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2720,16 +2726,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2752,16 +2758,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2784,16 +2790,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2816,16 +2822,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2848,16 +2854,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2880,16 +2886,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2912,16 +2918,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2944,16 +2950,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2976,16 +2982,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3008,16 +3014,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3040,16 +3046,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3072,16 +3078,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3104,16 +3110,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3136,16 +3142,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3168,16 +3174,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3200,16 +3206,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3232,16 +3238,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3264,16 +3270,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3296,16 +3302,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3328,16 +3334,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3360,16 +3366,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3392,16 +3398,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3424,16 +3430,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3456,16 +3462,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3488,16 +3494,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3520,16 +3526,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3552,16 +3558,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3584,16 +3590,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3616,16 +3622,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C97" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3648,16 +3654,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C98" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3680,16 +3686,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3712,16 +3718,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3744,16 +3750,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3776,16 +3782,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C102" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3808,16 +3814,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3840,16 +3846,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3872,16 +3878,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3904,16 +3910,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3936,16 +3942,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3968,16 +3974,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4000,16 +4006,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4032,16 +4038,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4064,16 +4070,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C111" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4096,16 +4102,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4128,16 +4134,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4160,16 +4166,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C114" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4192,16 +4198,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4224,16 +4230,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4256,16 +4262,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4288,16 +4294,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4320,16 +4326,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4352,16 +4358,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4384,16 +4390,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4416,16 +4422,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C122" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4448,16 +4454,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4480,16 +4486,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4512,16 +4518,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C125" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4544,16 +4550,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4576,16 +4582,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C127" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4608,16 +4614,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4640,16 +4646,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C129" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4672,16 +4678,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4704,16 +4710,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4736,16 +4742,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4768,16 +4774,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C133" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4800,16 +4806,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C134" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4832,16 +4838,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C135" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4864,16 +4870,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4896,16 +4902,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C137" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4928,16 +4934,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C138" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4960,16 +4966,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C139" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -4992,16 +4998,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5024,16 +5030,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5056,16 +5062,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C142" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5088,16 +5094,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C143" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5120,16 +5126,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5152,16 +5158,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5184,16 +5190,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5216,16 +5222,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C147" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5248,16 +5254,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C148" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5280,16 +5286,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5312,16 +5318,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5344,16 +5350,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C151" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5376,16 +5382,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C152" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5408,16 +5414,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5440,16 +5446,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C154" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5472,16 +5478,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C155" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5504,16 +5510,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C156" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5536,16 +5542,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5568,16 +5574,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C158" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5600,16 +5606,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5632,16 +5638,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C160" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5664,16 +5670,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C161" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5696,16 +5702,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C162" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5728,16 +5734,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C163" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5760,16 +5766,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C164" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5792,16 +5798,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C165" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5824,16 +5830,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C166" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5856,16 +5862,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C167" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5888,16 +5894,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5920,16 +5926,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C169" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5952,16 +5958,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C170" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5984,16 +5990,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C171" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6016,16 +6022,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C172" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6048,16 +6054,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C173" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6080,16 +6086,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C174" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6112,16 +6118,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6144,16 +6150,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C176" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6176,16 +6182,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6208,16 +6214,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C178" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6240,16 +6246,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C179" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6272,16 +6278,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C180" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6304,16 +6310,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C181" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6336,16 +6342,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C182" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6368,16 +6374,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C183" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6400,16 +6406,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C184" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6432,16 +6438,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C185" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6464,16 +6470,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C186" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6496,16 +6502,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6528,16 +6534,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6560,16 +6566,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6592,16 +6598,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C190" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6624,16 +6630,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C191" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6656,16 +6662,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C192" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6688,16 +6694,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C193" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6720,16 +6726,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C194" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6752,16 +6758,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C195" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6784,16 +6790,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C196" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6816,16 +6822,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C197" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6848,16 +6854,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C198" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6880,16 +6886,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C199" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6912,16 +6918,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C200" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6944,16 +6950,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C201" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6976,16 +6982,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C202" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7008,16 +7014,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C203" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7040,16 +7046,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7072,16 +7078,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C205" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7104,16 +7110,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C206" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7136,16 +7142,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C207" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7168,16 +7174,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C208" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7200,16 +7206,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C209" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7232,16 +7238,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C210" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7264,16 +7270,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C211" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7296,16 +7302,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C212" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7328,16 +7334,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C213" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7360,16 +7366,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C214" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7392,16 +7398,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7424,16 +7430,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7456,16 +7462,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C217" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7488,16 +7494,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C218" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7520,16 +7526,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C219" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7552,16 +7558,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C220" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7584,16 +7590,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C221" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7616,16 +7622,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C222" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7648,16 +7654,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C223" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7680,16 +7686,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7712,16 +7718,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C225" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7744,16 +7750,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C226" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7776,16 +7782,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C227" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7808,16 +7814,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C228" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7840,16 +7846,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C229" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7872,16 +7878,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C230" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7904,16 +7910,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C231" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7936,16 +7942,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C232" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7968,16 +7974,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C233" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8000,16 +8006,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C234" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8032,16 +8038,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C235" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8064,16 +8070,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C236" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8096,16 +8102,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C237" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8128,16 +8134,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C238" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8160,16 +8166,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C239" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8192,16 +8198,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C240" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8224,16 +8230,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C241" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8256,16 +8262,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C242" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8288,16 +8294,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C243" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8320,16 +8326,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8352,16 +8358,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8384,16 +8390,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C246" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8416,16 +8422,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8448,16 +8454,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8480,16 +8486,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8512,16 +8518,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8544,16 +8550,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8576,16 +8582,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8608,16 +8614,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8640,16 +8646,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8672,16 +8678,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8704,16 +8710,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8736,16 +8742,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8768,16 +8774,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8800,16 +8806,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8832,16 +8838,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8864,16 +8870,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8896,16 +8902,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8928,16 +8934,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8960,16 +8966,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -8992,16 +8998,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9024,16 +9030,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9056,16 +9062,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9088,16 +9094,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9120,16 +9126,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9152,16 +9158,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9184,16 +9190,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9216,16 +9222,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C272" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9248,16 +9254,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C273" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9280,16 +9286,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9312,16 +9318,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9344,16 +9350,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C276" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9369,6 +9375,1606 @@
       </c>
       <c r="J276">
         <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="A277" t="s">
+        <v>21</v>
+      </c>
+      <c r="B277" t="s">
+        <v>23</v>
+      </c>
+      <c r="C277" t="s">
+        <v>23</v>
+      </c>
+      <c r="D277">
+        <v>7381125</v>
+      </c>
+      <c r="E277" t="s">
+        <v>32</v>
+      </c>
+      <c r="F277">
+        <v>45</v>
+      </c>
+      <c r="G277">
+        <v>19</v>
+      </c>
+      <c r="H277">
+        <v>5</v>
+      </c>
+      <c r="I277">
+        <v>22</v>
+      </c>
+      <c r="J277">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278" t="s">
+        <v>21</v>
+      </c>
+      <c r="B278" t="s">
+        <v>23</v>
+      </c>
+      <c r="C278" t="s">
+        <v>23</v>
+      </c>
+      <c r="D278">
+        <v>2207663</v>
+      </c>
+      <c r="E278" t="s">
+        <v>33</v>
+      </c>
+      <c r="F278">
+        <v>20</v>
+      </c>
+      <c r="G278">
+        <v>17</v>
+      </c>
+      <c r="H278">
+        <v>3</v>
+      </c>
+      <c r="I278">
+        <v>23</v>
+      </c>
+      <c r="J278">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279" t="s">
+        <v>21</v>
+      </c>
+      <c r="B279" t="s">
+        <v>23</v>
+      </c>
+      <c r="C279" t="s">
+        <v>23</v>
+      </c>
+      <c r="D279">
+        <v>7397528</v>
+      </c>
+      <c r="E279" t="s">
+        <v>34</v>
+      </c>
+      <c r="F279">
+        <v>38</v>
+      </c>
+      <c r="G279">
+        <v>22</v>
+      </c>
+      <c r="H279">
+        <v>7</v>
+      </c>
+      <c r="I279">
+        <v>35</v>
+      </c>
+      <c r="J279">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="A280" t="s">
+        <v>21</v>
+      </c>
+      <c r="B280" t="s">
+        <v>23</v>
+      </c>
+      <c r="C280" t="s">
+        <v>23</v>
+      </c>
+      <c r="D280">
+        <v>5931712</v>
+      </c>
+      <c r="E280" t="s">
+        <v>35</v>
+      </c>
+      <c r="F280">
+        <v>43</v>
+      </c>
+      <c r="G280">
+        <v>20</v>
+      </c>
+      <c r="H280">
+        <v>18</v>
+      </c>
+      <c r="I280">
+        <v>23</v>
+      </c>
+      <c r="J280">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="A281" t="s">
+        <v>21</v>
+      </c>
+      <c r="B281" t="s">
+        <v>23</v>
+      </c>
+      <c r="C281" t="s">
+        <v>23</v>
+      </c>
+      <c r="D281">
+        <v>7325488</v>
+      </c>
+      <c r="E281" t="s">
+        <v>36</v>
+      </c>
+      <c r="F281">
+        <v>90</v>
+      </c>
+      <c r="G281">
+        <v>34</v>
+      </c>
+      <c r="H281">
+        <v>18</v>
+      </c>
+      <c r="I281">
+        <v>46</v>
+      </c>
+      <c r="J281">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="A282" t="s">
+        <v>21</v>
+      </c>
+      <c r="B282" t="s">
+        <v>23</v>
+      </c>
+      <c r="C282" t="s">
+        <v>23</v>
+      </c>
+      <c r="D282">
+        <v>3368175</v>
+      </c>
+      <c r="E282" t="s">
+        <v>37</v>
+      </c>
+      <c r="F282">
+        <v>34</v>
+      </c>
+      <c r="G282">
+        <v>30</v>
+      </c>
+      <c r="H282">
+        <v>6</v>
+      </c>
+      <c r="I282">
+        <v>36</v>
+      </c>
+      <c r="J282">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="A283" t="s">
+        <v>21</v>
+      </c>
+      <c r="B283" t="s">
+        <v>23</v>
+      </c>
+      <c r="C283" t="s">
+        <v>23</v>
+      </c>
+      <c r="D283">
+        <v>3864716</v>
+      </c>
+      <c r="E283" t="s">
+        <v>38</v>
+      </c>
+      <c r="F283">
+        <v>103</v>
+      </c>
+      <c r="G283">
+        <v>28</v>
+      </c>
+      <c r="H283">
+        <v>4</v>
+      </c>
+      <c r="I283">
+        <v>27</v>
+      </c>
+      <c r="J283">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="A284" t="s">
+        <v>21</v>
+      </c>
+      <c r="B284" t="s">
+        <v>23</v>
+      </c>
+      <c r="C284" t="s">
+        <v>23</v>
+      </c>
+      <c r="D284">
+        <v>3367403</v>
+      </c>
+      <c r="E284" t="s">
+        <v>39</v>
+      </c>
+      <c r="F284">
+        <v>8</v>
+      </c>
+      <c r="G284">
+        <v>12</v>
+      </c>
+      <c r="H284">
+        <v>3</v>
+      </c>
+      <c r="I284">
+        <v>18</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285" t="s">
+        <v>21</v>
+      </c>
+      <c r="B285" t="s">
+        <v>23</v>
+      </c>
+      <c r="C285" t="s">
+        <v>23</v>
+      </c>
+      <c r="D285">
+        <v>7381124</v>
+      </c>
+      <c r="E285" t="s">
+        <v>40</v>
+      </c>
+      <c r="F285">
+        <v>69</v>
+      </c>
+      <c r="G285">
+        <v>28</v>
+      </c>
+      <c r="H285">
+        <v>7</v>
+      </c>
+      <c r="I285">
+        <v>17</v>
+      </c>
+      <c r="J285">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286" t="s">
+        <v>21</v>
+      </c>
+      <c r="B286" t="s">
+        <v>23</v>
+      </c>
+      <c r="C286" t="s">
+        <v>24</v>
+      </c>
+      <c r="D286">
+        <v>7079978</v>
+      </c>
+      <c r="E286" t="s">
+        <v>41</v>
+      </c>
+      <c r="F286">
+        <v>9</v>
+      </c>
+      <c r="G286">
+        <v>10</v>
+      </c>
+      <c r="H286">
+        <v>1</v>
+      </c>
+      <c r="I286">
+        <v>16</v>
+      </c>
+      <c r="J286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="A287" t="s">
+        <v>21</v>
+      </c>
+      <c r="B287" t="s">
+        <v>23</v>
+      </c>
+      <c r="C287" t="s">
+        <v>24</v>
+      </c>
+      <c r="D287">
+        <v>3367739</v>
+      </c>
+      <c r="E287" t="s">
+        <v>42</v>
+      </c>
+      <c r="F287">
+        <v>16</v>
+      </c>
+      <c r="G287">
+        <v>4</v>
+      </c>
+      <c r="H287">
+        <v>1</v>
+      </c>
+      <c r="I287">
+        <v>9</v>
+      </c>
+      <c r="J287">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="A288" t="s">
+        <v>21</v>
+      </c>
+      <c r="B288" t="s">
+        <v>23</v>
+      </c>
+      <c r="C288" t="s">
+        <v>25</v>
+      </c>
+      <c r="D288">
+        <v>7072286</v>
+      </c>
+      <c r="E288" t="s">
+        <v>43</v>
+      </c>
+      <c r="F288">
+        <v>2</v>
+      </c>
+      <c r="G288">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>1</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" t="s">
+        <v>21</v>
+      </c>
+      <c r="B289" t="s">
+        <v>23</v>
+      </c>
+      <c r="C289" t="s">
+        <v>26</v>
+      </c>
+      <c r="D289">
+        <v>3367743</v>
+      </c>
+      <c r="E289" t="s">
+        <v>44</v>
+      </c>
+      <c r="F289">
+        <v>2</v>
+      </c>
+      <c r="G289">
+        <v>3</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" t="s">
+        <v>21</v>
+      </c>
+      <c r="B290" t="s">
+        <v>23</v>
+      </c>
+      <c r="C290" t="s">
+        <v>25</v>
+      </c>
+      <c r="D290">
+        <v>4214024</v>
+      </c>
+      <c r="E290" t="s">
+        <v>45</v>
+      </c>
+      <c r="F290">
+        <v>3</v>
+      </c>
+      <c r="G290">
+        <v>4</v>
+      </c>
+      <c r="H290">
+        <v>1</v>
+      </c>
+      <c r="I290">
+        <v>9</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291" t="s">
+        <v>21</v>
+      </c>
+      <c r="B291" t="s">
+        <v>23</v>
+      </c>
+      <c r="C291" t="s">
+        <v>26</v>
+      </c>
+      <c r="D291">
+        <v>7357843</v>
+      </c>
+      <c r="E291" t="s">
+        <v>46</v>
+      </c>
+      <c r="F291">
+        <v>51</v>
+      </c>
+      <c r="G291">
+        <v>26</v>
+      </c>
+      <c r="H291">
+        <v>6</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292" t="s">
+        <v>21</v>
+      </c>
+      <c r="B292" t="s">
+        <v>23</v>
+      </c>
+      <c r="C292" t="s">
+        <v>26</v>
+      </c>
+      <c r="D292">
+        <v>7077448</v>
+      </c>
+      <c r="E292" t="s">
+        <v>47</v>
+      </c>
+      <c r="F292">
+        <v>3</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293" t="s">
+        <v>21</v>
+      </c>
+      <c r="B293" t="s">
+        <v>23</v>
+      </c>
+      <c r="C293" t="s">
+        <v>27</v>
+      </c>
+      <c r="D293">
+        <v>2278099</v>
+      </c>
+      <c r="E293" t="s">
+        <v>48</v>
+      </c>
+      <c r="F293">
+        <v>44</v>
+      </c>
+      <c r="G293">
+        <v>35</v>
+      </c>
+      <c r="H293">
+        <v>4</v>
+      </c>
+      <c r="I293">
+        <v>43</v>
+      </c>
+      <c r="J293">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294" t="s">
+        <v>21</v>
+      </c>
+      <c r="B294" t="s">
+        <v>23</v>
+      </c>
+      <c r="C294" t="s">
+        <v>27</v>
+      </c>
+      <c r="D294">
+        <v>7077738</v>
+      </c>
+      <c r="E294" t="s">
+        <v>49</v>
+      </c>
+      <c r="F294">
+        <v>11</v>
+      </c>
+      <c r="G294">
+        <v>3</v>
+      </c>
+      <c r="H294">
+        <v>3</v>
+      </c>
+      <c r="I294">
+        <v>4</v>
+      </c>
+      <c r="J294">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="A295" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" t="s">
+        <v>23</v>
+      </c>
+      <c r="C295" t="s">
+        <v>27</v>
+      </c>
+      <c r="D295">
+        <v>4493936</v>
+      </c>
+      <c r="E295" t="s">
+        <v>50</v>
+      </c>
+      <c r="F295">
+        <v>20</v>
+      </c>
+      <c r="G295">
+        <v>3</v>
+      </c>
+      <c r="H295">
+        <v>2</v>
+      </c>
+      <c r="I295">
+        <v>4</v>
+      </c>
+      <c r="J295">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="A296" t="s">
+        <v>21</v>
+      </c>
+      <c r="B296" t="s">
+        <v>23</v>
+      </c>
+      <c r="C296" t="s">
+        <v>27</v>
+      </c>
+      <c r="D296">
+        <v>5284531</v>
+      </c>
+      <c r="E296" t="s">
+        <v>51</v>
+      </c>
+      <c r="F296">
+        <v>9</v>
+      </c>
+      <c r="G296">
+        <v>6</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="A297" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" t="s">
+        <v>23</v>
+      </c>
+      <c r="C297" t="s">
+        <v>28</v>
+      </c>
+      <c r="D297">
+        <v>5954007</v>
+      </c>
+      <c r="E297" t="s">
+        <v>52</v>
+      </c>
+      <c r="F297">
+        <v>117</v>
+      </c>
+      <c r="G297">
+        <v>26</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <v>16</v>
+      </c>
+      <c r="J297">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="A298" t="s">
+        <v>21</v>
+      </c>
+      <c r="B298" t="s">
+        <v>23</v>
+      </c>
+      <c r="C298" t="s">
+        <v>28</v>
+      </c>
+      <c r="D298">
+        <v>7081903</v>
+      </c>
+      <c r="E298" t="s">
+        <v>53</v>
+      </c>
+      <c r="F298">
+        <v>59</v>
+      </c>
+      <c r="G298">
+        <v>15</v>
+      </c>
+      <c r="H298">
+        <v>3</v>
+      </c>
+      <c r="I298">
+        <v>16</v>
+      </c>
+      <c r="J298">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="A299" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" t="s">
+        <v>23</v>
+      </c>
+      <c r="C299" t="s">
+        <v>29</v>
+      </c>
+      <c r="D299">
+        <v>9366541</v>
+      </c>
+      <c r="E299" t="s">
+        <v>54</v>
+      </c>
+      <c r="F299">
+        <v>40</v>
+      </c>
+      <c r="G299">
+        <v>21</v>
+      </c>
+      <c r="H299">
+        <v>1</v>
+      </c>
+      <c r="I299">
+        <v>23</v>
+      </c>
+      <c r="J299">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="A300" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" t="s">
+        <v>23</v>
+      </c>
+      <c r="C300" t="s">
+        <v>30</v>
+      </c>
+      <c r="D300">
+        <v>6435172</v>
+      </c>
+      <c r="E300" t="s">
+        <v>55</v>
+      </c>
+      <c r="F300">
+        <v>10</v>
+      </c>
+      <c r="G300">
+        <v>8</v>
+      </c>
+      <c r="H300">
+        <v>3</v>
+      </c>
+      <c r="I300">
+        <v>14</v>
+      </c>
+      <c r="J300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="A301" t="s">
+        <v>21</v>
+      </c>
+      <c r="B301" t="s">
+        <v>23</v>
+      </c>
+      <c r="C301" t="s">
+        <v>31</v>
+      </c>
+      <c r="D301">
+        <v>7077736</v>
+      </c>
+      <c r="E301" t="s">
+        <v>56</v>
+      </c>
+      <c r="F301">
+        <v>9</v>
+      </c>
+      <c r="G301">
+        <v>2</v>
+      </c>
+      <c r="H301">
+        <v>1</v>
+      </c>
+      <c r="I301">
+        <v>4</v>
+      </c>
+      <c r="J301">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="A302" t="s">
+        <v>22</v>
+      </c>
+      <c r="B302" t="s">
+        <v>23</v>
+      </c>
+      <c r="C302" t="s">
+        <v>23</v>
+      </c>
+      <c r="D302">
+        <v>7381125</v>
+      </c>
+      <c r="E302" t="s">
+        <v>32</v>
+      </c>
+      <c r="F302">
+        <v>44</v>
+      </c>
+      <c r="G302">
+        <v>15</v>
+      </c>
+      <c r="H302">
+        <v>3</v>
+      </c>
+      <c r="I302">
+        <v>21</v>
+      </c>
+      <c r="J302">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="A303" t="s">
+        <v>22</v>
+      </c>
+      <c r="B303" t="s">
+        <v>23</v>
+      </c>
+      <c r="C303" t="s">
+        <v>23</v>
+      </c>
+      <c r="D303">
+        <v>2207663</v>
+      </c>
+      <c r="E303" t="s">
+        <v>33</v>
+      </c>
+      <c r="F303">
+        <v>20</v>
+      </c>
+      <c r="G303">
+        <v>9</v>
+      </c>
+      <c r="H303">
+        <v>3</v>
+      </c>
+      <c r="I303">
+        <v>15</v>
+      </c>
+      <c r="J303">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="A304" t="s">
+        <v>22</v>
+      </c>
+      <c r="B304" t="s">
+        <v>23</v>
+      </c>
+      <c r="C304" t="s">
+        <v>23</v>
+      </c>
+      <c r="D304">
+        <v>7397528</v>
+      </c>
+      <c r="E304" t="s">
+        <v>34</v>
+      </c>
+      <c r="F304">
+        <v>28</v>
+      </c>
+      <c r="G304">
+        <v>14</v>
+      </c>
+      <c r="H304">
+        <v>5</v>
+      </c>
+      <c r="I304">
+        <v>32</v>
+      </c>
+      <c r="J304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10">
+      <c r="A305" t="s">
+        <v>22</v>
+      </c>
+      <c r="B305" t="s">
+        <v>23</v>
+      </c>
+      <c r="C305" t="s">
+        <v>23</v>
+      </c>
+      <c r="D305">
+        <v>5931712</v>
+      </c>
+      <c r="E305" t="s">
+        <v>35</v>
+      </c>
+      <c r="F305">
+        <v>24</v>
+      </c>
+      <c r="G305">
+        <v>16</v>
+      </c>
+      <c r="H305">
+        <v>15</v>
+      </c>
+      <c r="I305">
+        <v>29</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="A306" t="s">
+        <v>22</v>
+      </c>
+      <c r="B306" t="s">
+        <v>23</v>
+      </c>
+      <c r="C306" t="s">
+        <v>23</v>
+      </c>
+      <c r="D306">
+        <v>7325488</v>
+      </c>
+      <c r="E306" t="s">
+        <v>36</v>
+      </c>
+      <c r="F306">
+        <v>83</v>
+      </c>
+      <c r="G306">
+        <v>26</v>
+      </c>
+      <c r="H306">
+        <v>16</v>
+      </c>
+      <c r="I306">
+        <v>44</v>
+      </c>
+      <c r="J306">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10">
+      <c r="A307" t="s">
+        <v>22</v>
+      </c>
+      <c r="B307" t="s">
+        <v>23</v>
+      </c>
+      <c r="C307" t="s">
+        <v>23</v>
+      </c>
+      <c r="D307">
+        <v>3368175</v>
+      </c>
+      <c r="E307" t="s">
+        <v>37</v>
+      </c>
+      <c r="F307">
+        <v>43</v>
+      </c>
+      <c r="G307">
+        <v>24</v>
+      </c>
+      <c r="H307">
+        <v>7</v>
+      </c>
+      <c r="I307">
+        <v>33</v>
+      </c>
+      <c r="J307">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10">
+      <c r="A308" t="s">
+        <v>22</v>
+      </c>
+      <c r="B308" t="s">
+        <v>23</v>
+      </c>
+      <c r="C308" t="s">
+        <v>23</v>
+      </c>
+      <c r="D308">
+        <v>3864716</v>
+      </c>
+      <c r="E308" t="s">
+        <v>38</v>
+      </c>
+      <c r="F308">
+        <v>89</v>
+      </c>
+      <c r="G308">
+        <v>23</v>
+      </c>
+      <c r="H308">
+        <v>7</v>
+      </c>
+      <c r="I308">
+        <v>41</v>
+      </c>
+      <c r="J308">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10">
+      <c r="A309" t="s">
+        <v>22</v>
+      </c>
+      <c r="B309" t="s">
+        <v>23</v>
+      </c>
+      <c r="C309" t="s">
+        <v>23</v>
+      </c>
+      <c r="D309">
+        <v>3367403</v>
+      </c>
+      <c r="E309" t="s">
+        <v>39</v>
+      </c>
+      <c r="F309">
+        <v>13</v>
+      </c>
+      <c r="G309">
+        <v>2</v>
+      </c>
+      <c r="H309">
+        <v>2</v>
+      </c>
+      <c r="I309">
+        <v>8</v>
+      </c>
+      <c r="J309">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10">
+      <c r="A310" t="s">
+        <v>22</v>
+      </c>
+      <c r="B310" t="s">
+        <v>23</v>
+      </c>
+      <c r="C310" t="s">
+        <v>23</v>
+      </c>
+      <c r="D310">
+        <v>7381124</v>
+      </c>
+      <c r="E310" t="s">
+        <v>40</v>
+      </c>
+      <c r="F310">
+        <v>43</v>
+      </c>
+      <c r="G310">
+        <v>11</v>
+      </c>
+      <c r="H310">
+        <v>8</v>
+      </c>
+      <c r="I310">
+        <v>39</v>
+      </c>
+      <c r="J310">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10">
+      <c r="A311" t="s">
+        <v>22</v>
+      </c>
+      <c r="B311" t="s">
+        <v>23</v>
+      </c>
+      <c r="C311" t="s">
+        <v>24</v>
+      </c>
+      <c r="D311">
+        <v>7079978</v>
+      </c>
+      <c r="E311" t="s">
+        <v>41</v>
+      </c>
+      <c r="F311">
+        <v>10</v>
+      </c>
+      <c r="G311">
+        <v>11</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311">
+        <v>8</v>
+      </c>
+      <c r="J311">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10">
+      <c r="A312" t="s">
+        <v>22</v>
+      </c>
+      <c r="B312" t="s">
+        <v>23</v>
+      </c>
+      <c r="C312" t="s">
+        <v>24</v>
+      </c>
+      <c r="D312">
+        <v>3367739</v>
+      </c>
+      <c r="E312" t="s">
+        <v>42</v>
+      </c>
+      <c r="F312">
+        <v>7</v>
+      </c>
+      <c r="G312">
+        <v>1</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>9</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10">
+      <c r="A313" t="s">
+        <v>22</v>
+      </c>
+      <c r="B313" t="s">
+        <v>23</v>
+      </c>
+      <c r="C313" t="s">
+        <v>25</v>
+      </c>
+      <c r="D313">
+        <v>7072286</v>
+      </c>
+      <c r="E313" t="s">
+        <v>43</v>
+      </c>
+      <c r="F313">
+        <v>3</v>
+      </c>
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>2</v>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10">
+      <c r="A314" t="s">
+        <v>22</v>
+      </c>
+      <c r="B314" t="s">
+        <v>23</v>
+      </c>
+      <c r="C314" t="s">
+        <v>26</v>
+      </c>
+      <c r="D314">
+        <v>3367743</v>
+      </c>
+      <c r="E314" t="s">
+        <v>44</v>
+      </c>
+      <c r="F314">
+        <v>5</v>
+      </c>
+      <c r="G314">
+        <v>4</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+      <c r="J314">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10">
+      <c r="A315" t="s">
+        <v>22</v>
+      </c>
+      <c r="B315" t="s">
+        <v>23</v>
+      </c>
+      <c r="C315" t="s">
+        <v>25</v>
+      </c>
+      <c r="D315">
+        <v>4214024</v>
+      </c>
+      <c r="E315" t="s">
+        <v>45</v>
+      </c>
+      <c r="F315">
+        <v>4</v>
+      </c>
+      <c r="G315">
+        <v>4</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>3</v>
+      </c>
+      <c r="J315">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10">
+      <c r="A316" t="s">
+        <v>22</v>
+      </c>
+      <c r="B316" t="s">
+        <v>23</v>
+      </c>
+      <c r="C316" t="s">
+        <v>26</v>
+      </c>
+      <c r="D316">
+        <v>7357843</v>
+      </c>
+      <c r="E316" t="s">
+        <v>46</v>
+      </c>
+      <c r="F316">
+        <v>62</v>
+      </c>
+      <c r="G316">
+        <v>8</v>
+      </c>
+      <c r="H316">
+        <v>13</v>
+      </c>
+      <c r="I316">
+        <v>5</v>
+      </c>
+      <c r="J316">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10">
+      <c r="A317" t="s">
+        <v>22</v>
+      </c>
+      <c r="B317" t="s">
+        <v>23</v>
+      </c>
+      <c r="C317" t="s">
+        <v>26</v>
+      </c>
+      <c r="D317">
+        <v>7077448</v>
+      </c>
+      <c r="E317" t="s">
+        <v>47</v>
+      </c>
+      <c r="F317">
+        <v>3</v>
+      </c>
+      <c r="G317">
+        <v>1</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>2</v>
+      </c>
+      <c r="J317">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10">
+      <c r="A318" t="s">
+        <v>22</v>
+      </c>
+      <c r="B318" t="s">
+        <v>23</v>
+      </c>
+      <c r="C318" t="s">
+        <v>27</v>
+      </c>
+      <c r="D318">
+        <v>2278099</v>
+      </c>
+      <c r="E318" t="s">
+        <v>48</v>
+      </c>
+      <c r="F318">
+        <v>40</v>
+      </c>
+      <c r="G318">
+        <v>14</v>
+      </c>
+      <c r="H318">
+        <v>9</v>
+      </c>
+      <c r="I318">
+        <v>40</v>
+      </c>
+      <c r="J318">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10">
+      <c r="A319" t="s">
+        <v>22</v>
+      </c>
+      <c r="B319" t="s">
+        <v>23</v>
+      </c>
+      <c r="C319" t="s">
+        <v>27</v>
+      </c>
+      <c r="D319">
+        <v>7077738</v>
+      </c>
+      <c r="E319" t="s">
+        <v>49</v>
+      </c>
+      <c r="F319">
+        <v>8</v>
+      </c>
+      <c r="G319">
+        <v>2</v>
+      </c>
+      <c r="H319">
+        <v>2</v>
+      </c>
+      <c r="I319">
+        <v>8</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10">
+      <c r="A320" t="s">
+        <v>22</v>
+      </c>
+      <c r="B320" t="s">
+        <v>23</v>
+      </c>
+      <c r="C320" t="s">
+        <v>27</v>
+      </c>
+      <c r="D320">
+        <v>4493936</v>
+      </c>
+      <c r="E320" t="s">
+        <v>50</v>
+      </c>
+      <c r="F320">
+        <v>14</v>
+      </c>
+      <c r="G320">
+        <v>0</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320">
+        <v>9</v>
+      </c>
+      <c r="J320">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10">
+      <c r="A321" t="s">
+        <v>22</v>
+      </c>
+      <c r="B321" t="s">
+        <v>23</v>
+      </c>
+      <c r="C321" t="s">
+        <v>27</v>
+      </c>
+      <c r="D321">
+        <v>5284531</v>
+      </c>
+      <c r="E321" t="s">
+        <v>51</v>
+      </c>
+      <c r="F321">
+        <v>7</v>
+      </c>
+      <c r="G321">
+        <v>0</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+      <c r="I321">
+        <v>8</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10">
+      <c r="A322" t="s">
+        <v>22</v>
+      </c>
+      <c r="B322" t="s">
+        <v>23</v>
+      </c>
+      <c r="C322" t="s">
+        <v>28</v>
+      </c>
+      <c r="D322">
+        <v>5954007</v>
+      </c>
+      <c r="E322" t="s">
+        <v>52</v>
+      </c>
+      <c r="F322">
+        <v>132</v>
+      </c>
+      <c r="G322">
+        <v>22</v>
+      </c>
+      <c r="H322">
+        <v>20</v>
+      </c>
+      <c r="I322">
+        <v>23</v>
+      </c>
+      <c r="J322">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10">
+      <c r="A323" t="s">
+        <v>22</v>
+      </c>
+      <c r="B323" t="s">
+        <v>23</v>
+      </c>
+      <c r="C323" t="s">
+        <v>28</v>
+      </c>
+      <c r="D323">
+        <v>7081903</v>
+      </c>
+      <c r="E323" t="s">
+        <v>53</v>
+      </c>
+      <c r="F323">
+        <v>43</v>
+      </c>
+      <c r="G323">
+        <v>7</v>
+      </c>
+      <c r="H323">
+        <v>2</v>
+      </c>
+      <c r="I323">
+        <v>26</v>
+      </c>
+      <c r="J323">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10">
+      <c r="A324" t="s">
+        <v>22</v>
+      </c>
+      <c r="B324" t="s">
+        <v>23</v>
+      </c>
+      <c r="C324" t="s">
+        <v>29</v>
+      </c>
+      <c r="D324">
+        <v>9366541</v>
+      </c>
+      <c r="E324" t="s">
+        <v>54</v>
+      </c>
+      <c r="F324">
+        <v>48</v>
+      </c>
+      <c r="G324">
+        <v>11</v>
+      </c>
+      <c r="H324">
+        <v>3</v>
+      </c>
+      <c r="I324">
+        <v>14</v>
+      </c>
+      <c r="J324">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10">
+      <c r="A325" t="s">
+        <v>22</v>
+      </c>
+      <c r="B325" t="s">
+        <v>23</v>
+      </c>
+      <c r="C325" t="s">
+        <v>30</v>
+      </c>
+      <c r="D325">
+        <v>6435172</v>
+      </c>
+      <c r="E325" t="s">
+        <v>55</v>
+      </c>
+      <c r="F325">
+        <v>17</v>
+      </c>
+      <c r="G325">
+        <v>9</v>
+      </c>
+      <c r="H325">
+        <v>3</v>
+      </c>
+      <c r="I325">
+        <v>10</v>
+      </c>
+      <c r="J325">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10">
+      <c r="A326" t="s">
+        <v>22</v>
+      </c>
+      <c r="B326" t="s">
+        <v>23</v>
+      </c>
+      <c r="C326" t="s">
+        <v>31</v>
+      </c>
+      <c r="D326">
+        <v>7077736</v>
+      </c>
+      <c r="E326" t="s">
+        <v>56</v>
+      </c>
+      <c r="F326">
+        <v>8</v>
+      </c>
+      <c r="G326">
+        <v>0</v>
+      </c>
+      <c r="H326">
+        <v>1</v>
+      </c>
+      <c r="I326">
+        <v>3</v>
+      </c>
+      <c r="J326">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="58">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -542,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J351"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -582,16 +585,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -614,16 +617,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -646,16 +649,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -678,16 +681,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -710,16 +713,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -742,16 +745,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -774,16 +777,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -806,16 +809,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -838,16 +841,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -870,16 +873,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -902,16 +905,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -934,16 +937,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -966,16 +969,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -998,16 +1001,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1030,16 +1033,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1062,16 +1065,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1094,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1126,16 +1129,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1158,16 +1161,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1190,16 +1193,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1222,16 +1225,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1254,16 +1257,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1286,16 +1289,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1318,16 +1321,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1350,16 +1353,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1382,16 +1385,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1414,16 +1417,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1446,16 +1449,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1478,16 +1481,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1510,16 +1513,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1542,16 +1545,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1574,16 +1577,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1606,16 +1609,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1638,16 +1641,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1670,16 +1673,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1702,16 +1705,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1734,16 +1737,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1766,16 +1769,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1798,16 +1801,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1830,16 +1833,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1862,16 +1865,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1894,16 +1897,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1926,16 +1929,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1958,16 +1961,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1990,16 +1993,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2022,16 +2025,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2054,16 +2057,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2086,16 +2089,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2118,16 +2121,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2150,16 +2153,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2182,16 +2185,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2214,16 +2217,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2246,16 +2249,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2278,16 +2281,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2310,16 +2313,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2342,16 +2345,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2374,16 +2377,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2406,16 +2409,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2438,16 +2441,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2470,16 +2473,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2502,16 +2505,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2534,16 +2537,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2566,16 +2569,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2598,16 +2601,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2630,16 +2633,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2662,16 +2665,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2694,16 +2697,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2726,16 +2729,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2758,16 +2761,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2790,16 +2793,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2822,16 +2825,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2854,16 +2857,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2886,16 +2889,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2918,16 +2921,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2950,16 +2953,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2982,16 +2985,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3014,16 +3017,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3046,16 +3049,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3078,16 +3081,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3110,16 +3113,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3142,16 +3145,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3174,16 +3177,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3206,16 +3209,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3238,16 +3241,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3270,16 +3273,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3302,16 +3305,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3334,16 +3337,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3366,16 +3369,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3398,16 +3401,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3430,16 +3433,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3462,16 +3465,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3494,16 +3497,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3526,16 +3529,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3558,16 +3561,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3590,16 +3593,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3622,16 +3625,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3654,16 +3657,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3686,16 +3689,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3718,16 +3721,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3750,16 +3753,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3782,16 +3785,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3814,16 +3817,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3846,16 +3849,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3878,16 +3881,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3910,16 +3913,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3942,16 +3945,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3974,16 +3977,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4006,16 +4009,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4038,16 +4041,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4070,16 +4073,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4102,16 +4105,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4134,16 +4137,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4166,16 +4169,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4198,16 +4201,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4230,16 +4233,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C116" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4262,16 +4265,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4294,16 +4297,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4326,16 +4329,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C119" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4358,16 +4361,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C120" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4390,16 +4393,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4422,16 +4425,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C122" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4454,16 +4457,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4486,16 +4489,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4518,16 +4521,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4550,16 +4553,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4582,16 +4585,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4614,16 +4617,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4646,16 +4649,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4678,16 +4681,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4710,16 +4713,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4742,16 +4745,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4774,16 +4777,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4806,16 +4809,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4838,16 +4841,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C135" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4870,16 +4873,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4902,16 +4905,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4934,16 +4937,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4966,16 +4969,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C139" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -4998,16 +5001,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5030,16 +5033,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C141" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5062,16 +5065,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C142" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5094,16 +5097,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C143" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5126,16 +5129,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C144" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5158,16 +5161,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C145" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5190,16 +5193,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C146" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5222,16 +5225,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5254,16 +5257,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5286,16 +5289,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5318,16 +5321,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5350,16 +5353,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C151" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5382,16 +5385,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5414,16 +5417,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C153" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5446,16 +5449,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5478,16 +5481,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5510,16 +5513,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5542,16 +5545,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C157" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5574,16 +5577,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5606,16 +5609,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C159" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5638,16 +5641,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C160" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5670,16 +5673,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5702,16 +5705,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5734,16 +5737,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5766,16 +5769,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C164" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5798,16 +5801,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5830,16 +5833,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5862,16 +5865,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C167" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5894,16 +5897,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C168" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5926,16 +5929,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C169" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5958,16 +5961,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C170" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5990,16 +5993,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C171" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6022,16 +6025,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6054,16 +6057,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6086,16 +6089,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C174" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6118,16 +6121,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C175" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6150,16 +6153,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C176" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6182,16 +6185,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C177" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6214,16 +6217,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C178" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6246,16 +6249,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6278,16 +6281,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C180" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6310,16 +6313,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C181" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6342,16 +6345,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C182" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6374,16 +6377,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C183" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6406,16 +6409,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C184" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6438,16 +6441,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C185" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6470,16 +6473,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C186" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6502,16 +6505,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C187" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6534,16 +6537,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C188" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6566,16 +6569,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C189" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6598,16 +6601,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6630,16 +6633,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C191" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6662,16 +6665,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C192" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6694,16 +6697,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C193" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6726,16 +6729,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C194" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6758,16 +6761,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C195" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6790,16 +6793,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C196" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6822,16 +6825,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6854,16 +6857,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C198" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6886,16 +6889,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C199" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6918,16 +6921,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C200" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6950,16 +6953,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C201" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6982,16 +6985,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C202" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7014,16 +7017,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C203" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7046,16 +7049,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7078,16 +7081,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C205" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7110,16 +7113,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7142,16 +7145,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C207" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7174,16 +7177,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7206,16 +7209,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7238,16 +7241,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C210" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7270,16 +7273,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C211" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7302,16 +7305,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7334,16 +7337,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7366,16 +7369,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C214" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7398,16 +7401,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C215" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7430,16 +7433,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C216" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7462,16 +7465,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C217" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7494,16 +7497,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C218" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7526,16 +7529,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C219" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7558,16 +7561,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C220" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7590,16 +7593,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C221" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7622,16 +7625,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C222" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7654,16 +7657,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7686,16 +7689,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C224" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7718,16 +7721,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C225" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7750,16 +7753,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C226" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7782,16 +7785,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C227" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7814,16 +7817,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C228" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7846,16 +7849,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C229" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7878,16 +7881,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C230" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7910,16 +7913,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C231" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7942,16 +7945,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C232" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7974,16 +7977,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C233" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8006,16 +8009,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C234" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8038,16 +8041,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C235" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8070,16 +8073,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C236" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8102,16 +8105,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C237" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8134,16 +8137,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C238" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8166,16 +8169,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C239" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8198,16 +8201,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C240" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8230,16 +8233,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C241" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8262,16 +8265,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C242" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8294,16 +8297,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C243" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8326,16 +8329,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C244" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8358,16 +8361,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C245" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8390,16 +8393,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C246" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8422,16 +8425,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C247" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8454,16 +8457,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C248" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8486,16 +8489,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C249" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8518,16 +8521,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C250" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8550,16 +8553,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C251" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8582,16 +8585,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C252" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8614,16 +8617,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C253" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8646,16 +8649,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C254" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8678,16 +8681,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C255" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8710,16 +8713,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C256" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8742,16 +8745,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C257" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8774,16 +8777,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C258" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8806,16 +8809,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C259" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8838,16 +8841,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8870,16 +8873,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C261" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8902,16 +8905,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C262" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8934,16 +8937,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C263" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8966,16 +8969,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C264" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -8998,16 +9001,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C265" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9030,16 +9033,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C266" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9062,16 +9065,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C267" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9094,16 +9097,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C268" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9126,16 +9129,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C269" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9158,16 +9161,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C270" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9190,16 +9193,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C271" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9222,16 +9225,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C272" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9254,16 +9257,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C273" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9286,16 +9289,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C274" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9318,16 +9321,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C275" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9350,16 +9353,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C276" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9382,16 +9385,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F277">
         <v>45</v>
@@ -9414,16 +9417,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F278">
         <v>20</v>
@@ -9446,16 +9449,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C279" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F279">
         <v>38</v>
@@ -9478,16 +9481,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C280" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F280">
         <v>43</v>
@@ -9510,16 +9513,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C281" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F281">
         <v>90</v>
@@ -9542,16 +9545,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C282" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F282">
         <v>34</v>
@@ -9574,16 +9577,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C283" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F283">
         <v>103</v>
@@ -9606,16 +9609,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C284" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -9638,16 +9641,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C285" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F285">
         <v>69</v>
@@ -9670,16 +9673,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C286" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F286">
         <v>9</v>
@@ -9702,16 +9705,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C287" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F287">
         <v>16</v>
@@ -9734,16 +9737,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C288" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F288">
         <v>2</v>
@@ -9766,16 +9769,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C289" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F289">
         <v>2</v>
@@ -9798,16 +9801,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C290" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F290">
         <v>3</v>
@@ -9830,16 +9833,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C291" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F291">
         <v>51</v>
@@ -9862,16 +9865,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C292" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F292">
         <v>3</v>
@@ -9894,16 +9897,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C293" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F293">
         <v>44</v>
@@ -9926,16 +9929,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C294" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F294">
         <v>11</v>
@@ -9958,16 +9961,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C295" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F295">
         <v>20</v>
@@ -9990,16 +9993,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C296" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F296">
         <v>9</v>
@@ -10022,16 +10025,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C297" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F297">
         <v>117</v>
@@ -10054,16 +10057,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C298" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F298">
         <v>59</v>
@@ -10086,16 +10089,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C299" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F299">
         <v>40</v>
@@ -10118,16 +10121,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C300" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F300">
         <v>10</v>
@@ -10150,16 +10153,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C301" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F301">
         <v>9</v>
@@ -10182,16 +10185,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C302" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F302">
         <v>44</v>
@@ -10214,16 +10217,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C303" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F303">
         <v>20</v>
@@ -10246,16 +10249,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C304" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F304">
         <v>28</v>
@@ -10278,16 +10281,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C305" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F305">
         <v>24</v>
@@ -10310,16 +10313,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C306" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F306">
         <v>83</v>
@@ -10342,16 +10345,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C307" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F307">
         <v>43</v>
@@ -10374,16 +10377,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C308" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F308">
         <v>89</v>
@@ -10406,16 +10409,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C309" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F309">
         <v>13</v>
@@ -10438,16 +10441,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C310" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F310">
         <v>43</v>
@@ -10470,16 +10473,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C311" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F311">
         <v>10</v>
@@ -10502,16 +10505,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C312" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F312">
         <v>7</v>
@@ -10534,16 +10537,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C313" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F313">
         <v>3</v>
@@ -10566,16 +10569,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C314" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -10598,16 +10601,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C315" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -10630,16 +10633,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C316" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F316">
         <v>62</v>
@@ -10662,16 +10665,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C317" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F317">
         <v>3</v>
@@ -10694,16 +10697,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C318" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F318">
         <v>40</v>
@@ -10726,16 +10729,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C319" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F319">
         <v>8</v>
@@ -10758,16 +10761,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C320" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F320">
         <v>14</v>
@@ -10790,16 +10793,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C321" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -10822,16 +10825,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C322" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F322">
         <v>132</v>
@@ -10854,16 +10857,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C323" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F323">
         <v>43</v>
@@ -10886,16 +10889,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C324" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F324">
         <v>48</v>
@@ -10918,16 +10921,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C325" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F325">
         <v>17</v>
@@ -10950,16 +10953,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C326" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F326">
         <v>8</v>
@@ -10975,6 +10978,806 @@
       </c>
       <c r="J326">
         <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10">
+      <c r="A327" t="s">
+        <v>23</v>
+      </c>
+      <c r="B327" t="s">
+        <v>24</v>
+      </c>
+      <c r="C327" t="s">
+        <v>24</v>
+      </c>
+      <c r="D327">
+        <v>7381125</v>
+      </c>
+      <c r="E327" t="s">
+        <v>33</v>
+      </c>
+      <c r="F327">
+        <v>56</v>
+      </c>
+      <c r="G327">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+      <c r="I327">
+        <v>2</v>
+      </c>
+      <c r="J327">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10">
+      <c r="A328" t="s">
+        <v>23</v>
+      </c>
+      <c r="B328" t="s">
+        <v>24</v>
+      </c>
+      <c r="C328" t="s">
+        <v>24</v>
+      </c>
+      <c r="D328">
+        <v>2207663</v>
+      </c>
+      <c r="E328" t="s">
+        <v>34</v>
+      </c>
+      <c r="F328">
+        <v>26</v>
+      </c>
+      <c r="G328">
+        <v>8</v>
+      </c>
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
+        <v>4</v>
+      </c>
+      <c r="J328">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10">
+      <c r="A329" t="s">
+        <v>23</v>
+      </c>
+      <c r="B329" t="s">
+        <v>24</v>
+      </c>
+      <c r="C329" t="s">
+        <v>24</v>
+      </c>
+      <c r="D329">
+        <v>7397528</v>
+      </c>
+      <c r="E329" t="s">
+        <v>35</v>
+      </c>
+      <c r="F329">
+        <v>40</v>
+      </c>
+      <c r="G329">
+        <v>9</v>
+      </c>
+      <c r="H329">
+        <v>4</v>
+      </c>
+      <c r="I329">
+        <v>6</v>
+      </c>
+      <c r="J329">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10">
+      <c r="A330" t="s">
+        <v>23</v>
+      </c>
+      <c r="B330" t="s">
+        <v>24</v>
+      </c>
+      <c r="C330" t="s">
+        <v>24</v>
+      </c>
+      <c r="D330">
+        <v>5931712</v>
+      </c>
+      <c r="E330" t="s">
+        <v>36</v>
+      </c>
+      <c r="F330">
+        <v>34</v>
+      </c>
+      <c r="G330">
+        <v>8</v>
+      </c>
+      <c r="H330">
+        <v>2</v>
+      </c>
+      <c r="I330">
+        <v>9</v>
+      </c>
+      <c r="J330">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10">
+      <c r="A331" t="s">
+        <v>23</v>
+      </c>
+      <c r="B331" t="s">
+        <v>24</v>
+      </c>
+      <c r="C331" t="s">
+        <v>24</v>
+      </c>
+      <c r="D331">
+        <v>7325488</v>
+      </c>
+      <c r="E331" t="s">
+        <v>37</v>
+      </c>
+      <c r="F331">
+        <v>99</v>
+      </c>
+      <c r="G331">
+        <v>12</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>2</v>
+      </c>
+      <c r="J331">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10">
+      <c r="A332" t="s">
+        <v>23</v>
+      </c>
+      <c r="B332" t="s">
+        <v>24</v>
+      </c>
+      <c r="C332" t="s">
+        <v>24</v>
+      </c>
+      <c r="D332">
+        <v>3368175</v>
+      </c>
+      <c r="E332" t="s">
+        <v>38</v>
+      </c>
+      <c r="F332">
+        <v>51</v>
+      </c>
+      <c r="G332">
+        <v>8</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10">
+      <c r="A333" t="s">
+        <v>23</v>
+      </c>
+      <c r="B333" t="s">
+        <v>24</v>
+      </c>
+      <c r="C333" t="s">
+        <v>24</v>
+      </c>
+      <c r="D333">
+        <v>3864716</v>
+      </c>
+      <c r="E333" t="s">
+        <v>39</v>
+      </c>
+      <c r="F333">
+        <v>104</v>
+      </c>
+      <c r="G333">
+        <v>16</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+      <c r="I333">
+        <v>5</v>
+      </c>
+      <c r="J333">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10">
+      <c r="A334" t="s">
+        <v>23</v>
+      </c>
+      <c r="B334" t="s">
+        <v>24</v>
+      </c>
+      <c r="C334" t="s">
+        <v>24</v>
+      </c>
+      <c r="D334">
+        <v>3367403</v>
+      </c>
+      <c r="E334" t="s">
+        <v>40</v>
+      </c>
+      <c r="F334">
+        <v>14</v>
+      </c>
+      <c r="G334">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
+      </c>
+      <c r="I334">
+        <v>0</v>
+      </c>
+      <c r="J334">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10">
+      <c r="A335" t="s">
+        <v>23</v>
+      </c>
+      <c r="B335" t="s">
+        <v>24</v>
+      </c>
+      <c r="C335" t="s">
+        <v>24</v>
+      </c>
+      <c r="D335">
+        <v>7381124</v>
+      </c>
+      <c r="E335" t="s">
+        <v>41</v>
+      </c>
+      <c r="F335">
+        <v>49</v>
+      </c>
+      <c r="G335">
+        <v>6</v>
+      </c>
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
+        <v>12</v>
+      </c>
+      <c r="J335">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="A336" t="s">
+        <v>23</v>
+      </c>
+      <c r="B336" t="s">
+        <v>24</v>
+      </c>
+      <c r="C336" t="s">
+        <v>25</v>
+      </c>
+      <c r="D336">
+        <v>7079978</v>
+      </c>
+      <c r="E336" t="s">
+        <v>42</v>
+      </c>
+      <c r="F336">
+        <v>20</v>
+      </c>
+      <c r="G336">
+        <v>6</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10">
+      <c r="A337" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" t="s">
+        <v>24</v>
+      </c>
+      <c r="C337" t="s">
+        <v>25</v>
+      </c>
+      <c r="D337">
+        <v>3367739</v>
+      </c>
+      <c r="E337" t="s">
+        <v>43</v>
+      </c>
+      <c r="F337">
+        <v>8</v>
+      </c>
+      <c r="G337">
+        <v>2</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <v>7</v>
+      </c>
+      <c r="J337">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10">
+      <c r="A338" t="s">
+        <v>23</v>
+      </c>
+      <c r="B338" t="s">
+        <v>24</v>
+      </c>
+      <c r="C338" t="s">
+        <v>26</v>
+      </c>
+      <c r="D338">
+        <v>7072286</v>
+      </c>
+      <c r="E338" t="s">
+        <v>44</v>
+      </c>
+      <c r="F338">
+        <v>3</v>
+      </c>
+      <c r="G338">
+        <v>0</v>
+      </c>
+      <c r="H338">
+        <v>0</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10">
+      <c r="A339" t="s">
+        <v>23</v>
+      </c>
+      <c r="B339" t="s">
+        <v>24</v>
+      </c>
+      <c r="C339" t="s">
+        <v>27</v>
+      </c>
+      <c r="D339">
+        <v>3367743</v>
+      </c>
+      <c r="E339" t="s">
+        <v>45</v>
+      </c>
+      <c r="F339">
+        <v>8</v>
+      </c>
+      <c r="G339">
+        <v>0</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10">
+      <c r="A340" t="s">
+        <v>23</v>
+      </c>
+      <c r="B340" t="s">
+        <v>24</v>
+      </c>
+      <c r="C340" t="s">
+        <v>26</v>
+      </c>
+      <c r="D340">
+        <v>4214024</v>
+      </c>
+      <c r="E340" t="s">
+        <v>46</v>
+      </c>
+      <c r="F340">
+        <v>8</v>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10">
+      <c r="A341" t="s">
+        <v>23</v>
+      </c>
+      <c r="B341" t="s">
+        <v>24</v>
+      </c>
+      <c r="C341" t="s">
+        <v>27</v>
+      </c>
+      <c r="D341">
+        <v>7357843</v>
+      </c>
+      <c r="E341" t="s">
+        <v>47</v>
+      </c>
+      <c r="F341">
+        <v>68</v>
+      </c>
+      <c r="G341">
+        <v>4</v>
+      </c>
+      <c r="H341">
+        <v>1</v>
+      </c>
+      <c r="I341">
+        <v>5</v>
+      </c>
+      <c r="J341">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10">
+      <c r="A342" t="s">
+        <v>23</v>
+      </c>
+      <c r="B342" t="s">
+        <v>24</v>
+      </c>
+      <c r="C342" t="s">
+        <v>27</v>
+      </c>
+      <c r="D342">
+        <v>7077448</v>
+      </c>
+      <c r="E342" t="s">
+        <v>48</v>
+      </c>
+      <c r="F342">
+        <v>3</v>
+      </c>
+      <c r="G342">
+        <v>0</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10">
+      <c r="A343" t="s">
+        <v>23</v>
+      </c>
+      <c r="B343" t="s">
+        <v>24</v>
+      </c>
+      <c r="C343" t="s">
+        <v>28</v>
+      </c>
+      <c r="D343">
+        <v>2278099</v>
+      </c>
+      <c r="E343" t="s">
+        <v>49</v>
+      </c>
+      <c r="F343">
+        <v>48</v>
+      </c>
+      <c r="G343">
+        <v>4</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+      <c r="I343">
+        <v>8</v>
+      </c>
+      <c r="J343">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10">
+      <c r="A344" t="s">
+        <v>23</v>
+      </c>
+      <c r="B344" t="s">
+        <v>24</v>
+      </c>
+      <c r="C344" t="s">
+        <v>28</v>
+      </c>
+      <c r="D344">
+        <v>7077738</v>
+      </c>
+      <c r="E344" t="s">
+        <v>50</v>
+      </c>
+      <c r="F344">
+        <v>8</v>
+      </c>
+      <c r="G344">
+        <v>0</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="A345" t="s">
+        <v>23</v>
+      </c>
+      <c r="B345" t="s">
+        <v>24</v>
+      </c>
+      <c r="C345" t="s">
+        <v>28</v>
+      </c>
+      <c r="D345">
+        <v>4493936</v>
+      </c>
+      <c r="E345" t="s">
+        <v>51</v>
+      </c>
+      <c r="F345">
+        <v>14</v>
+      </c>
+      <c r="G345">
+        <v>1</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10">
+      <c r="A346" t="s">
+        <v>23</v>
+      </c>
+      <c r="B346" t="s">
+        <v>24</v>
+      </c>
+      <c r="C346" t="s">
+        <v>28</v>
+      </c>
+      <c r="D346">
+        <v>5284531</v>
+      </c>
+      <c r="E346" t="s">
+        <v>52</v>
+      </c>
+      <c r="F346">
+        <v>7</v>
+      </c>
+      <c r="G346">
+        <v>0</v>
+      </c>
+      <c r="H346">
+        <v>0</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10">
+      <c r="A347" t="s">
+        <v>23</v>
+      </c>
+      <c r="B347" t="s">
+        <v>24</v>
+      </c>
+      <c r="C347" t="s">
+        <v>29</v>
+      </c>
+      <c r="D347">
+        <v>5954007</v>
+      </c>
+      <c r="E347" t="s">
+        <v>53</v>
+      </c>
+      <c r="F347">
+        <v>123</v>
+      </c>
+      <c r="G347">
+        <v>4</v>
+      </c>
+      <c r="H347">
+        <v>0</v>
+      </c>
+      <c r="I347">
+        <v>14</v>
+      </c>
+      <c r="J347">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10">
+      <c r="A348" t="s">
+        <v>23</v>
+      </c>
+      <c r="B348" t="s">
+        <v>24</v>
+      </c>
+      <c r="C348" t="s">
+        <v>29</v>
+      </c>
+      <c r="D348">
+        <v>7081903</v>
+      </c>
+      <c r="E348" t="s">
+        <v>54</v>
+      </c>
+      <c r="F348">
+        <v>50</v>
+      </c>
+      <c r="G348">
+        <v>5</v>
+      </c>
+      <c r="H348">
+        <v>0</v>
+      </c>
+      <c r="I348">
+        <v>9</v>
+      </c>
+      <c r="J348">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10">
+      <c r="A349" t="s">
+        <v>23</v>
+      </c>
+      <c r="B349" t="s">
+        <v>24</v>
+      </c>
+      <c r="C349" t="s">
+        <v>30</v>
+      </c>
+      <c r="D349">
+        <v>9366541</v>
+      </c>
+      <c r="E349" t="s">
+        <v>55</v>
+      </c>
+      <c r="F349">
+        <v>49</v>
+      </c>
+      <c r="G349">
+        <v>2</v>
+      </c>
+      <c r="H349">
+        <v>0</v>
+      </c>
+      <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="J349">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10">
+      <c r="A350" t="s">
+        <v>23</v>
+      </c>
+      <c r="B350" t="s">
+        <v>24</v>
+      </c>
+      <c r="C350" t="s">
+        <v>31</v>
+      </c>
+      <c r="D350">
+        <v>6435172</v>
+      </c>
+      <c r="E350" t="s">
+        <v>56</v>
+      </c>
+      <c r="F350">
+        <v>17</v>
+      </c>
+      <c r="G350">
+        <v>4</v>
+      </c>
+      <c r="H350">
+        <v>0</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10">
+      <c r="A351" t="s">
+        <v>23</v>
+      </c>
+      <c r="B351" t="s">
+        <v>24</v>
+      </c>
+      <c r="C351" t="s">
+        <v>32</v>
+      </c>
+      <c r="D351">
+        <v>7077736</v>
+      </c>
+      <c r="E351" t="s">
+        <v>57</v>
+      </c>
+      <c r="F351">
+        <v>8</v>
+      </c>
+      <c r="G351">
+        <v>0</v>
+      </c>
+      <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>0</v>
+      </c>
+      <c r="J351">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="59">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -545,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J351"/>
+  <dimension ref="A1:J376"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -585,16 +588,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -617,16 +620,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -649,16 +652,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -681,16 +684,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -713,16 +716,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -745,16 +748,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -777,16 +780,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -809,16 +812,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -841,16 +844,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -873,16 +876,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -905,16 +908,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -937,16 +940,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -969,16 +972,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1001,16 +1004,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1033,16 +1036,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1065,16 +1068,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1097,16 +1100,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1129,16 +1132,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1161,16 +1164,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1193,16 +1196,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1225,16 +1228,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1257,16 +1260,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1289,16 +1292,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1321,16 +1324,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1353,16 +1356,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1385,16 +1388,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1417,16 +1420,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1449,16 +1452,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1481,16 +1484,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1513,16 +1516,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1545,16 +1548,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1577,16 +1580,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1609,16 +1612,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1641,16 +1644,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1673,16 +1676,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1705,16 +1708,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1737,16 +1740,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1769,16 +1772,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1801,16 +1804,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1833,16 +1836,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1865,16 +1868,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1897,16 +1900,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1929,16 +1932,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1961,16 +1964,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1993,16 +1996,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2025,16 +2028,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2057,16 +2060,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2089,16 +2092,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2121,16 +2124,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2153,16 +2156,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2185,16 +2188,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2217,16 +2220,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2249,16 +2252,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2281,16 +2284,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2313,16 +2316,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2345,16 +2348,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2377,16 +2380,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2409,16 +2412,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2441,16 +2444,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2473,16 +2476,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2505,16 +2508,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2537,16 +2540,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2569,16 +2572,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2601,16 +2604,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2633,16 +2636,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2665,16 +2668,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2697,16 +2700,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2729,16 +2732,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2761,16 +2764,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2793,16 +2796,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2825,16 +2828,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2857,16 +2860,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2889,16 +2892,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2921,16 +2924,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2953,16 +2956,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2985,16 +2988,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3017,16 +3020,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3049,16 +3052,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3081,16 +3084,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3113,16 +3116,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3145,16 +3148,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3177,16 +3180,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3209,16 +3212,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3241,16 +3244,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3273,16 +3276,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3305,16 +3308,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3337,16 +3340,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3369,16 +3372,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3401,16 +3404,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3433,16 +3436,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3465,16 +3468,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3497,16 +3500,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3529,16 +3532,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3561,16 +3564,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3593,16 +3596,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3625,16 +3628,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3657,16 +3660,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3689,16 +3692,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3721,16 +3724,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3753,16 +3756,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3785,16 +3788,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3817,16 +3820,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3849,16 +3852,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3881,16 +3884,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3913,16 +3916,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3945,16 +3948,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3977,16 +3980,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4009,16 +4012,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4041,16 +4044,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4073,16 +4076,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4105,16 +4108,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4137,16 +4140,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4169,16 +4172,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4201,16 +4204,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C115" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4233,16 +4236,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4265,16 +4268,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4297,16 +4300,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4329,16 +4332,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4361,16 +4364,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4393,16 +4396,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4425,16 +4428,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4457,16 +4460,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4489,16 +4492,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4521,16 +4524,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4553,16 +4556,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4585,16 +4588,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4617,16 +4620,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4649,16 +4652,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4681,16 +4684,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4713,16 +4716,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4745,16 +4748,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4777,16 +4780,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4809,16 +4812,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4841,16 +4844,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4873,16 +4876,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4905,16 +4908,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4937,16 +4940,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4969,16 +4972,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -5001,16 +5004,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5033,16 +5036,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C141" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5065,16 +5068,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5097,16 +5100,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5129,16 +5132,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5161,16 +5164,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5193,16 +5196,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5225,16 +5228,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5257,16 +5260,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5289,16 +5292,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5321,16 +5324,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5353,16 +5356,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5385,16 +5388,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5417,16 +5420,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5449,16 +5452,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5481,16 +5484,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5513,16 +5516,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5545,16 +5548,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5577,16 +5580,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5609,16 +5612,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5641,16 +5644,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5673,16 +5676,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5705,16 +5708,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5737,16 +5740,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C163" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5769,16 +5772,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C164" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5801,16 +5804,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C165" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5833,16 +5836,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C166" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5865,16 +5868,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5897,16 +5900,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5929,16 +5932,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5961,16 +5964,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5993,16 +5996,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6025,16 +6028,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C172" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6057,16 +6060,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C173" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6089,16 +6092,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C174" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6121,16 +6124,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C175" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6153,16 +6156,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6185,16 +6188,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C177" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6217,16 +6220,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C178" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6249,16 +6252,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6281,16 +6284,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6313,16 +6316,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C181" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6345,16 +6348,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C182" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6377,16 +6380,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C183" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6409,16 +6412,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6441,16 +6444,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6473,16 +6476,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6505,16 +6508,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6537,16 +6540,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C188" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6569,16 +6572,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C189" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6601,16 +6604,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6633,16 +6636,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C191" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6665,16 +6668,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C192" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6697,16 +6700,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6729,16 +6732,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C194" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6761,16 +6764,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C195" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6793,16 +6796,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C196" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6825,16 +6828,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C197" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6857,16 +6860,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C198" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6889,16 +6892,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C199" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6921,16 +6924,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C200" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6953,16 +6956,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C201" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6985,16 +6988,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C202" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7017,16 +7020,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C203" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7049,16 +7052,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C204" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7081,16 +7084,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C205" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7113,16 +7116,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C206" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7145,16 +7148,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7177,16 +7180,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C208" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7209,16 +7212,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C209" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7241,16 +7244,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7273,16 +7276,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7305,16 +7308,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C212" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7337,16 +7340,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C213" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7369,16 +7372,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C214" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7401,16 +7404,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C215" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7433,16 +7436,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C216" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7465,16 +7468,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C217" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7497,16 +7500,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C218" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7529,16 +7532,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C219" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7561,16 +7564,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C220" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7593,16 +7596,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C221" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7625,16 +7628,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C222" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7657,16 +7660,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C223" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7689,16 +7692,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C224" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7721,16 +7724,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C225" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7753,16 +7756,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C226" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7785,16 +7788,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C227" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7817,16 +7820,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C228" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7849,16 +7852,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C229" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7881,16 +7884,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C230" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7913,16 +7916,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C231" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7945,16 +7948,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C232" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7977,16 +7980,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C233" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8009,16 +8012,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C234" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8041,16 +8044,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C235" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8073,16 +8076,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C236" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8105,16 +8108,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C237" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8137,16 +8140,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C238" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8169,16 +8172,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C239" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8201,16 +8204,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C240" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8233,16 +8236,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C241" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8265,16 +8268,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C242" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8297,16 +8300,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C243" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8329,16 +8332,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C244" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8361,16 +8364,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C245" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8393,16 +8396,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C246" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8425,16 +8428,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C247" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8457,16 +8460,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C248" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8489,16 +8492,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C249" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8521,16 +8524,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C250" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8553,16 +8556,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C251" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8585,16 +8588,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C252" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8617,16 +8620,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C253" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8649,16 +8652,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C254" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8681,16 +8684,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C255" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8713,16 +8716,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C256" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8745,16 +8748,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C257" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8777,16 +8780,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C258" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8809,16 +8812,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C259" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8841,16 +8844,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C260" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8873,16 +8876,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8905,16 +8908,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8937,16 +8940,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C263" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8969,16 +8972,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C264" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -9001,16 +9004,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C265" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9033,16 +9036,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C266" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9065,16 +9068,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C267" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9097,16 +9100,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C268" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9129,16 +9132,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C269" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9161,16 +9164,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C270" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9193,16 +9196,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C271" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9225,16 +9228,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C272" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9257,16 +9260,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C273" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9289,16 +9292,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C274" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9321,16 +9324,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C275" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9353,16 +9356,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C276" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9385,16 +9388,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C277" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F277">
         <v>45</v>
@@ -9417,16 +9420,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C278" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F278">
         <v>20</v>
@@ -9449,16 +9452,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C279" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F279">
         <v>38</v>
@@ -9481,16 +9484,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C280" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F280">
         <v>43</v>
@@ -9513,16 +9516,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C281" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F281">
         <v>90</v>
@@ -9545,16 +9548,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C282" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F282">
         <v>34</v>
@@ -9577,16 +9580,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C283" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F283">
         <v>103</v>
@@ -9609,16 +9612,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C284" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -9641,16 +9644,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C285" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F285">
         <v>69</v>
@@ -9673,16 +9676,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C286" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F286">
         <v>9</v>
@@ -9705,16 +9708,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C287" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F287">
         <v>16</v>
@@ -9737,16 +9740,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C288" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F288">
         <v>2</v>
@@ -9769,16 +9772,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C289" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F289">
         <v>2</v>
@@ -9801,16 +9804,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C290" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F290">
         <v>3</v>
@@ -9833,16 +9836,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C291" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F291">
         <v>51</v>
@@ -9865,16 +9868,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C292" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F292">
         <v>3</v>
@@ -9897,16 +9900,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C293" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F293">
         <v>44</v>
@@ -9929,16 +9932,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C294" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F294">
         <v>11</v>
@@ -9961,16 +9964,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C295" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F295">
         <v>20</v>
@@ -9993,16 +9996,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C296" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F296">
         <v>9</v>
@@ -10025,16 +10028,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C297" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F297">
         <v>117</v>
@@ -10057,16 +10060,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C298" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F298">
         <v>59</v>
@@ -10089,16 +10092,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C299" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F299">
         <v>40</v>
@@ -10121,16 +10124,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C300" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F300">
         <v>10</v>
@@ -10153,16 +10156,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C301" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F301">
         <v>9</v>
@@ -10185,16 +10188,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C302" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F302">
         <v>44</v>
@@ -10217,16 +10220,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C303" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F303">
         <v>20</v>
@@ -10249,16 +10252,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C304" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F304">
         <v>28</v>
@@ -10281,16 +10284,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C305" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F305">
         <v>24</v>
@@ -10313,16 +10316,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F306">
         <v>83</v>
@@ -10345,16 +10348,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C307" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F307">
         <v>43</v>
@@ -10377,16 +10380,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C308" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F308">
         <v>89</v>
@@ -10409,16 +10412,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C309" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F309">
         <v>13</v>
@@ -10441,16 +10444,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C310" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F310">
         <v>43</v>
@@ -10473,16 +10476,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C311" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F311">
         <v>10</v>
@@ -10505,16 +10508,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C312" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F312">
         <v>7</v>
@@ -10537,16 +10540,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C313" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F313">
         <v>3</v>
@@ -10569,16 +10572,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C314" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -10601,16 +10604,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C315" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -10633,16 +10636,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C316" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F316">
         <v>62</v>
@@ -10665,16 +10668,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C317" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F317">
         <v>3</v>
@@ -10697,16 +10700,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C318" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F318">
         <v>40</v>
@@ -10729,16 +10732,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C319" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F319">
         <v>8</v>
@@ -10761,16 +10764,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C320" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F320">
         <v>14</v>
@@ -10793,16 +10796,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C321" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -10825,16 +10828,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C322" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F322">
         <v>132</v>
@@ -10857,16 +10860,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C323" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F323">
         <v>43</v>
@@ -10889,16 +10892,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C324" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F324">
         <v>48</v>
@@ -10921,16 +10924,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C325" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F325">
         <v>17</v>
@@ -10953,16 +10956,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C326" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F326">
         <v>8</v>
@@ -10985,16 +10988,16 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C327" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D327">
         <v>7381125</v>
       </c>
       <c r="E327" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F327">
         <v>56</v>
@@ -11017,16 +11020,16 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C328" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D328">
         <v>2207663</v>
       </c>
       <c r="E328" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F328">
         <v>26</v>
@@ -11049,16 +11052,16 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C329" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D329">
         <v>7397528</v>
       </c>
       <c r="E329" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F329">
         <v>40</v>
@@ -11081,16 +11084,16 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C330" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D330">
         <v>5931712</v>
       </c>
       <c r="E330" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F330">
         <v>34</v>
@@ -11113,16 +11116,16 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C331" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D331">
         <v>7325488</v>
       </c>
       <c r="E331" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F331">
         <v>99</v>
@@ -11145,16 +11148,16 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C332" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D332">
         <v>3368175</v>
       </c>
       <c r="E332" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F332">
         <v>51</v>
@@ -11177,16 +11180,16 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C333" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D333">
         <v>3864716</v>
       </c>
       <c r="E333" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F333">
         <v>104</v>
@@ -11209,16 +11212,16 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C334" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D334">
         <v>3367403</v>
       </c>
       <c r="E334" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F334">
         <v>14</v>
@@ -11241,16 +11244,16 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D335">
         <v>7381124</v>
       </c>
       <c r="E335" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F335">
         <v>49</v>
@@ -11273,16 +11276,16 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C336" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D336">
         <v>7079978</v>
       </c>
       <c r="E336" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F336">
         <v>20</v>
@@ -11305,16 +11308,16 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C337" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D337">
         <v>3367739</v>
       </c>
       <c r="E337" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F337">
         <v>8</v>
@@ -11337,16 +11340,16 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C338" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D338">
         <v>7072286</v>
       </c>
       <c r="E338" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F338">
         <v>3</v>
@@ -11369,16 +11372,16 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C339" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D339">
         <v>3367743</v>
       </c>
       <c r="E339" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F339">
         <v>8</v>
@@ -11401,16 +11404,16 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C340" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D340">
         <v>4214024</v>
       </c>
       <c r="E340" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F340">
         <v>8</v>
@@ -11433,16 +11436,16 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C341" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D341">
         <v>7357843</v>
       </c>
       <c r="E341" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F341">
         <v>68</v>
@@ -11465,16 +11468,16 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C342" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D342">
         <v>7077448</v>
       </c>
       <c r="E342" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F342">
         <v>3</v>
@@ -11497,16 +11500,16 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C343" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D343">
         <v>2278099</v>
       </c>
       <c r="E343" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F343">
         <v>48</v>
@@ -11529,16 +11532,16 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C344" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D344">
         <v>7077738</v>
       </c>
       <c r="E344" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F344">
         <v>8</v>
@@ -11561,16 +11564,16 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C345" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D345">
         <v>4493936</v>
       </c>
       <c r="E345" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F345">
         <v>14</v>
@@ -11593,16 +11596,16 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C346" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D346">
         <v>5284531</v>
       </c>
       <c r="E346" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F346">
         <v>7</v>
@@ -11625,16 +11628,16 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C347" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D347">
         <v>5954007</v>
       </c>
       <c r="E347" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F347">
         <v>123</v>
@@ -11657,16 +11660,16 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C348" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D348">
         <v>7081903</v>
       </c>
       <c r="E348" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F348">
         <v>50</v>
@@ -11689,16 +11692,16 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C349" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D349">
         <v>9366541</v>
       </c>
       <c r="E349" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F349">
         <v>49</v>
@@ -11721,16 +11724,16 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C350" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D350">
         <v>6435172</v>
       </c>
       <c r="E350" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F350">
         <v>17</v>
@@ -11753,16 +11756,16 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C351" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D351">
         <v>7077736</v>
       </c>
       <c r="E351" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F351">
         <v>8</v>
@@ -11778,6 +11781,806 @@
       </c>
       <c r="J351">
         <v>8</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="A352" t="s">
+        <v>24</v>
+      </c>
+      <c r="B352" t="s">
+        <v>25</v>
+      </c>
+      <c r="C352" t="s">
+        <v>25</v>
+      </c>
+      <c r="D352">
+        <v>7381125</v>
+      </c>
+      <c r="E352" t="s">
+        <v>34</v>
+      </c>
+      <c r="F352">
+        <v>33</v>
+      </c>
+      <c r="G352">
+        <v>20</v>
+      </c>
+      <c r="H352">
+        <v>8</v>
+      </c>
+      <c r="I352">
+        <v>25</v>
+      </c>
+      <c r="J352">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10">
+      <c r="A353" t="s">
+        <v>24</v>
+      </c>
+      <c r="B353" t="s">
+        <v>25</v>
+      </c>
+      <c r="C353" t="s">
+        <v>25</v>
+      </c>
+      <c r="D353">
+        <v>2207663</v>
+      </c>
+      <c r="E353" t="s">
+        <v>35</v>
+      </c>
+      <c r="F353">
+        <v>21</v>
+      </c>
+      <c r="G353">
+        <v>9</v>
+      </c>
+      <c r="H353">
+        <v>3</v>
+      </c>
+      <c r="I353">
+        <v>17</v>
+      </c>
+      <c r="J353">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10">
+      <c r="A354" t="s">
+        <v>24</v>
+      </c>
+      <c r="B354" t="s">
+        <v>25</v>
+      </c>
+      <c r="C354" t="s">
+        <v>25</v>
+      </c>
+      <c r="D354">
+        <v>7397528</v>
+      </c>
+      <c r="E354" t="s">
+        <v>36</v>
+      </c>
+      <c r="F354">
+        <v>27</v>
+      </c>
+      <c r="G354">
+        <v>18</v>
+      </c>
+      <c r="H354">
+        <v>7</v>
+      </c>
+      <c r="I354">
+        <v>32</v>
+      </c>
+      <c r="J354">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="A355" t="s">
+        <v>24</v>
+      </c>
+      <c r="B355" t="s">
+        <v>25</v>
+      </c>
+      <c r="C355" t="s">
+        <v>25</v>
+      </c>
+      <c r="D355">
+        <v>5931712</v>
+      </c>
+      <c r="E355" t="s">
+        <v>37</v>
+      </c>
+      <c r="F355">
+        <v>23</v>
+      </c>
+      <c r="G355">
+        <v>20</v>
+      </c>
+      <c r="H355">
+        <v>7</v>
+      </c>
+      <c r="I355">
+        <v>20</v>
+      </c>
+      <c r="J355">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="A356" t="s">
+        <v>24</v>
+      </c>
+      <c r="B356" t="s">
+        <v>25</v>
+      </c>
+      <c r="C356" t="s">
+        <v>25</v>
+      </c>
+      <c r="D356">
+        <v>7325488</v>
+      </c>
+      <c r="E356" t="s">
+        <v>38</v>
+      </c>
+      <c r="F356">
+        <v>69</v>
+      </c>
+      <c r="G356">
+        <v>37</v>
+      </c>
+      <c r="H356">
+        <v>14</v>
+      </c>
+      <c r="I356">
+        <v>36</v>
+      </c>
+      <c r="J356">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="A357" t="s">
+        <v>24</v>
+      </c>
+      <c r="B357" t="s">
+        <v>25</v>
+      </c>
+      <c r="C357" t="s">
+        <v>25</v>
+      </c>
+      <c r="D357">
+        <v>3368175</v>
+      </c>
+      <c r="E357" t="s">
+        <v>39</v>
+      </c>
+      <c r="F357">
+        <v>21</v>
+      </c>
+      <c r="G357">
+        <v>34</v>
+      </c>
+      <c r="H357">
+        <v>13</v>
+      </c>
+      <c r="I357">
+        <v>39</v>
+      </c>
+      <c r="J357">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="A358" t="s">
+        <v>24</v>
+      </c>
+      <c r="B358" t="s">
+        <v>25</v>
+      </c>
+      <c r="C358" t="s">
+        <v>25</v>
+      </c>
+      <c r="D358">
+        <v>3864716</v>
+      </c>
+      <c r="E358" t="s">
+        <v>40</v>
+      </c>
+      <c r="F358">
+        <v>72</v>
+      </c>
+      <c r="G358">
+        <v>37</v>
+      </c>
+      <c r="H358">
+        <v>7</v>
+      </c>
+      <c r="I358">
+        <v>41</v>
+      </c>
+      <c r="J358">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="A359" t="s">
+        <v>24</v>
+      </c>
+      <c r="B359" t="s">
+        <v>25</v>
+      </c>
+      <c r="C359" t="s">
+        <v>25</v>
+      </c>
+      <c r="D359">
+        <v>3367403</v>
+      </c>
+      <c r="E359" t="s">
+        <v>41</v>
+      </c>
+      <c r="F359">
+        <v>6</v>
+      </c>
+      <c r="G359">
+        <v>6</v>
+      </c>
+      <c r="H359">
+        <v>2</v>
+      </c>
+      <c r="I359">
+        <v>12</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="A360" t="s">
+        <v>24</v>
+      </c>
+      <c r="B360" t="s">
+        <v>25</v>
+      </c>
+      <c r="C360" t="s">
+        <v>25</v>
+      </c>
+      <c r="D360">
+        <v>7381124</v>
+      </c>
+      <c r="E360" t="s">
+        <v>42</v>
+      </c>
+      <c r="F360">
+        <v>28</v>
+      </c>
+      <c r="G360">
+        <v>28</v>
+      </c>
+      <c r="H360">
+        <v>6</v>
+      </c>
+      <c r="I360">
+        <v>22</v>
+      </c>
+      <c r="J360">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="A361" t="s">
+        <v>24</v>
+      </c>
+      <c r="B361" t="s">
+        <v>25</v>
+      </c>
+      <c r="C361" t="s">
+        <v>26</v>
+      </c>
+      <c r="D361">
+        <v>7079978</v>
+      </c>
+      <c r="E361" t="s">
+        <v>43</v>
+      </c>
+      <c r="F361">
+        <v>10</v>
+      </c>
+      <c r="G361">
+        <v>5</v>
+      </c>
+      <c r="H361">
+        <v>1</v>
+      </c>
+      <c r="I361">
+        <v>16</v>
+      </c>
+      <c r="J361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="A362" t="s">
+        <v>24</v>
+      </c>
+      <c r="B362" t="s">
+        <v>25</v>
+      </c>
+      <c r="C362" t="s">
+        <v>26</v>
+      </c>
+      <c r="D362">
+        <v>3367739</v>
+      </c>
+      <c r="E362" t="s">
+        <v>44</v>
+      </c>
+      <c r="F362">
+        <v>3</v>
+      </c>
+      <c r="G362">
+        <v>2</v>
+      </c>
+      <c r="H362">
+        <v>2</v>
+      </c>
+      <c r="I362">
+        <v>8</v>
+      </c>
+      <c r="J362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="A363" t="s">
+        <v>24</v>
+      </c>
+      <c r="B363" t="s">
+        <v>25</v>
+      </c>
+      <c r="C363" t="s">
+        <v>27</v>
+      </c>
+      <c r="D363">
+        <v>7072286</v>
+      </c>
+      <c r="E363" t="s">
+        <v>45</v>
+      </c>
+      <c r="F363">
+        <v>3</v>
+      </c>
+      <c r="G363">
+        <v>3</v>
+      </c>
+      <c r="H363">
+        <v>1</v>
+      </c>
+      <c r="I363">
+        <v>2</v>
+      </c>
+      <c r="J363">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10">
+      <c r="A364" t="s">
+        <v>24</v>
+      </c>
+      <c r="B364" t="s">
+        <v>25</v>
+      </c>
+      <c r="C364" t="s">
+        <v>28</v>
+      </c>
+      <c r="D364">
+        <v>3367743</v>
+      </c>
+      <c r="E364" t="s">
+        <v>46</v>
+      </c>
+      <c r="F364">
+        <v>6</v>
+      </c>
+      <c r="G364">
+        <v>0</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>2</v>
+      </c>
+      <c r="J364">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="A365" t="s">
+        <v>24</v>
+      </c>
+      <c r="B365" t="s">
+        <v>25</v>
+      </c>
+      <c r="C365" t="s">
+        <v>27</v>
+      </c>
+      <c r="D365">
+        <v>4214024</v>
+      </c>
+      <c r="E365" t="s">
+        <v>47</v>
+      </c>
+      <c r="F365">
+        <v>4</v>
+      </c>
+      <c r="G365">
+        <v>5</v>
+      </c>
+      <c r="H365">
+        <v>3</v>
+      </c>
+      <c r="I365">
+        <v>3</v>
+      </c>
+      <c r="J365">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="A366" t="s">
+        <v>24</v>
+      </c>
+      <c r="B366" t="s">
+        <v>25</v>
+      </c>
+      <c r="C366" t="s">
+        <v>28</v>
+      </c>
+      <c r="D366">
+        <v>7357843</v>
+      </c>
+      <c r="E366" t="s">
+        <v>48</v>
+      </c>
+      <c r="F366">
+        <v>50</v>
+      </c>
+      <c r="G366">
+        <v>3</v>
+      </c>
+      <c r="H366">
+        <v>9</v>
+      </c>
+      <c r="I366">
+        <v>13</v>
+      </c>
+      <c r="J366">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="A367" t="s">
+        <v>24</v>
+      </c>
+      <c r="B367" t="s">
+        <v>25</v>
+      </c>
+      <c r="C367" t="s">
+        <v>28</v>
+      </c>
+      <c r="D367">
+        <v>7077448</v>
+      </c>
+      <c r="E367" t="s">
+        <v>49</v>
+      </c>
+      <c r="F367">
+        <v>2</v>
+      </c>
+      <c r="G367">
+        <v>5</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="A368" t="s">
+        <v>24</v>
+      </c>
+      <c r="B368" t="s">
+        <v>25</v>
+      </c>
+      <c r="C368" t="s">
+        <v>29</v>
+      </c>
+      <c r="D368">
+        <v>2278099</v>
+      </c>
+      <c r="E368" t="s">
+        <v>50</v>
+      </c>
+      <c r="F368">
+        <v>26</v>
+      </c>
+      <c r="G368">
+        <v>48</v>
+      </c>
+      <c r="H368">
+        <v>7</v>
+      </c>
+      <c r="I368">
+        <v>33</v>
+      </c>
+      <c r="J368">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="A369" t="s">
+        <v>24</v>
+      </c>
+      <c r="B369" t="s">
+        <v>25</v>
+      </c>
+      <c r="C369" t="s">
+        <v>29</v>
+      </c>
+      <c r="D369">
+        <v>7077738</v>
+      </c>
+      <c r="E369" t="s">
+        <v>51</v>
+      </c>
+      <c r="F369">
+        <v>6</v>
+      </c>
+      <c r="G369">
+        <v>4</v>
+      </c>
+      <c r="H369">
+        <v>1</v>
+      </c>
+      <c r="I369">
+        <v>2</v>
+      </c>
+      <c r="J369">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="A370" t="s">
+        <v>24</v>
+      </c>
+      <c r="B370" t="s">
+        <v>25</v>
+      </c>
+      <c r="C370" t="s">
+        <v>29</v>
+      </c>
+      <c r="D370">
+        <v>4493936</v>
+      </c>
+      <c r="E370" t="s">
+        <v>52</v>
+      </c>
+      <c r="F370">
+        <v>10</v>
+      </c>
+      <c r="G370">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>6</v>
+      </c>
+      <c r="J370">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="A371" t="s">
+        <v>24</v>
+      </c>
+      <c r="B371" t="s">
+        <v>25</v>
+      </c>
+      <c r="C371" t="s">
+        <v>29</v>
+      </c>
+      <c r="D371">
+        <v>5284531</v>
+      </c>
+      <c r="E371" t="s">
+        <v>53</v>
+      </c>
+      <c r="F371">
+        <v>3</v>
+      </c>
+      <c r="G371">
+        <v>2</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+      <c r="I371">
+        <v>4</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="A372" t="s">
+        <v>24</v>
+      </c>
+      <c r="B372" t="s">
+        <v>25</v>
+      </c>
+      <c r="C372" t="s">
+        <v>30</v>
+      </c>
+      <c r="D372">
+        <v>5954007</v>
+      </c>
+      <c r="E372" t="s">
+        <v>54</v>
+      </c>
+      <c r="F372">
+        <v>91</v>
+      </c>
+      <c r="G372">
+        <v>29</v>
+      </c>
+      <c r="H372">
+        <v>19</v>
+      </c>
+      <c r="I372">
+        <v>48</v>
+      </c>
+      <c r="J372">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="A373" t="s">
+        <v>24</v>
+      </c>
+      <c r="B373" t="s">
+        <v>25</v>
+      </c>
+      <c r="C373" t="s">
+        <v>30</v>
+      </c>
+      <c r="D373">
+        <v>7081903</v>
+      </c>
+      <c r="E373" t="s">
+        <v>55</v>
+      </c>
+      <c r="F373">
+        <v>35</v>
+      </c>
+      <c r="G373">
+        <v>19</v>
+      </c>
+      <c r="H373">
+        <v>10</v>
+      </c>
+      <c r="I373">
+        <v>20</v>
+      </c>
+      <c r="J373">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374" t="s">
+        <v>24</v>
+      </c>
+      <c r="B374" t="s">
+        <v>25</v>
+      </c>
+      <c r="C374" t="s">
+        <v>31</v>
+      </c>
+      <c r="D374">
+        <v>9366541</v>
+      </c>
+      <c r="E374" t="s">
+        <v>56</v>
+      </c>
+      <c r="F374">
+        <v>33</v>
+      </c>
+      <c r="G374">
+        <v>18</v>
+      </c>
+      <c r="H374">
+        <v>7</v>
+      </c>
+      <c r="I374">
+        <v>19</v>
+      </c>
+      <c r="J374">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="A375" t="s">
+        <v>24</v>
+      </c>
+      <c r="B375" t="s">
+        <v>25</v>
+      </c>
+      <c r="C375" t="s">
+        <v>32</v>
+      </c>
+      <c r="D375">
+        <v>6435172</v>
+      </c>
+      <c r="E375" t="s">
+        <v>57</v>
+      </c>
+      <c r="F375">
+        <v>10</v>
+      </c>
+      <c r="G375">
+        <v>3</v>
+      </c>
+      <c r="H375">
+        <v>6</v>
+      </c>
+      <c r="I375">
+        <v>7</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376" t="s">
+        <v>24</v>
+      </c>
+      <c r="B376" t="s">
+        <v>25</v>
+      </c>
+      <c r="C376" t="s">
+        <v>33</v>
+      </c>
+      <c r="D376">
+        <v>7077736</v>
+      </c>
+      <c r="E376" t="s">
+        <v>58</v>
+      </c>
+      <c r="F376">
+        <v>3</v>
+      </c>
+      <c r="G376">
+        <v>4</v>
+      </c>
+      <c r="H376">
+        <v>2</v>
+      </c>
+      <c r="I376">
+        <v>4</v>
+      </c>
+      <c r="J376">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="60">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -548,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J376"/>
+  <dimension ref="A1:J401"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -588,16 +591,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -620,16 +623,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -652,16 +655,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -684,16 +687,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -716,16 +719,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -748,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -780,16 +783,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -812,16 +815,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -844,16 +847,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -876,16 +879,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -908,16 +911,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -940,16 +943,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -972,16 +975,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1004,16 +1007,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1036,16 +1039,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1068,16 +1071,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1100,16 +1103,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1132,16 +1135,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1164,16 +1167,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1196,16 +1199,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1228,16 +1231,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1260,16 +1263,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1292,16 +1295,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1324,16 +1327,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1356,16 +1359,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1388,16 +1391,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1420,16 +1423,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1452,16 +1455,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1484,16 +1487,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1516,16 +1519,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1548,16 +1551,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1580,16 +1583,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1612,16 +1615,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1644,16 +1647,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1676,16 +1679,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1708,16 +1711,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1740,16 +1743,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1772,16 +1775,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1804,16 +1807,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1836,16 +1839,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1868,16 +1871,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1900,16 +1903,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1932,16 +1935,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1964,16 +1967,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1996,16 +1999,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2028,16 +2031,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2060,16 +2063,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2092,16 +2095,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2124,16 +2127,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2156,16 +2159,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2188,16 +2191,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2220,16 +2223,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2252,16 +2255,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2284,16 +2287,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2316,16 +2319,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2348,16 +2351,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2380,16 +2383,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2412,16 +2415,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2444,16 +2447,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2476,16 +2479,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2508,16 +2511,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2540,16 +2543,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2572,16 +2575,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2604,16 +2607,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2636,16 +2639,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2668,16 +2671,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2700,16 +2703,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2732,16 +2735,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2764,16 +2767,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2796,16 +2799,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2828,16 +2831,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2860,16 +2863,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2892,16 +2895,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2924,16 +2927,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2956,16 +2959,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2988,16 +2991,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3020,16 +3023,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3052,16 +3055,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3084,16 +3087,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3116,16 +3119,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3148,16 +3151,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3180,16 +3183,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3212,16 +3215,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3244,16 +3247,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3276,16 +3279,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3308,16 +3311,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3340,16 +3343,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3372,16 +3375,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3404,16 +3407,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3436,16 +3439,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3468,16 +3471,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3500,16 +3503,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3532,16 +3535,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3564,16 +3567,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3596,16 +3599,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3628,16 +3631,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3660,16 +3663,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3692,16 +3695,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3724,16 +3727,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3756,16 +3759,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3788,16 +3791,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3820,16 +3823,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3852,16 +3855,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3884,16 +3887,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3916,16 +3919,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3948,16 +3951,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3980,16 +3983,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4012,16 +4015,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4044,16 +4047,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4076,16 +4079,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4108,16 +4111,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4140,16 +4143,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4172,16 +4175,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4204,16 +4207,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4236,16 +4239,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4268,16 +4271,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C117" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4300,16 +4303,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4332,16 +4335,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4364,16 +4367,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4396,16 +4399,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4428,16 +4431,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4460,16 +4463,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4492,16 +4495,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4524,16 +4527,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4556,16 +4559,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4588,16 +4591,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4620,16 +4623,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4652,16 +4655,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C129" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4684,16 +4687,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4716,16 +4719,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4748,16 +4751,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4780,16 +4783,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4812,16 +4815,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4844,16 +4847,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4876,16 +4879,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C136" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4908,16 +4911,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4940,16 +4943,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C138" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4972,16 +4975,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -5004,16 +5007,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C140" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5036,16 +5039,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5068,16 +5071,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5100,16 +5103,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5132,16 +5135,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5164,16 +5167,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5196,16 +5199,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5228,16 +5231,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C147" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5260,16 +5263,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C148" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5292,16 +5295,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C149" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5324,16 +5327,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C150" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5356,16 +5359,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C151" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5388,16 +5391,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C152" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5420,16 +5423,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C153" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5452,16 +5455,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5484,16 +5487,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C155" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5516,16 +5519,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C156" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5548,16 +5551,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5580,16 +5583,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C158" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5612,16 +5615,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5644,16 +5647,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C160" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5676,16 +5679,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C161" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5708,16 +5711,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C162" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5740,16 +5743,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5772,16 +5775,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C164" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5804,16 +5807,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C165" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5836,16 +5839,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C166" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5868,16 +5871,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5900,16 +5903,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C168" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5932,16 +5935,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C169" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5964,16 +5967,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C170" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5996,16 +5999,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C171" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6028,16 +6031,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C172" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6060,16 +6063,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C173" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6092,16 +6095,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C174" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6124,16 +6127,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C175" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6156,16 +6159,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C176" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6188,16 +6191,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C177" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6220,16 +6223,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C178" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6252,16 +6255,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C179" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6284,16 +6287,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6316,16 +6319,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6348,16 +6351,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6380,16 +6383,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C183" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6412,16 +6415,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C184" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6444,16 +6447,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C185" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6476,16 +6479,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C186" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6508,16 +6511,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C187" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6540,16 +6543,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C188" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6572,16 +6575,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C189" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6604,16 +6607,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C190" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6636,16 +6639,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6668,16 +6671,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C192" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6700,16 +6703,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6732,16 +6735,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C194" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6764,16 +6767,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C195" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6796,16 +6799,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C196" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6828,16 +6831,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C197" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6860,16 +6863,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C198" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6892,16 +6895,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C199" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6924,16 +6927,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C200" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6956,16 +6959,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C201" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6988,16 +6991,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C202" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7020,16 +7023,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C203" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7052,16 +7055,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C204" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7084,16 +7087,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C205" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7116,16 +7119,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C206" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7148,16 +7151,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C207" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7180,16 +7183,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7212,16 +7215,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C209" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7244,16 +7247,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C210" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7276,16 +7279,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C211" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7308,16 +7311,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C212" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7340,16 +7343,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C213" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7372,16 +7375,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C214" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7404,16 +7407,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C215" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7436,16 +7439,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C216" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7468,16 +7471,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C217" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7500,16 +7503,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C218" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7532,16 +7535,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C219" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7564,16 +7567,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C220" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7596,16 +7599,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C221" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7628,16 +7631,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C222" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7660,16 +7663,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C223" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7692,16 +7695,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C224" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7724,16 +7727,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C225" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7756,16 +7759,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C226" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7788,16 +7791,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C227" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7820,16 +7823,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C228" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7852,16 +7855,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C229" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7884,16 +7887,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C230" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7916,16 +7919,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C231" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7948,16 +7951,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C232" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7980,16 +7983,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C233" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8012,16 +8015,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C234" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8044,16 +8047,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8076,16 +8079,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C236" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8108,16 +8111,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C237" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8140,16 +8143,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C238" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8172,16 +8175,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C239" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8204,16 +8207,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C240" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8236,16 +8239,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C241" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8268,16 +8271,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8300,16 +8303,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8332,16 +8335,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C244" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8364,16 +8367,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C245" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8396,16 +8399,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C246" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8428,16 +8431,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C247" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8460,16 +8463,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C248" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8492,16 +8495,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C249" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8524,16 +8527,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C250" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8556,16 +8559,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C251" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8588,16 +8591,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C252" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8620,16 +8623,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8652,16 +8655,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C254" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8684,16 +8687,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C255" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8716,16 +8719,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C256" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8748,16 +8751,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C257" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8780,16 +8783,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C258" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8812,16 +8815,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C259" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8844,16 +8847,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C260" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8876,16 +8879,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C261" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8908,16 +8911,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C262" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8940,16 +8943,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C263" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8972,16 +8975,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C264" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -9004,16 +9007,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C265" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9036,16 +9039,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C266" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9068,16 +9071,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C267" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9100,16 +9103,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C268" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9132,16 +9135,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C269" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9164,16 +9167,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C270" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9196,16 +9199,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C271" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9228,16 +9231,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C272" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9260,16 +9263,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C273" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9292,16 +9295,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C274" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9324,16 +9327,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C275" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9356,16 +9359,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C276" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9388,16 +9391,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C277" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F277">
         <v>45</v>
@@ -9420,16 +9423,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C278" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F278">
         <v>20</v>
@@ -9452,16 +9455,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C279" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F279">
         <v>38</v>
@@ -9484,16 +9487,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F280">
         <v>43</v>
@@ -9516,16 +9519,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C281" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F281">
         <v>90</v>
@@ -9548,16 +9551,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C282" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F282">
         <v>34</v>
@@ -9580,16 +9583,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C283" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F283">
         <v>103</v>
@@ -9612,16 +9615,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C284" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -9644,16 +9647,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C285" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F285">
         <v>69</v>
@@ -9676,16 +9679,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C286" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F286">
         <v>9</v>
@@ -9708,16 +9711,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C287" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F287">
         <v>16</v>
@@ -9740,16 +9743,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C288" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F288">
         <v>2</v>
@@ -9772,16 +9775,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C289" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F289">
         <v>2</v>
@@ -9804,16 +9807,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C290" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F290">
         <v>3</v>
@@ -9836,16 +9839,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C291" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F291">
         <v>51</v>
@@ -9868,16 +9871,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C292" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F292">
         <v>3</v>
@@ -9900,16 +9903,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C293" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F293">
         <v>44</v>
@@ -9932,16 +9935,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C294" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F294">
         <v>11</v>
@@ -9964,16 +9967,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C295" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F295">
         <v>20</v>
@@ -9996,16 +9999,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C296" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F296">
         <v>9</v>
@@ -10028,16 +10031,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C297" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F297">
         <v>117</v>
@@ -10060,16 +10063,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C298" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F298">
         <v>59</v>
@@ -10092,16 +10095,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C299" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F299">
         <v>40</v>
@@ -10124,16 +10127,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C300" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F300">
         <v>10</v>
@@ -10156,16 +10159,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C301" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F301">
         <v>9</v>
@@ -10188,16 +10191,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C302" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F302">
         <v>44</v>
@@ -10220,16 +10223,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C303" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F303">
         <v>20</v>
@@ -10252,16 +10255,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C304" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F304">
         <v>28</v>
@@ -10284,16 +10287,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C305" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F305">
         <v>24</v>
@@ -10316,16 +10319,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C306" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F306">
         <v>83</v>
@@ -10348,16 +10351,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C307" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F307">
         <v>43</v>
@@ -10380,16 +10383,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C308" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F308">
         <v>89</v>
@@ -10412,16 +10415,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C309" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F309">
         <v>13</v>
@@ -10444,16 +10447,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C310" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F310">
         <v>43</v>
@@ -10476,16 +10479,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C311" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F311">
         <v>10</v>
@@ -10508,16 +10511,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C312" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F312">
         <v>7</v>
@@ -10540,16 +10543,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C313" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F313">
         <v>3</v>
@@ -10572,16 +10575,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C314" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -10604,16 +10607,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C315" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -10636,16 +10639,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C316" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F316">
         <v>62</v>
@@ -10668,16 +10671,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C317" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F317">
         <v>3</v>
@@ -10700,16 +10703,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C318" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F318">
         <v>40</v>
@@ -10732,16 +10735,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C319" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F319">
         <v>8</v>
@@ -10764,16 +10767,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C320" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F320">
         <v>14</v>
@@ -10796,16 +10799,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C321" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -10828,16 +10831,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C322" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F322">
         <v>132</v>
@@ -10860,16 +10863,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C323" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F323">
         <v>43</v>
@@ -10892,16 +10895,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C324" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F324">
         <v>48</v>
@@ -10924,16 +10927,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C325" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F325">
         <v>17</v>
@@ -10956,16 +10959,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C326" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F326">
         <v>8</v>
@@ -10988,16 +10991,16 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C327" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D327">
         <v>7381125</v>
       </c>
       <c r="E327" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F327">
         <v>56</v>
@@ -11020,16 +11023,16 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C328" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D328">
         <v>2207663</v>
       </c>
       <c r="E328" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F328">
         <v>26</v>
@@ -11052,16 +11055,16 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C329" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D329">
         <v>7397528</v>
       </c>
       <c r="E329" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F329">
         <v>40</v>
@@ -11084,16 +11087,16 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C330" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D330">
         <v>5931712</v>
       </c>
       <c r="E330" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F330">
         <v>34</v>
@@ -11116,16 +11119,16 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C331" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D331">
         <v>7325488</v>
       </c>
       <c r="E331" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F331">
         <v>99</v>
@@ -11148,16 +11151,16 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C332" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D332">
         <v>3368175</v>
       </c>
       <c r="E332" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F332">
         <v>51</v>
@@ -11180,16 +11183,16 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C333" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D333">
         <v>3864716</v>
       </c>
       <c r="E333" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F333">
         <v>104</v>
@@ -11212,16 +11215,16 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C334" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D334">
         <v>3367403</v>
       </c>
       <c r="E334" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F334">
         <v>14</v>
@@ -11244,16 +11247,16 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C335" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D335">
         <v>7381124</v>
       </c>
       <c r="E335" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F335">
         <v>49</v>
@@ -11276,16 +11279,16 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C336" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D336">
         <v>7079978</v>
       </c>
       <c r="E336" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F336">
         <v>20</v>
@@ -11308,16 +11311,16 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C337" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D337">
         <v>3367739</v>
       </c>
       <c r="E337" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F337">
         <v>8</v>
@@ -11340,16 +11343,16 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C338" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D338">
         <v>7072286</v>
       </c>
       <c r="E338" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F338">
         <v>3</v>
@@ -11372,16 +11375,16 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C339" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D339">
         <v>3367743</v>
       </c>
       <c r="E339" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F339">
         <v>8</v>
@@ -11404,16 +11407,16 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C340" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D340">
         <v>4214024</v>
       </c>
       <c r="E340" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F340">
         <v>8</v>
@@ -11436,16 +11439,16 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C341" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D341">
         <v>7357843</v>
       </c>
       <c r="E341" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F341">
         <v>68</v>
@@ -11468,16 +11471,16 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C342" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D342">
         <v>7077448</v>
       </c>
       <c r="E342" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F342">
         <v>3</v>
@@ -11500,16 +11503,16 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C343" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D343">
         <v>2278099</v>
       </c>
       <c r="E343" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F343">
         <v>48</v>
@@ -11532,16 +11535,16 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C344" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D344">
         <v>7077738</v>
       </c>
       <c r="E344" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F344">
         <v>8</v>
@@ -11564,16 +11567,16 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C345" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D345">
         <v>4493936</v>
       </c>
       <c r="E345" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F345">
         <v>14</v>
@@ -11596,16 +11599,16 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C346" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D346">
         <v>5284531</v>
       </c>
       <c r="E346" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F346">
         <v>7</v>
@@ -11628,16 +11631,16 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C347" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D347">
         <v>5954007</v>
       </c>
       <c r="E347" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F347">
         <v>123</v>
@@ -11660,16 +11663,16 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C348" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D348">
         <v>7081903</v>
       </c>
       <c r="E348" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F348">
         <v>50</v>
@@ -11692,16 +11695,16 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C349" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D349">
         <v>9366541</v>
       </c>
       <c r="E349" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F349">
         <v>49</v>
@@ -11724,16 +11727,16 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C350" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D350">
         <v>6435172</v>
       </c>
       <c r="E350" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F350">
         <v>17</v>
@@ -11756,16 +11759,16 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C351" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D351">
         <v>7077736</v>
       </c>
       <c r="E351" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F351">
         <v>8</v>
@@ -11788,16 +11791,16 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C352" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D352">
         <v>7381125</v>
       </c>
       <c r="E352" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F352">
         <v>33</v>
@@ -11820,16 +11823,16 @@
         <v>24</v>
       </c>
       <c r="B353" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C353" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D353">
         <v>2207663</v>
       </c>
       <c r="E353" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F353">
         <v>21</v>
@@ -11852,16 +11855,16 @@
         <v>24</v>
       </c>
       <c r="B354" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C354" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D354">
         <v>7397528</v>
       </c>
       <c r="E354" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F354">
         <v>27</v>
@@ -11884,16 +11887,16 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C355" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D355">
         <v>5931712</v>
       </c>
       <c r="E355" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F355">
         <v>23</v>
@@ -11916,16 +11919,16 @@
         <v>24</v>
       </c>
       <c r="B356" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C356" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D356">
         <v>7325488</v>
       </c>
       <c r="E356" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F356">
         <v>69</v>
@@ -11948,16 +11951,16 @@
         <v>24</v>
       </c>
       <c r="B357" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C357" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D357">
         <v>3368175</v>
       </c>
       <c r="E357" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F357">
         <v>21</v>
@@ -11980,16 +11983,16 @@
         <v>24</v>
       </c>
       <c r="B358" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C358" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D358">
         <v>3864716</v>
       </c>
       <c r="E358" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F358">
         <v>72</v>
@@ -12012,16 +12015,16 @@
         <v>24</v>
       </c>
       <c r="B359" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C359" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D359">
         <v>3367403</v>
       </c>
       <c r="E359" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F359">
         <v>6</v>
@@ -12044,16 +12047,16 @@
         <v>24</v>
       </c>
       <c r="B360" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C360" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D360">
         <v>7381124</v>
       </c>
       <c r="E360" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F360">
         <v>28</v>
@@ -12076,16 +12079,16 @@
         <v>24</v>
       </c>
       <c r="B361" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C361" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D361">
         <v>7079978</v>
       </c>
       <c r="E361" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F361">
         <v>10</v>
@@ -12108,16 +12111,16 @@
         <v>24</v>
       </c>
       <c r="B362" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C362" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D362">
         <v>3367739</v>
       </c>
       <c r="E362" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F362">
         <v>3</v>
@@ -12140,16 +12143,16 @@
         <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C363" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D363">
         <v>7072286</v>
       </c>
       <c r="E363" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F363">
         <v>3</v>
@@ -12172,16 +12175,16 @@
         <v>24</v>
       </c>
       <c r="B364" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C364" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D364">
         <v>3367743</v>
       </c>
       <c r="E364" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F364">
         <v>6</v>
@@ -12204,16 +12207,16 @@
         <v>24</v>
       </c>
       <c r="B365" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C365" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D365">
         <v>4214024</v>
       </c>
       <c r="E365" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F365">
         <v>4</v>
@@ -12236,16 +12239,16 @@
         <v>24</v>
       </c>
       <c r="B366" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C366" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D366">
         <v>7357843</v>
       </c>
       <c r="E366" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F366">
         <v>50</v>
@@ -12268,16 +12271,16 @@
         <v>24</v>
       </c>
       <c r="B367" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C367" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D367">
         <v>7077448</v>
       </c>
       <c r="E367" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F367">
         <v>2</v>
@@ -12300,16 +12303,16 @@
         <v>24</v>
       </c>
       <c r="B368" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C368" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D368">
         <v>2278099</v>
       </c>
       <c r="E368" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F368">
         <v>26</v>
@@ -12332,16 +12335,16 @@
         <v>24</v>
       </c>
       <c r="B369" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C369" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D369">
         <v>7077738</v>
       </c>
       <c r="E369" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F369">
         <v>6</v>
@@ -12364,16 +12367,16 @@
         <v>24</v>
       </c>
       <c r="B370" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C370" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D370">
         <v>4493936</v>
       </c>
       <c r="E370" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F370">
         <v>10</v>
@@ -12396,16 +12399,16 @@
         <v>24</v>
       </c>
       <c r="B371" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C371" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D371">
         <v>5284531</v>
       </c>
       <c r="E371" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F371">
         <v>3</v>
@@ -12428,16 +12431,16 @@
         <v>24</v>
       </c>
       <c r="B372" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C372" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D372">
         <v>5954007</v>
       </c>
       <c r="E372" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F372">
         <v>91</v>
@@ -12460,16 +12463,16 @@
         <v>24</v>
       </c>
       <c r="B373" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C373" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D373">
         <v>7081903</v>
       </c>
       <c r="E373" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F373">
         <v>35</v>
@@ -12492,16 +12495,16 @@
         <v>24</v>
       </c>
       <c r="B374" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C374" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D374">
         <v>9366541</v>
       </c>
       <c r="E374" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F374">
         <v>33</v>
@@ -12524,16 +12527,16 @@
         <v>24</v>
       </c>
       <c r="B375" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C375" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D375">
         <v>6435172</v>
       </c>
       <c r="E375" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F375">
         <v>10</v>
@@ -12556,16 +12559,16 @@
         <v>24</v>
       </c>
       <c r="B376" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C376" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D376">
         <v>7077736</v>
       </c>
       <c r="E376" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F376">
         <v>3</v>
@@ -12581,6 +12584,806 @@
       </c>
       <c r="J376">
         <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="A377" t="s">
+        <v>25</v>
+      </c>
+      <c r="B377" t="s">
+        <v>26</v>
+      </c>
+      <c r="C377" t="s">
+        <v>26</v>
+      </c>
+      <c r="D377">
+        <v>7381125</v>
+      </c>
+      <c r="E377" t="s">
+        <v>35</v>
+      </c>
+      <c r="F377">
+        <v>32</v>
+      </c>
+      <c r="G377">
+        <v>19</v>
+      </c>
+      <c r="H377">
+        <v>7</v>
+      </c>
+      <c r="I377">
+        <v>19</v>
+      </c>
+      <c r="J377">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10">
+      <c r="A378" t="s">
+        <v>25</v>
+      </c>
+      <c r="B378" t="s">
+        <v>26</v>
+      </c>
+      <c r="C378" t="s">
+        <v>26</v>
+      </c>
+      <c r="D378">
+        <v>2207663</v>
+      </c>
+      <c r="E378" t="s">
+        <v>36</v>
+      </c>
+      <c r="F378">
+        <v>18</v>
+      </c>
+      <c r="G378">
+        <v>11</v>
+      </c>
+      <c r="H378">
+        <v>2</v>
+      </c>
+      <c r="I378">
+        <v>17</v>
+      </c>
+      <c r="J378">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="A379" t="s">
+        <v>25</v>
+      </c>
+      <c r="B379" t="s">
+        <v>26</v>
+      </c>
+      <c r="C379" t="s">
+        <v>26</v>
+      </c>
+      <c r="D379">
+        <v>7397528</v>
+      </c>
+      <c r="E379" t="s">
+        <v>37</v>
+      </c>
+      <c r="F379">
+        <v>28</v>
+      </c>
+      <c r="G379">
+        <v>28</v>
+      </c>
+      <c r="H379">
+        <v>11</v>
+      </c>
+      <c r="I379">
+        <v>22</v>
+      </c>
+      <c r="J379">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10">
+      <c r="A380" t="s">
+        <v>25</v>
+      </c>
+      <c r="B380" t="s">
+        <v>26</v>
+      </c>
+      <c r="C380" t="s">
+        <v>26</v>
+      </c>
+      <c r="D380">
+        <v>5931712</v>
+      </c>
+      <c r="E380" t="s">
+        <v>38</v>
+      </c>
+      <c r="F380">
+        <v>22</v>
+      </c>
+      <c r="G380">
+        <v>13</v>
+      </c>
+      <c r="H380">
+        <v>9</v>
+      </c>
+      <c r="I380">
+        <v>20</v>
+      </c>
+      <c r="J380">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10">
+      <c r="A381" t="s">
+        <v>25</v>
+      </c>
+      <c r="B381" t="s">
+        <v>26</v>
+      </c>
+      <c r="C381" t="s">
+        <v>26</v>
+      </c>
+      <c r="D381">
+        <v>7325488</v>
+      </c>
+      <c r="E381" t="s">
+        <v>39</v>
+      </c>
+      <c r="F381">
+        <v>62</v>
+      </c>
+      <c r="G381">
+        <v>40</v>
+      </c>
+      <c r="H381">
+        <v>11</v>
+      </c>
+      <c r="I381">
+        <v>40</v>
+      </c>
+      <c r="J381">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10">
+      <c r="A382" t="s">
+        <v>25</v>
+      </c>
+      <c r="B382" t="s">
+        <v>26</v>
+      </c>
+      <c r="C382" t="s">
+        <v>26</v>
+      </c>
+      <c r="D382">
+        <v>3368175</v>
+      </c>
+      <c r="E382" t="s">
+        <v>40</v>
+      </c>
+      <c r="F382">
+        <v>26</v>
+      </c>
+      <c r="G382">
+        <v>31</v>
+      </c>
+      <c r="H382">
+        <v>8</v>
+      </c>
+      <c r="I382">
+        <v>27</v>
+      </c>
+      <c r="J382">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10">
+      <c r="A383" t="s">
+        <v>25</v>
+      </c>
+      <c r="B383" t="s">
+        <v>26</v>
+      </c>
+      <c r="C383" t="s">
+        <v>26</v>
+      </c>
+      <c r="D383">
+        <v>3864716</v>
+      </c>
+      <c r="E383" t="s">
+        <v>41</v>
+      </c>
+      <c r="F383">
+        <v>44</v>
+      </c>
+      <c r="G383">
+        <v>29</v>
+      </c>
+      <c r="H383">
+        <v>18</v>
+      </c>
+      <c r="I383">
+        <v>53</v>
+      </c>
+      <c r="J383">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10">
+      <c r="A384" t="s">
+        <v>25</v>
+      </c>
+      <c r="B384" t="s">
+        <v>26</v>
+      </c>
+      <c r="C384" t="s">
+        <v>26</v>
+      </c>
+      <c r="D384">
+        <v>3367403</v>
+      </c>
+      <c r="E384" t="s">
+        <v>42</v>
+      </c>
+      <c r="F384">
+        <v>4</v>
+      </c>
+      <c r="G384">
+        <v>2</v>
+      </c>
+      <c r="H384">
+        <v>4</v>
+      </c>
+      <c r="I384">
+        <v>10</v>
+      </c>
+      <c r="J384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10">
+      <c r="A385" t="s">
+        <v>25</v>
+      </c>
+      <c r="B385" t="s">
+        <v>26</v>
+      </c>
+      <c r="C385" t="s">
+        <v>26</v>
+      </c>
+      <c r="D385">
+        <v>7381124</v>
+      </c>
+      <c r="E385" t="s">
+        <v>43</v>
+      </c>
+      <c r="F385">
+        <v>27</v>
+      </c>
+      <c r="G385">
+        <v>23</v>
+      </c>
+      <c r="H385">
+        <v>11</v>
+      </c>
+      <c r="I385">
+        <v>22</v>
+      </c>
+      <c r="J385">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10">
+      <c r="A386" t="s">
+        <v>25</v>
+      </c>
+      <c r="B386" t="s">
+        <v>26</v>
+      </c>
+      <c r="C386" t="s">
+        <v>27</v>
+      </c>
+      <c r="D386">
+        <v>7079978</v>
+      </c>
+      <c r="E386" t="s">
+        <v>44</v>
+      </c>
+      <c r="F386">
+        <v>7</v>
+      </c>
+      <c r="G386">
+        <v>6</v>
+      </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
+      <c r="I386">
+        <v>9</v>
+      </c>
+      <c r="J386">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10">
+      <c r="A387" t="s">
+        <v>25</v>
+      </c>
+      <c r="B387" t="s">
+        <v>26</v>
+      </c>
+      <c r="C387" t="s">
+        <v>27</v>
+      </c>
+      <c r="D387">
+        <v>3367739</v>
+      </c>
+      <c r="E387" t="s">
+        <v>45</v>
+      </c>
+      <c r="F387">
+        <v>2</v>
+      </c>
+      <c r="G387">
+        <v>0</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+      <c r="I387">
+        <v>4</v>
+      </c>
+      <c r="J387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
+      <c r="A388" t="s">
+        <v>25</v>
+      </c>
+      <c r="B388" t="s">
+        <v>26</v>
+      </c>
+      <c r="C388" t="s">
+        <v>28</v>
+      </c>
+      <c r="D388">
+        <v>7072286</v>
+      </c>
+      <c r="E388" t="s">
+        <v>46</v>
+      </c>
+      <c r="F388">
+        <v>4</v>
+      </c>
+      <c r="G388">
+        <v>0</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+      <c r="I388">
+        <v>3</v>
+      </c>
+      <c r="J388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
+      <c r="A389" t="s">
+        <v>25</v>
+      </c>
+      <c r="B389" t="s">
+        <v>26</v>
+      </c>
+      <c r="C389" t="s">
+        <v>29</v>
+      </c>
+      <c r="D389">
+        <v>3367743</v>
+      </c>
+      <c r="E389" t="s">
+        <v>47</v>
+      </c>
+      <c r="F389">
+        <v>6</v>
+      </c>
+      <c r="G389">
+        <v>0</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+      <c r="I389">
+        <v>1</v>
+      </c>
+      <c r="J389">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="A390" t="s">
+        <v>25</v>
+      </c>
+      <c r="B390" t="s">
+        <v>26</v>
+      </c>
+      <c r="C390" t="s">
+        <v>28</v>
+      </c>
+      <c r="D390">
+        <v>4214024</v>
+      </c>
+      <c r="E390" t="s">
+        <v>48</v>
+      </c>
+      <c r="F390">
+        <v>2</v>
+      </c>
+      <c r="G390">
+        <v>6</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+      <c r="I390">
+        <v>6</v>
+      </c>
+      <c r="J390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
+      <c r="A391" t="s">
+        <v>25</v>
+      </c>
+      <c r="B391" t="s">
+        <v>26</v>
+      </c>
+      <c r="C391" t="s">
+        <v>29</v>
+      </c>
+      <c r="D391">
+        <v>7357843</v>
+      </c>
+      <c r="E391" t="s">
+        <v>49</v>
+      </c>
+      <c r="F391">
+        <v>46</v>
+      </c>
+      <c r="G391">
+        <v>10</v>
+      </c>
+      <c r="H391">
+        <v>2</v>
+      </c>
+      <c r="I391">
+        <v>7</v>
+      </c>
+      <c r="J391">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
+      <c r="A392" t="s">
+        <v>25</v>
+      </c>
+      <c r="B392" t="s">
+        <v>26</v>
+      </c>
+      <c r="C392" t="s">
+        <v>29</v>
+      </c>
+      <c r="D392">
+        <v>7077448</v>
+      </c>
+      <c r="E392" t="s">
+        <v>50</v>
+      </c>
+      <c r="F392">
+        <v>4</v>
+      </c>
+      <c r="G392">
+        <v>1</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
+      <c r="I392">
+        <v>3</v>
+      </c>
+      <c r="J392">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
+      <c r="A393" t="s">
+        <v>25</v>
+      </c>
+      <c r="B393" t="s">
+        <v>26</v>
+      </c>
+      <c r="C393" t="s">
+        <v>30</v>
+      </c>
+      <c r="D393">
+        <v>2278099</v>
+      </c>
+      <c r="E393" t="s">
+        <v>51</v>
+      </c>
+      <c r="F393">
+        <v>33</v>
+      </c>
+      <c r="G393">
+        <v>29</v>
+      </c>
+      <c r="H393">
+        <v>9</v>
+      </c>
+      <c r="I393">
+        <v>39</v>
+      </c>
+      <c r="J393">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="A394" t="s">
+        <v>25</v>
+      </c>
+      <c r="B394" t="s">
+        <v>26</v>
+      </c>
+      <c r="C394" t="s">
+        <v>30</v>
+      </c>
+      <c r="D394">
+        <v>7077738</v>
+      </c>
+      <c r="E394" t="s">
+        <v>52</v>
+      </c>
+      <c r="F394">
+        <v>6</v>
+      </c>
+      <c r="G394">
+        <v>2</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+      <c r="I394">
+        <v>5</v>
+      </c>
+      <c r="J394">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="A395" t="s">
+        <v>25</v>
+      </c>
+      <c r="B395" t="s">
+        <v>26</v>
+      </c>
+      <c r="C395" t="s">
+        <v>30</v>
+      </c>
+      <c r="D395">
+        <v>4493936</v>
+      </c>
+      <c r="E395" t="s">
+        <v>53</v>
+      </c>
+      <c r="F395">
+        <v>8</v>
+      </c>
+      <c r="G395">
+        <v>5</v>
+      </c>
+      <c r="H395">
+        <v>0</v>
+      </c>
+      <c r="I395">
+        <v>3</v>
+      </c>
+      <c r="J395">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10">
+      <c r="A396" t="s">
+        <v>25</v>
+      </c>
+      <c r="B396" t="s">
+        <v>26</v>
+      </c>
+      <c r="C396" t="s">
+        <v>30</v>
+      </c>
+      <c r="D396">
+        <v>5284531</v>
+      </c>
+      <c r="E396" t="s">
+        <v>54</v>
+      </c>
+      <c r="F396">
+        <v>4</v>
+      </c>
+      <c r="G396">
+        <v>4</v>
+      </c>
+      <c r="H396">
+        <v>0</v>
+      </c>
+      <c r="I396">
+        <v>1</v>
+      </c>
+      <c r="J396">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10">
+      <c r="A397" t="s">
+        <v>25</v>
+      </c>
+      <c r="B397" t="s">
+        <v>26</v>
+      </c>
+      <c r="C397" t="s">
+        <v>31</v>
+      </c>
+      <c r="D397">
+        <v>5954007</v>
+      </c>
+      <c r="E397" t="s">
+        <v>55</v>
+      </c>
+      <c r="F397">
+        <v>75</v>
+      </c>
+      <c r="G397">
+        <v>20</v>
+      </c>
+      <c r="H397">
+        <v>15</v>
+      </c>
+      <c r="I397">
+        <v>42</v>
+      </c>
+      <c r="J397">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10">
+      <c r="A398" t="s">
+        <v>25</v>
+      </c>
+      <c r="B398" t="s">
+        <v>26</v>
+      </c>
+      <c r="C398" t="s">
+        <v>31</v>
+      </c>
+      <c r="D398">
+        <v>7081903</v>
+      </c>
+      <c r="E398" t="s">
+        <v>56</v>
+      </c>
+      <c r="F398">
+        <v>37</v>
+      </c>
+      <c r="G398">
+        <v>11</v>
+      </c>
+      <c r="H398">
+        <v>2</v>
+      </c>
+      <c r="I398">
+        <v>20</v>
+      </c>
+      <c r="J398">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10">
+      <c r="A399" t="s">
+        <v>25</v>
+      </c>
+      <c r="B399" t="s">
+        <v>26</v>
+      </c>
+      <c r="C399" t="s">
+        <v>32</v>
+      </c>
+      <c r="D399">
+        <v>9366541</v>
+      </c>
+      <c r="E399" t="s">
+        <v>57</v>
+      </c>
+      <c r="F399">
+        <v>34</v>
+      </c>
+      <c r="G399">
+        <v>11</v>
+      </c>
+      <c r="H399">
+        <v>1</v>
+      </c>
+      <c r="I399">
+        <v>18</v>
+      </c>
+      <c r="J399">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10">
+      <c r="A400" t="s">
+        <v>25</v>
+      </c>
+      <c r="B400" t="s">
+        <v>26</v>
+      </c>
+      <c r="C400" t="s">
+        <v>33</v>
+      </c>
+      <c r="D400">
+        <v>6435172</v>
+      </c>
+      <c r="E400" t="s">
+        <v>58</v>
+      </c>
+      <c r="F400">
+        <v>8</v>
+      </c>
+      <c r="G400">
+        <v>6</v>
+      </c>
+      <c r="H400">
+        <v>0</v>
+      </c>
+      <c r="I400">
+        <v>8</v>
+      </c>
+      <c r="J400">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10">
+      <c r="A401" t="s">
+        <v>25</v>
+      </c>
+      <c r="B401" t="s">
+        <v>26</v>
+      </c>
+      <c r="C401" t="s">
+        <v>34</v>
+      </c>
+      <c r="D401">
+        <v>7077736</v>
+      </c>
+      <c r="E401" t="s">
+        <v>59</v>
+      </c>
+      <c r="F401">
+        <v>6</v>
+      </c>
+      <c r="G401">
+        <v>2</v>
+      </c>
+      <c r="H401">
+        <v>0</v>
+      </c>
+      <c r="I401">
+        <v>4</v>
+      </c>
+      <c r="J401">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="61">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -551,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J401"/>
+  <dimension ref="A1:J426"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -591,16 +594,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -623,16 +626,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -655,16 +658,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -687,16 +690,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -719,16 +722,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -751,16 +754,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -783,16 +786,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -815,16 +818,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -847,16 +850,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -879,16 +882,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -911,16 +914,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -943,16 +946,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -975,16 +978,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1007,16 +1010,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1039,16 +1042,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1071,16 +1074,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1103,16 +1106,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1135,16 +1138,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1167,16 +1170,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1199,16 +1202,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1231,16 +1234,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1263,16 +1266,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1295,16 +1298,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1327,16 +1330,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1359,16 +1362,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1391,16 +1394,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1423,16 +1426,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1455,16 +1458,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1487,16 +1490,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1519,16 +1522,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1551,16 +1554,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1583,16 +1586,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1615,16 +1618,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1647,16 +1650,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1679,16 +1682,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1711,16 +1714,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1743,16 +1746,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1775,16 +1778,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1807,16 +1810,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1839,16 +1842,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1871,16 +1874,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1903,16 +1906,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1935,16 +1938,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1967,16 +1970,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -1999,16 +2002,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2031,16 +2034,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2063,16 +2066,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2095,16 +2098,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2127,16 +2130,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2159,16 +2162,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2191,16 +2194,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2223,16 +2226,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2255,16 +2258,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2287,16 +2290,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2319,16 +2322,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2351,16 +2354,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2383,16 +2386,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2415,16 +2418,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2447,16 +2450,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2479,16 +2482,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2511,16 +2514,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2543,16 +2546,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2575,16 +2578,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2607,16 +2610,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2639,16 +2642,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2671,16 +2674,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2703,16 +2706,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2735,16 +2738,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2767,16 +2770,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2799,16 +2802,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2831,16 +2834,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2863,16 +2866,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2895,16 +2898,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2927,16 +2930,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2959,16 +2962,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2991,16 +2994,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3023,16 +3026,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3055,16 +3058,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3087,16 +3090,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3119,16 +3122,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3151,16 +3154,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3183,16 +3186,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3215,16 +3218,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3247,16 +3250,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3279,16 +3282,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3311,16 +3314,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3343,16 +3346,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3375,16 +3378,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3407,16 +3410,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3439,16 +3442,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3471,16 +3474,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3503,16 +3506,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3535,16 +3538,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3567,16 +3570,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3599,16 +3602,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3631,16 +3634,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C97" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3663,16 +3666,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3695,16 +3698,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3727,16 +3730,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3759,16 +3762,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3791,16 +3794,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3823,16 +3826,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3855,16 +3858,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3887,16 +3890,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C105" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3919,16 +3922,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C106" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3951,16 +3954,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3983,16 +3986,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4015,16 +4018,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C109" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4047,16 +4050,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4079,16 +4082,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C111" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4111,16 +4114,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C112" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4143,16 +4146,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4175,16 +4178,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4207,16 +4210,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4239,16 +4242,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4271,16 +4274,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4303,16 +4306,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4335,16 +4338,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4367,16 +4370,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4399,16 +4402,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4431,16 +4434,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4463,16 +4466,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4495,16 +4498,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4527,16 +4530,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4559,16 +4562,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4591,16 +4594,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C127" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4623,16 +4626,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C128" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4655,16 +4658,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C129" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4687,16 +4690,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4719,16 +4722,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4751,16 +4754,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C132" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4783,16 +4786,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C133" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4815,16 +4818,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C134" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4847,16 +4850,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C135" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4879,16 +4882,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4911,16 +4914,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4943,16 +4946,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4975,16 +4978,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C139" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -5007,16 +5010,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C140" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5039,16 +5042,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C141" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5071,16 +5074,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C142" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5103,16 +5106,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5135,16 +5138,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5167,16 +5170,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5199,16 +5202,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5231,16 +5234,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C147" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5263,16 +5266,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C148" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5295,16 +5298,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C149" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5327,16 +5330,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C150" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5359,16 +5362,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C151" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5391,16 +5394,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C152" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5423,16 +5426,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C153" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5455,16 +5458,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C154" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5487,16 +5490,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C155" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5519,16 +5522,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C156" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5551,16 +5554,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C157" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5583,16 +5586,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C158" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5615,16 +5618,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C159" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5647,16 +5650,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C160" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5679,16 +5682,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C161" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5711,16 +5714,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C162" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5743,16 +5746,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C163" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5775,16 +5778,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5807,16 +5810,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C165" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5839,16 +5842,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C166" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5871,16 +5874,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C167" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5903,16 +5906,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C168" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5935,16 +5938,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C169" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5967,16 +5970,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -5999,16 +6002,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C171" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6031,16 +6034,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C172" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6063,16 +6066,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C173" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6095,16 +6098,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C174" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6127,16 +6130,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C175" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6159,16 +6162,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C176" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6191,16 +6194,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C177" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6223,16 +6226,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C178" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6255,16 +6258,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C179" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6287,16 +6290,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C180" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6319,16 +6322,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C181" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6351,16 +6354,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C182" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6383,16 +6386,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C183" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6415,16 +6418,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C184" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6447,16 +6450,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C185" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6479,16 +6482,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C186" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6511,16 +6514,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6543,16 +6546,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C188" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6575,16 +6578,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C189" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6607,16 +6610,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C190" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6639,16 +6642,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C191" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6671,16 +6674,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6703,16 +6706,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C193" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6735,16 +6738,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C194" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6767,16 +6770,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C195" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6799,16 +6802,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C196" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6831,16 +6834,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6863,16 +6866,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6895,16 +6898,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6927,16 +6930,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C200" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6959,16 +6962,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C201" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6991,16 +6994,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7023,16 +7026,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C203" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7055,16 +7058,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C204" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7087,16 +7090,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C205" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7119,16 +7122,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7151,16 +7154,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7183,16 +7186,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C208" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7215,16 +7218,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7247,16 +7250,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C210" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7279,16 +7282,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7311,16 +7314,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7343,16 +7346,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C213" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7375,16 +7378,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7407,16 +7410,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C215" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7439,16 +7442,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C216" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7471,16 +7474,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C217" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7503,16 +7506,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C218" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7535,16 +7538,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C219" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7567,16 +7570,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C220" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7599,16 +7602,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C221" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7631,16 +7634,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7663,16 +7666,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C223" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7695,16 +7698,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C224" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7727,16 +7730,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C225" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7759,16 +7762,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C226" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7791,16 +7794,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C227" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7823,16 +7826,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C228" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7855,16 +7858,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C229" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7887,16 +7890,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C230" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7919,16 +7922,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C231" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7951,16 +7954,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C232" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7983,16 +7986,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C233" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8015,16 +8018,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C234" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8047,16 +8050,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C235" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8079,16 +8082,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C236" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8111,16 +8114,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C237" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8143,16 +8146,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C238" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8175,16 +8178,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C239" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8207,16 +8210,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C240" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8239,16 +8242,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C241" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8271,16 +8274,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C242" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8303,16 +8306,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C243" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8335,16 +8338,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C244" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8367,16 +8370,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C245" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8399,16 +8402,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C246" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8431,16 +8434,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C247" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8463,16 +8466,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C248" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8495,16 +8498,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C249" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8527,16 +8530,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C250" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8559,16 +8562,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C251" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8591,16 +8594,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C252" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8623,16 +8626,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C253" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8655,16 +8658,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C254" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8687,16 +8690,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C255" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8719,16 +8722,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C256" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8751,16 +8754,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C257" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8783,16 +8786,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C258" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8815,16 +8818,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C259" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8847,16 +8850,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C260" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8879,16 +8882,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C261" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8911,16 +8914,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C262" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8943,16 +8946,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C263" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8975,16 +8978,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C264" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -9007,16 +9010,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C265" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9039,16 +9042,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C266" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9071,16 +9074,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C267" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9103,16 +9106,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C268" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9135,16 +9138,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C269" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9167,16 +9170,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9199,16 +9202,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C271" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9231,16 +9234,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C272" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9263,16 +9266,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C273" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9295,16 +9298,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C274" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9327,16 +9330,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C275" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9359,16 +9362,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C276" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9391,16 +9394,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C277" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F277">
         <v>45</v>
@@ -9423,16 +9426,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F278">
         <v>20</v>
@@ -9455,16 +9458,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C279" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F279">
         <v>38</v>
@@ -9487,16 +9490,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C280" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F280">
         <v>43</v>
@@ -9519,16 +9522,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C281" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F281">
         <v>90</v>
@@ -9551,16 +9554,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C282" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F282">
         <v>34</v>
@@ -9583,16 +9586,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C283" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F283">
         <v>103</v>
@@ -9615,16 +9618,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C284" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -9647,16 +9650,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C285" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F285">
         <v>69</v>
@@ -9679,16 +9682,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C286" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F286">
         <v>9</v>
@@ -9711,16 +9714,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C287" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F287">
         <v>16</v>
@@ -9743,16 +9746,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C288" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F288">
         <v>2</v>
@@ -9775,16 +9778,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C289" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F289">
         <v>2</v>
@@ -9807,16 +9810,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C290" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F290">
         <v>3</v>
@@ -9839,16 +9842,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C291" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F291">
         <v>51</v>
@@ -9871,16 +9874,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C292" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F292">
         <v>3</v>
@@ -9903,16 +9906,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C293" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F293">
         <v>44</v>
@@ -9935,16 +9938,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C294" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F294">
         <v>11</v>
@@ -9967,16 +9970,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C295" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F295">
         <v>20</v>
@@ -9999,16 +10002,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C296" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F296">
         <v>9</v>
@@ -10031,16 +10034,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C297" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F297">
         <v>117</v>
@@ -10063,16 +10066,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C298" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F298">
         <v>59</v>
@@ -10095,16 +10098,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C299" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F299">
         <v>40</v>
@@ -10127,16 +10130,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C300" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F300">
         <v>10</v>
@@ -10159,16 +10162,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C301" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F301">
         <v>9</v>
@@ -10191,16 +10194,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C302" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F302">
         <v>44</v>
@@ -10223,16 +10226,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C303" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F303">
         <v>20</v>
@@ -10255,16 +10258,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C304" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F304">
         <v>28</v>
@@ -10287,16 +10290,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C305" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F305">
         <v>24</v>
@@ -10319,16 +10322,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C306" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F306">
         <v>83</v>
@@ -10351,16 +10354,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C307" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F307">
         <v>43</v>
@@ -10383,16 +10386,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C308" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F308">
         <v>89</v>
@@ -10415,16 +10418,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C309" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F309">
         <v>13</v>
@@ -10447,16 +10450,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C310" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F310">
         <v>43</v>
@@ -10479,16 +10482,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C311" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F311">
         <v>10</v>
@@ -10511,16 +10514,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C312" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F312">
         <v>7</v>
@@ -10543,16 +10546,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C313" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F313">
         <v>3</v>
@@ -10575,16 +10578,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C314" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -10607,16 +10610,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C315" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -10639,16 +10642,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C316" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F316">
         <v>62</v>
@@ -10671,16 +10674,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C317" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F317">
         <v>3</v>
@@ -10703,16 +10706,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C318" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F318">
         <v>40</v>
@@ -10735,16 +10738,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C319" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F319">
         <v>8</v>
@@ -10767,16 +10770,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C320" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F320">
         <v>14</v>
@@ -10799,16 +10802,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C321" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -10831,16 +10834,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C322" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F322">
         <v>132</v>
@@ -10863,16 +10866,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C323" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F323">
         <v>43</v>
@@ -10895,16 +10898,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C324" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F324">
         <v>48</v>
@@ -10927,16 +10930,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C325" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F325">
         <v>17</v>
@@ -10959,16 +10962,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C326" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F326">
         <v>8</v>
@@ -10991,16 +10994,16 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C327" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D327">
         <v>7381125</v>
       </c>
       <c r="E327" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F327">
         <v>56</v>
@@ -11023,16 +11026,16 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C328" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D328">
         <v>2207663</v>
       </c>
       <c r="E328" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F328">
         <v>26</v>
@@ -11055,16 +11058,16 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C329" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D329">
         <v>7397528</v>
       </c>
       <c r="E329" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F329">
         <v>40</v>
@@ -11087,16 +11090,16 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C330" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D330">
         <v>5931712</v>
       </c>
       <c r="E330" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F330">
         <v>34</v>
@@ -11119,16 +11122,16 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C331" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D331">
         <v>7325488</v>
       </c>
       <c r="E331" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F331">
         <v>99</v>
@@ -11151,16 +11154,16 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C332" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D332">
         <v>3368175</v>
       </c>
       <c r="E332" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F332">
         <v>51</v>
@@ -11183,16 +11186,16 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C333" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D333">
         <v>3864716</v>
       </c>
       <c r="E333" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F333">
         <v>104</v>
@@ -11215,16 +11218,16 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C334" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D334">
         <v>3367403</v>
       </c>
       <c r="E334" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F334">
         <v>14</v>
@@ -11247,16 +11250,16 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C335" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D335">
         <v>7381124</v>
       </c>
       <c r="E335" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F335">
         <v>49</v>
@@ -11279,16 +11282,16 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C336" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D336">
         <v>7079978</v>
       </c>
       <c r="E336" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F336">
         <v>20</v>
@@ -11311,16 +11314,16 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C337" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D337">
         <v>3367739</v>
       </c>
       <c r="E337" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F337">
         <v>8</v>
@@ -11343,16 +11346,16 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C338" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D338">
         <v>7072286</v>
       </c>
       <c r="E338" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F338">
         <v>3</v>
@@ -11375,16 +11378,16 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C339" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D339">
         <v>3367743</v>
       </c>
       <c r="E339" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F339">
         <v>8</v>
@@ -11407,16 +11410,16 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C340" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D340">
         <v>4214024</v>
       </c>
       <c r="E340" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F340">
         <v>8</v>
@@ -11439,16 +11442,16 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C341" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D341">
         <v>7357843</v>
       </c>
       <c r="E341" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F341">
         <v>68</v>
@@ -11471,16 +11474,16 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C342" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D342">
         <v>7077448</v>
       </c>
       <c r="E342" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F342">
         <v>3</v>
@@ -11503,16 +11506,16 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C343" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D343">
         <v>2278099</v>
       </c>
       <c r="E343" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F343">
         <v>48</v>
@@ -11535,16 +11538,16 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C344" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D344">
         <v>7077738</v>
       </c>
       <c r="E344" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F344">
         <v>8</v>
@@ -11567,16 +11570,16 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C345" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D345">
         <v>4493936</v>
       </c>
       <c r="E345" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F345">
         <v>14</v>
@@ -11599,16 +11602,16 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C346" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D346">
         <v>5284531</v>
       </c>
       <c r="E346" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F346">
         <v>7</v>
@@ -11631,16 +11634,16 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C347" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D347">
         <v>5954007</v>
       </c>
       <c r="E347" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F347">
         <v>123</v>
@@ -11663,16 +11666,16 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C348" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D348">
         <v>7081903</v>
       </c>
       <c r="E348" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F348">
         <v>50</v>
@@ -11695,16 +11698,16 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C349" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D349">
         <v>9366541</v>
       </c>
       <c r="E349" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F349">
         <v>49</v>
@@ -11727,16 +11730,16 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C350" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D350">
         <v>6435172</v>
       </c>
       <c r="E350" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F350">
         <v>17</v>
@@ -11759,16 +11762,16 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C351" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D351">
         <v>7077736</v>
       </c>
       <c r="E351" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F351">
         <v>8</v>
@@ -11791,16 +11794,16 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C352" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D352">
         <v>7381125</v>
       </c>
       <c r="E352" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F352">
         <v>33</v>
@@ -11823,16 +11826,16 @@
         <v>24</v>
       </c>
       <c r="B353" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C353" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D353">
         <v>2207663</v>
       </c>
       <c r="E353" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F353">
         <v>21</v>
@@ -11855,16 +11858,16 @@
         <v>24</v>
       </c>
       <c r="B354" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C354" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D354">
         <v>7397528</v>
       </c>
       <c r="E354" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F354">
         <v>27</v>
@@ -11887,16 +11890,16 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C355" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D355">
         <v>5931712</v>
       </c>
       <c r="E355" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F355">
         <v>23</v>
@@ -11919,16 +11922,16 @@
         <v>24</v>
       </c>
       <c r="B356" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C356" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D356">
         <v>7325488</v>
       </c>
       <c r="E356" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F356">
         <v>69</v>
@@ -11951,16 +11954,16 @@
         <v>24</v>
       </c>
       <c r="B357" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C357" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D357">
         <v>3368175</v>
       </c>
       <c r="E357" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F357">
         <v>21</v>
@@ -11983,16 +11986,16 @@
         <v>24</v>
       </c>
       <c r="B358" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C358" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D358">
         <v>3864716</v>
       </c>
       <c r="E358" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F358">
         <v>72</v>
@@ -12015,16 +12018,16 @@
         <v>24</v>
       </c>
       <c r="B359" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C359" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D359">
         <v>3367403</v>
       </c>
       <c r="E359" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F359">
         <v>6</v>
@@ -12047,16 +12050,16 @@
         <v>24</v>
       </c>
       <c r="B360" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C360" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D360">
         <v>7381124</v>
       </c>
       <c r="E360" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F360">
         <v>28</v>
@@ -12079,16 +12082,16 @@
         <v>24</v>
       </c>
       <c r="B361" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C361" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D361">
         <v>7079978</v>
       </c>
       <c r="E361" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F361">
         <v>10</v>
@@ -12111,16 +12114,16 @@
         <v>24</v>
       </c>
       <c r="B362" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C362" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D362">
         <v>3367739</v>
       </c>
       <c r="E362" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F362">
         <v>3</v>
@@ -12143,16 +12146,16 @@
         <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C363" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D363">
         <v>7072286</v>
       </c>
       <c r="E363" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F363">
         <v>3</v>
@@ -12175,16 +12178,16 @@
         <v>24</v>
       </c>
       <c r="B364" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C364" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D364">
         <v>3367743</v>
       </c>
       <c r="E364" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F364">
         <v>6</v>
@@ -12207,16 +12210,16 @@
         <v>24</v>
       </c>
       <c r="B365" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C365" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D365">
         <v>4214024</v>
       </c>
       <c r="E365" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F365">
         <v>4</v>
@@ -12239,16 +12242,16 @@
         <v>24</v>
       </c>
       <c r="B366" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C366" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D366">
         <v>7357843</v>
       </c>
       <c r="E366" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F366">
         <v>50</v>
@@ -12271,16 +12274,16 @@
         <v>24</v>
       </c>
       <c r="B367" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C367" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D367">
         <v>7077448</v>
       </c>
       <c r="E367" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F367">
         <v>2</v>
@@ -12303,16 +12306,16 @@
         <v>24</v>
       </c>
       <c r="B368" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C368" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D368">
         <v>2278099</v>
       </c>
       <c r="E368" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F368">
         <v>26</v>
@@ -12335,16 +12338,16 @@
         <v>24</v>
       </c>
       <c r="B369" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C369" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D369">
         <v>7077738</v>
       </c>
       <c r="E369" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F369">
         <v>6</v>
@@ -12367,16 +12370,16 @@
         <v>24</v>
       </c>
       <c r="B370" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C370" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D370">
         <v>4493936</v>
       </c>
       <c r="E370" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F370">
         <v>10</v>
@@ -12399,16 +12402,16 @@
         <v>24</v>
       </c>
       <c r="B371" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C371" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D371">
         <v>5284531</v>
       </c>
       <c r="E371" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F371">
         <v>3</v>
@@ -12431,16 +12434,16 @@
         <v>24</v>
       </c>
       <c r="B372" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C372" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D372">
         <v>5954007</v>
       </c>
       <c r="E372" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F372">
         <v>91</v>
@@ -12463,16 +12466,16 @@
         <v>24</v>
       </c>
       <c r="B373" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C373" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D373">
         <v>7081903</v>
       </c>
       <c r="E373" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F373">
         <v>35</v>
@@ -12495,16 +12498,16 @@
         <v>24</v>
       </c>
       <c r="B374" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C374" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D374">
         <v>9366541</v>
       </c>
       <c r="E374" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F374">
         <v>33</v>
@@ -12527,16 +12530,16 @@
         <v>24</v>
       </c>
       <c r="B375" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C375" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D375">
         <v>6435172</v>
       </c>
       <c r="E375" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F375">
         <v>10</v>
@@ -12559,16 +12562,16 @@
         <v>24</v>
       </c>
       <c r="B376" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C376" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D376">
         <v>7077736</v>
       </c>
       <c r="E376" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F376">
         <v>3</v>
@@ -12591,16 +12594,16 @@
         <v>25</v>
       </c>
       <c r="B377" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C377" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D377">
         <v>7381125</v>
       </c>
       <c r="E377" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F377">
         <v>32</v>
@@ -12623,16 +12626,16 @@
         <v>25</v>
       </c>
       <c r="B378" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C378" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D378">
         <v>2207663</v>
       </c>
       <c r="E378" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F378">
         <v>18</v>
@@ -12655,16 +12658,16 @@
         <v>25</v>
       </c>
       <c r="B379" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C379" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D379">
         <v>7397528</v>
       </c>
       <c r="E379" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F379">
         <v>28</v>
@@ -12687,16 +12690,16 @@
         <v>25</v>
       </c>
       <c r="B380" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C380" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D380">
         <v>5931712</v>
       </c>
       <c r="E380" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F380">
         <v>22</v>
@@ -12719,16 +12722,16 @@
         <v>25</v>
       </c>
       <c r="B381" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C381" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D381">
         <v>7325488</v>
       </c>
       <c r="E381" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F381">
         <v>62</v>
@@ -12751,16 +12754,16 @@
         <v>25</v>
       </c>
       <c r="B382" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C382" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D382">
         <v>3368175</v>
       </c>
       <c r="E382" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F382">
         <v>26</v>
@@ -12783,16 +12786,16 @@
         <v>25</v>
       </c>
       <c r="B383" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C383" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D383">
         <v>3864716</v>
       </c>
       <c r="E383" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F383">
         <v>44</v>
@@ -12815,16 +12818,16 @@
         <v>25</v>
       </c>
       <c r="B384" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C384" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D384">
         <v>3367403</v>
       </c>
       <c r="E384" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F384">
         <v>4</v>
@@ -12847,16 +12850,16 @@
         <v>25</v>
       </c>
       <c r="B385" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C385" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D385">
         <v>7381124</v>
       </c>
       <c r="E385" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F385">
         <v>27</v>
@@ -12879,16 +12882,16 @@
         <v>25</v>
       </c>
       <c r="B386" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C386" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D386">
         <v>7079978</v>
       </c>
       <c r="E386" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F386">
         <v>7</v>
@@ -12911,16 +12914,16 @@
         <v>25</v>
       </c>
       <c r="B387" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C387" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D387">
         <v>3367739</v>
       </c>
       <c r="E387" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F387">
         <v>2</v>
@@ -12943,16 +12946,16 @@
         <v>25</v>
       </c>
       <c r="B388" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C388" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D388">
         <v>7072286</v>
       </c>
       <c r="E388" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F388">
         <v>4</v>
@@ -12975,16 +12978,16 @@
         <v>25</v>
       </c>
       <c r="B389" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C389" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D389">
         <v>3367743</v>
       </c>
       <c r="E389" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F389">
         <v>6</v>
@@ -13007,16 +13010,16 @@
         <v>25</v>
       </c>
       <c r="B390" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C390" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D390">
         <v>4214024</v>
       </c>
       <c r="E390" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F390">
         <v>2</v>
@@ -13039,16 +13042,16 @@
         <v>25</v>
       </c>
       <c r="B391" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C391" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D391">
         <v>7357843</v>
       </c>
       <c r="E391" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F391">
         <v>46</v>
@@ -13071,16 +13074,16 @@
         <v>25</v>
       </c>
       <c r="B392" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C392" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D392">
         <v>7077448</v>
       </c>
       <c r="E392" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F392">
         <v>4</v>
@@ -13103,16 +13106,16 @@
         <v>25</v>
       </c>
       <c r="B393" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C393" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D393">
         <v>2278099</v>
       </c>
       <c r="E393" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F393">
         <v>33</v>
@@ -13135,16 +13138,16 @@
         <v>25</v>
       </c>
       <c r="B394" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C394" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D394">
         <v>7077738</v>
       </c>
       <c r="E394" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F394">
         <v>6</v>
@@ -13167,16 +13170,16 @@
         <v>25</v>
       </c>
       <c r="B395" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C395" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D395">
         <v>4493936</v>
       </c>
       <c r="E395" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F395">
         <v>8</v>
@@ -13199,16 +13202,16 @@
         <v>25</v>
       </c>
       <c r="B396" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C396" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D396">
         <v>5284531</v>
       </c>
       <c r="E396" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F396">
         <v>4</v>
@@ -13231,16 +13234,16 @@
         <v>25</v>
       </c>
       <c r="B397" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C397" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D397">
         <v>5954007</v>
       </c>
       <c r="E397" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F397">
         <v>75</v>
@@ -13263,16 +13266,16 @@
         <v>25</v>
       </c>
       <c r="B398" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C398" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D398">
         <v>7081903</v>
       </c>
       <c r="E398" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F398">
         <v>37</v>
@@ -13295,16 +13298,16 @@
         <v>25</v>
       </c>
       <c r="B399" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C399" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D399">
         <v>9366541</v>
       </c>
       <c r="E399" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F399">
         <v>34</v>
@@ -13327,16 +13330,16 @@
         <v>25</v>
       </c>
       <c r="B400" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C400" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D400">
         <v>6435172</v>
       </c>
       <c r="E400" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F400">
         <v>8</v>
@@ -13359,16 +13362,16 @@
         <v>25</v>
       </c>
       <c r="B401" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C401" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D401">
         <v>7077736</v>
       </c>
       <c r="E401" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F401">
         <v>6</v>
@@ -13384,6 +13387,806 @@
       </c>
       <c r="J401">
         <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10">
+      <c r="A402" t="s">
+        <v>26</v>
+      </c>
+      <c r="B402" t="s">
+        <v>27</v>
+      </c>
+      <c r="C402" t="s">
+        <v>27</v>
+      </c>
+      <c r="D402">
+        <v>7381125</v>
+      </c>
+      <c r="E402" t="s">
+        <v>36</v>
+      </c>
+      <c r="F402">
+        <v>32</v>
+      </c>
+      <c r="G402">
+        <v>15</v>
+      </c>
+      <c r="H402">
+        <v>8</v>
+      </c>
+      <c r="I402">
+        <v>17</v>
+      </c>
+      <c r="J402">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="A403" t="s">
+        <v>26</v>
+      </c>
+      <c r="B403" t="s">
+        <v>27</v>
+      </c>
+      <c r="C403" t="s">
+        <v>27</v>
+      </c>
+      <c r="D403">
+        <v>2207663</v>
+      </c>
+      <c r="E403" t="s">
+        <v>37</v>
+      </c>
+      <c r="F403">
+        <v>15</v>
+      </c>
+      <c r="G403">
+        <v>12</v>
+      </c>
+      <c r="H403">
+        <v>2</v>
+      </c>
+      <c r="I403">
+        <v>15</v>
+      </c>
+      <c r="J403">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="A404" t="s">
+        <v>26</v>
+      </c>
+      <c r="B404" t="s">
+        <v>27</v>
+      </c>
+      <c r="C404" t="s">
+        <v>27</v>
+      </c>
+      <c r="D404">
+        <v>7397528</v>
+      </c>
+      <c r="E404" t="s">
+        <v>38</v>
+      </c>
+      <c r="F404">
+        <v>29</v>
+      </c>
+      <c r="G404">
+        <v>13</v>
+      </c>
+      <c r="H404">
+        <v>9</v>
+      </c>
+      <c r="I404">
+        <v>33</v>
+      </c>
+      <c r="J404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
+      <c r="A405" t="s">
+        <v>26</v>
+      </c>
+      <c r="B405" t="s">
+        <v>27</v>
+      </c>
+      <c r="C405" t="s">
+        <v>27</v>
+      </c>
+      <c r="D405">
+        <v>5931712</v>
+      </c>
+      <c r="E405" t="s">
+        <v>39</v>
+      </c>
+      <c r="F405">
+        <v>15</v>
+      </c>
+      <c r="G405">
+        <v>20</v>
+      </c>
+      <c r="H405">
+        <v>3</v>
+      </c>
+      <c r="I405">
+        <v>22</v>
+      </c>
+      <c r="J405">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
+      <c r="A406" t="s">
+        <v>26</v>
+      </c>
+      <c r="B406" t="s">
+        <v>27</v>
+      </c>
+      <c r="C406" t="s">
+        <v>27</v>
+      </c>
+      <c r="D406">
+        <v>7325488</v>
+      </c>
+      <c r="E406" t="s">
+        <v>40</v>
+      </c>
+      <c r="F406">
+        <v>70</v>
+      </c>
+      <c r="G406">
+        <v>20</v>
+      </c>
+      <c r="H406">
+        <v>11</v>
+      </c>
+      <c r="I406">
+        <v>22</v>
+      </c>
+      <c r="J406">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
+      <c r="A407" t="s">
+        <v>26</v>
+      </c>
+      <c r="B407" t="s">
+        <v>27</v>
+      </c>
+      <c r="C407" t="s">
+        <v>27</v>
+      </c>
+      <c r="D407">
+        <v>3368175</v>
+      </c>
+      <c r="E407" t="s">
+        <v>41</v>
+      </c>
+      <c r="F407">
+        <v>28</v>
+      </c>
+      <c r="G407">
+        <v>18</v>
+      </c>
+      <c r="H407">
+        <v>9</v>
+      </c>
+      <c r="I407">
+        <v>36</v>
+      </c>
+      <c r="J407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10">
+      <c r="A408" t="s">
+        <v>26</v>
+      </c>
+      <c r="B408" t="s">
+        <v>27</v>
+      </c>
+      <c r="C408" t="s">
+        <v>27</v>
+      </c>
+      <c r="D408">
+        <v>3864716</v>
+      </c>
+      <c r="E408" t="s">
+        <v>42</v>
+      </c>
+      <c r="F408">
+        <v>50</v>
+      </c>
+      <c r="G408">
+        <v>24</v>
+      </c>
+      <c r="H408">
+        <v>8</v>
+      </c>
+      <c r="I408">
+        <v>22</v>
+      </c>
+      <c r="J408">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10">
+      <c r="A409" t="s">
+        <v>26</v>
+      </c>
+      <c r="B409" t="s">
+        <v>27</v>
+      </c>
+      <c r="C409" t="s">
+        <v>27</v>
+      </c>
+      <c r="D409">
+        <v>3367403</v>
+      </c>
+      <c r="E409" t="s">
+        <v>43</v>
+      </c>
+      <c r="F409">
+        <v>4</v>
+      </c>
+      <c r="G409">
+        <v>6</v>
+      </c>
+      <c r="H409">
+        <v>3</v>
+      </c>
+      <c r="I409">
+        <v>4</v>
+      </c>
+      <c r="J409">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10">
+      <c r="A410" t="s">
+        <v>26</v>
+      </c>
+      <c r="B410" t="s">
+        <v>27</v>
+      </c>
+      <c r="C410" t="s">
+        <v>27</v>
+      </c>
+      <c r="D410">
+        <v>7381124</v>
+      </c>
+      <c r="E410" t="s">
+        <v>44</v>
+      </c>
+      <c r="F410">
+        <v>29</v>
+      </c>
+      <c r="G410">
+        <v>20</v>
+      </c>
+      <c r="H410">
+        <v>6</v>
+      </c>
+      <c r="I410">
+        <v>16</v>
+      </c>
+      <c r="J410">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10">
+      <c r="A411" t="s">
+        <v>26</v>
+      </c>
+      <c r="B411" t="s">
+        <v>27</v>
+      </c>
+      <c r="C411" t="s">
+        <v>28</v>
+      </c>
+      <c r="D411">
+        <v>7079978</v>
+      </c>
+      <c r="E411" t="s">
+        <v>45</v>
+      </c>
+      <c r="F411">
+        <v>10</v>
+      </c>
+      <c r="G411">
+        <v>10</v>
+      </c>
+      <c r="H411">
+        <v>2</v>
+      </c>
+      <c r="I411">
+        <v>2</v>
+      </c>
+      <c r="J411">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10">
+      <c r="A412" t="s">
+        <v>26</v>
+      </c>
+      <c r="B412" t="s">
+        <v>27</v>
+      </c>
+      <c r="C412" t="s">
+        <v>28</v>
+      </c>
+      <c r="D412">
+        <v>3367739</v>
+      </c>
+      <c r="E412" t="s">
+        <v>46</v>
+      </c>
+      <c r="F412">
+        <v>1</v>
+      </c>
+      <c r="G412">
+        <v>2</v>
+      </c>
+      <c r="H412">
+        <v>0</v>
+      </c>
+      <c r="I412">
+        <v>5</v>
+      </c>
+      <c r="J412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10">
+      <c r="A413" t="s">
+        <v>26</v>
+      </c>
+      <c r="B413" t="s">
+        <v>27</v>
+      </c>
+      <c r="C413" t="s">
+        <v>29</v>
+      </c>
+      <c r="D413">
+        <v>7072286</v>
+      </c>
+      <c r="E413" t="s">
+        <v>47</v>
+      </c>
+      <c r="F413">
+        <v>3</v>
+      </c>
+      <c r="G413">
+        <v>1</v>
+      </c>
+      <c r="H413">
+        <v>0</v>
+      </c>
+      <c r="I413">
+        <v>0</v>
+      </c>
+      <c r="J413">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10">
+      <c r="A414" t="s">
+        <v>26</v>
+      </c>
+      <c r="B414" t="s">
+        <v>27</v>
+      </c>
+      <c r="C414" t="s">
+        <v>30</v>
+      </c>
+      <c r="D414">
+        <v>3367743</v>
+      </c>
+      <c r="E414" t="s">
+        <v>48</v>
+      </c>
+      <c r="F414">
+        <v>4</v>
+      </c>
+      <c r="G414">
+        <v>2</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+      <c r="I414">
+        <v>1</v>
+      </c>
+      <c r="J414">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10">
+      <c r="A415" t="s">
+        <v>26</v>
+      </c>
+      <c r="B415" t="s">
+        <v>27</v>
+      </c>
+      <c r="C415" t="s">
+        <v>29</v>
+      </c>
+      <c r="D415">
+        <v>4214024</v>
+      </c>
+      <c r="E415" t="s">
+        <v>49</v>
+      </c>
+      <c r="F415">
+        <v>6</v>
+      </c>
+      <c r="G415">
+        <v>1</v>
+      </c>
+      <c r="H415">
+        <v>0</v>
+      </c>
+      <c r="I415">
+        <v>3</v>
+      </c>
+      <c r="J415">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10">
+      <c r="A416" t="s">
+        <v>26</v>
+      </c>
+      <c r="B416" t="s">
+        <v>27</v>
+      </c>
+      <c r="C416" t="s">
+        <v>30</v>
+      </c>
+      <c r="D416">
+        <v>7357843</v>
+      </c>
+      <c r="E416" t="s">
+        <v>50</v>
+      </c>
+      <c r="F416">
+        <v>43</v>
+      </c>
+      <c r="G416">
+        <v>12</v>
+      </c>
+      <c r="H416">
+        <v>10</v>
+      </c>
+      <c r="I416">
+        <v>3</v>
+      </c>
+      <c r="J416">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10">
+      <c r="A417" t="s">
+        <v>26</v>
+      </c>
+      <c r="B417" t="s">
+        <v>27</v>
+      </c>
+      <c r="C417" t="s">
+        <v>30</v>
+      </c>
+      <c r="D417">
+        <v>7077448</v>
+      </c>
+      <c r="E417" t="s">
+        <v>51</v>
+      </c>
+      <c r="F417">
+        <v>8</v>
+      </c>
+      <c r="G417">
+        <v>0</v>
+      </c>
+      <c r="H417">
+        <v>0</v>
+      </c>
+      <c r="I417">
+        <v>2</v>
+      </c>
+      <c r="J417">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10">
+      <c r="A418" t="s">
+        <v>26</v>
+      </c>
+      <c r="B418" t="s">
+        <v>27</v>
+      </c>
+      <c r="C418" t="s">
+        <v>31</v>
+      </c>
+      <c r="D418">
+        <v>2278099</v>
+      </c>
+      <c r="E418" t="s">
+        <v>52</v>
+      </c>
+      <c r="F418">
+        <v>36</v>
+      </c>
+      <c r="G418">
+        <v>25</v>
+      </c>
+      <c r="H418">
+        <v>4</v>
+      </c>
+      <c r="I418">
+        <v>36</v>
+      </c>
+      <c r="J418">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10">
+      <c r="A419" t="s">
+        <v>26</v>
+      </c>
+      <c r="B419" t="s">
+        <v>27</v>
+      </c>
+      <c r="C419" t="s">
+        <v>31</v>
+      </c>
+      <c r="D419">
+        <v>7077738</v>
+      </c>
+      <c r="E419" t="s">
+        <v>53</v>
+      </c>
+      <c r="F419">
+        <v>6</v>
+      </c>
+      <c r="G419">
+        <v>4</v>
+      </c>
+      <c r="H419">
+        <v>0</v>
+      </c>
+      <c r="I419">
+        <v>4</v>
+      </c>
+      <c r="J419">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
+      <c r="A420" t="s">
+        <v>26</v>
+      </c>
+      <c r="B420" t="s">
+        <v>27</v>
+      </c>
+      <c r="C420" t="s">
+        <v>31</v>
+      </c>
+      <c r="D420">
+        <v>4493936</v>
+      </c>
+      <c r="E420" t="s">
+        <v>54</v>
+      </c>
+      <c r="F420">
+        <v>8</v>
+      </c>
+      <c r="G420">
+        <v>2</v>
+      </c>
+      <c r="H420">
+        <v>0</v>
+      </c>
+      <c r="I420">
+        <v>5</v>
+      </c>
+      <c r="J420">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
+      <c r="A421" t="s">
+        <v>26</v>
+      </c>
+      <c r="B421" t="s">
+        <v>27</v>
+      </c>
+      <c r="C421" t="s">
+        <v>31</v>
+      </c>
+      <c r="D421">
+        <v>5284531</v>
+      </c>
+      <c r="E421" t="s">
+        <v>55</v>
+      </c>
+      <c r="F421">
+        <v>5</v>
+      </c>
+      <c r="G421">
+        <v>4</v>
+      </c>
+      <c r="H421">
+        <v>1</v>
+      </c>
+      <c r="I421">
+        <v>2</v>
+      </c>
+      <c r="J421">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10">
+      <c r="A422" t="s">
+        <v>26</v>
+      </c>
+      <c r="B422" t="s">
+        <v>27</v>
+      </c>
+      <c r="C422" t="s">
+        <v>32</v>
+      </c>
+      <c r="D422">
+        <v>5954007</v>
+      </c>
+      <c r="E422" t="s">
+        <v>56</v>
+      </c>
+      <c r="F422">
+        <v>65</v>
+      </c>
+      <c r="G422">
+        <v>19</v>
+      </c>
+      <c r="H422">
+        <v>25</v>
+      </c>
+      <c r="I422">
+        <v>35</v>
+      </c>
+      <c r="J422">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
+      <c r="A423" t="s">
+        <v>26</v>
+      </c>
+      <c r="B423" t="s">
+        <v>27</v>
+      </c>
+      <c r="C423" t="s">
+        <v>32</v>
+      </c>
+      <c r="D423">
+        <v>7081903</v>
+      </c>
+      <c r="E423" t="s">
+        <v>57</v>
+      </c>
+      <c r="F423">
+        <v>30</v>
+      </c>
+      <c r="G423">
+        <v>14</v>
+      </c>
+      <c r="H423">
+        <v>3</v>
+      </c>
+      <c r="I423">
+        <v>19</v>
+      </c>
+      <c r="J423">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10">
+      <c r="A424" t="s">
+        <v>26</v>
+      </c>
+      <c r="B424" t="s">
+        <v>27</v>
+      </c>
+      <c r="C424" t="s">
+        <v>33</v>
+      </c>
+      <c r="D424">
+        <v>9366541</v>
+      </c>
+      <c r="E424" t="s">
+        <v>58</v>
+      </c>
+      <c r="F424">
+        <v>33</v>
+      </c>
+      <c r="G424">
+        <v>8</v>
+      </c>
+      <c r="H424">
+        <v>3</v>
+      </c>
+      <c r="I424">
+        <v>6</v>
+      </c>
+      <c r="J424">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10">
+      <c r="A425" t="s">
+        <v>26</v>
+      </c>
+      <c r="B425" t="s">
+        <v>27</v>
+      </c>
+      <c r="C425" t="s">
+        <v>34</v>
+      </c>
+      <c r="D425">
+        <v>6435172</v>
+      </c>
+      <c r="E425" t="s">
+        <v>59</v>
+      </c>
+      <c r="F425">
+        <v>9</v>
+      </c>
+      <c r="G425">
+        <v>7</v>
+      </c>
+      <c r="H425">
+        <v>0</v>
+      </c>
+      <c r="I425">
+        <v>5</v>
+      </c>
+      <c r="J425">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
+      <c r="A426" t="s">
+        <v>26</v>
+      </c>
+      <c r="B426" t="s">
+        <v>27</v>
+      </c>
+      <c r="C426" t="s">
+        <v>35</v>
+      </c>
+      <c r="D426">
+        <v>7077736</v>
+      </c>
+      <c r="E426" t="s">
+        <v>60</v>
+      </c>
+      <c r="F426">
+        <v>6</v>
+      </c>
+      <c r="G426">
+        <v>0</v>
+      </c>
+      <c r="H426">
+        <v>0</v>
+      </c>
+      <c r="I426">
+        <v>6</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Jobsdata.xlsx
+++ b/Jobsdata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="62">
   <si>
     <t>POSTING_DATE</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>İSTANBUL</t>
@@ -554,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J426"/>
+  <dimension ref="A1:J451"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -594,16 +597,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>7381125</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>19</v>
@@ -626,16 +629,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2207663</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>15</v>
@@ -658,16 +661,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>7397528</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -690,16 +693,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>5931712</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -722,16 +725,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>7325488</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -754,16 +757,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>3368175</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -786,16 +789,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>3864716</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>21</v>
@@ -818,16 +821,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>3367403</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -850,16 +853,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>7381124</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -882,16 +885,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>7079978</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -914,16 +917,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>3367739</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -946,16 +949,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>7072286</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -978,16 +981,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>3367743</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1010,16 +1013,16 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>4214024</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -1042,16 +1045,16 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>7357843</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>16</v>
@@ -1074,16 +1077,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17">
         <v>7077448</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1106,16 +1109,16 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>2278099</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1138,16 +1141,16 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19">
         <v>7077738</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -1170,16 +1173,16 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>4493936</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -1202,16 +1205,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>5284531</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -1234,16 +1237,16 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>5954007</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22">
         <v>26</v>
@@ -1266,16 +1269,16 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>7081903</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1298,16 +1301,16 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>9366541</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -1330,16 +1333,16 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>6435172</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1362,16 +1365,16 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26">
         <v>7077736</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -1394,16 +1397,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>7381125</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F27">
         <v>24</v>
@@ -1426,16 +1429,16 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2207663</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28">
         <v>16</v>
@@ -1458,16 +1461,16 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>7397528</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -1490,16 +1493,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>5931712</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F30">
         <v>13</v>
@@ -1522,16 +1525,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>7325488</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F31">
         <v>18</v>
@@ -1554,16 +1557,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>3368175</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32">
         <v>22</v>
@@ -1586,16 +1589,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>3864716</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33">
         <v>30</v>
@@ -1618,16 +1621,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>3367403</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -1650,16 +1653,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>7381124</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F35">
         <v>36</v>
@@ -1682,16 +1685,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>7079978</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1714,16 +1717,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37">
         <v>3367739</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1746,16 +1749,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D38">
         <v>7072286</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -1778,16 +1781,16 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39">
         <v>3367743</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1810,16 +1813,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D40">
         <v>4214024</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1842,16 +1845,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D41">
         <v>7357843</v>
       </c>
       <c r="E41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F41">
         <v>16</v>
@@ -1874,16 +1877,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D42">
         <v>7077448</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1906,16 +1909,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D43">
         <v>2278099</v>
       </c>
       <c r="E43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F43">
         <v>28</v>
@@ -1938,16 +1941,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D44">
         <v>7077738</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -1970,16 +1973,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D45">
         <v>4493936</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -2002,16 +2005,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D46">
         <v>5284531</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -2034,16 +2037,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D47">
         <v>5954007</v>
       </c>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F47">
         <v>23</v>
@@ -2066,16 +2069,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D48">
         <v>7081903</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F48">
         <v>10</v>
@@ -2098,16 +2101,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49">
         <v>9366541</v>
       </c>
       <c r="E49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F49">
         <v>27</v>
@@ -2130,16 +2133,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D50">
         <v>6435172</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -2162,16 +2165,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51">
         <v>7077736</v>
       </c>
       <c r="E51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2194,16 +2197,16 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>7381125</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F52">
         <v>27</v>
@@ -2226,16 +2229,16 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>2207663</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F53">
         <v>19</v>
@@ -2258,16 +2261,16 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>7397528</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F54">
         <v>28</v>
@@ -2290,16 +2293,16 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>5931712</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F55">
         <v>13</v>
@@ -2322,16 +2325,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>7325488</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F56">
         <v>28</v>
@@ -2354,16 +2357,16 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>3368175</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F57">
         <v>29</v>
@@ -2386,16 +2389,16 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>3864716</v>
       </c>
       <c r="E58" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F58">
         <v>41</v>
@@ -2418,16 +2421,16 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>3367403</v>
       </c>
       <c r="E59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F59">
         <v>6</v>
@@ -2450,16 +2453,16 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>7381124</v>
       </c>
       <c r="E60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F60">
         <v>34</v>
@@ -2482,16 +2485,16 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>7079978</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F61">
         <v>7</v>
@@ -2514,16 +2517,16 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>3367739</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -2546,16 +2549,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D63">
         <v>7072286</v>
       </c>
       <c r="E63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -2578,16 +2581,16 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D64">
         <v>3367743</v>
       </c>
       <c r="E64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2610,16 +2613,16 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D65">
         <v>4214024</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>2</v>
@@ -2642,16 +2645,16 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66">
         <v>7357843</v>
       </c>
       <c r="E66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F66">
         <v>17</v>
@@ -2674,16 +2677,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D67">
         <v>7077448</v>
       </c>
       <c r="E67" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F67">
         <v>2</v>
@@ -2706,16 +2709,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D68">
         <v>2278099</v>
       </c>
       <c r="E68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F68">
         <v>27</v>
@@ -2738,16 +2741,16 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D69">
         <v>7077738</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -2770,16 +2773,16 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D70">
         <v>4493936</v>
       </c>
       <c r="E70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F70">
         <v>7</v>
@@ -2802,16 +2805,16 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D71">
         <v>5284531</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F71">
         <v>6</v>
@@ -2834,16 +2837,16 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>5954007</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F72">
         <v>20</v>
@@ -2866,16 +2869,16 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>7081903</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -2898,16 +2901,16 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D74">
         <v>9366541</v>
       </c>
       <c r="E74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F74">
         <v>29</v>
@@ -2930,16 +2933,16 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D75">
         <v>6435172</v>
       </c>
       <c r="E75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -2962,16 +2965,16 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76">
         <v>7077736</v>
       </c>
       <c r="E76" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -2994,16 +2997,16 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D77">
         <v>7381125</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F77">
         <v>39</v>
@@ -3026,16 +3029,16 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D78">
         <v>2207663</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78">
         <v>25</v>
@@ -3058,16 +3061,16 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D79">
         <v>7397528</v>
       </c>
       <c r="E79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F79">
         <v>29</v>
@@ -3090,16 +3093,16 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D80">
         <v>5931712</v>
       </c>
       <c r="E80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F80">
         <v>22</v>
@@ -3122,16 +3125,16 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>7325488</v>
       </c>
       <c r="E81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F81">
         <v>39</v>
@@ -3154,16 +3157,16 @@
         <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D82">
         <v>3368175</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F82">
         <v>35</v>
@@ -3186,16 +3189,16 @@
         <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D83">
         <v>3864716</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F83">
         <v>36</v>
@@ -3218,16 +3221,16 @@
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D84">
         <v>3367403</v>
       </c>
       <c r="E84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -3250,16 +3253,16 @@
         <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D85">
         <v>7381124</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F85">
         <v>36</v>
@@ -3282,16 +3285,16 @@
         <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>7079978</v>
       </c>
       <c r="E86" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -3314,16 +3317,16 @@
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>3367739</v>
       </c>
       <c r="E87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F87">
         <v>7</v>
@@ -3346,16 +3349,16 @@
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D88">
         <v>7072286</v>
       </c>
       <c r="E88" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3378,16 +3381,16 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D89">
         <v>3367743</v>
       </c>
       <c r="E89" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F89">
         <v>2</v>
@@ -3410,16 +3413,16 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D90">
         <v>4214024</v>
       </c>
       <c r="E90" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -3442,16 +3445,16 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D91">
         <v>7357843</v>
       </c>
       <c r="E91" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F91">
         <v>20</v>
@@ -3474,16 +3477,16 @@
         <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D92">
         <v>7077448</v>
       </c>
       <c r="E92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -3506,16 +3509,16 @@
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D93">
         <v>2278099</v>
       </c>
       <c r="E93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F93">
         <v>23</v>
@@ -3538,16 +3541,16 @@
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D94">
         <v>7077738</v>
       </c>
       <c r="E94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F94">
         <v>7</v>
@@ -3570,16 +3573,16 @@
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D95">
         <v>4493936</v>
       </c>
       <c r="E95" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -3602,16 +3605,16 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D96">
         <v>5284531</v>
       </c>
       <c r="E96" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -3634,16 +3637,16 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C97" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>5954007</v>
       </c>
       <c r="E97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F97">
         <v>38</v>
@@ -3666,16 +3669,16 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D98">
         <v>7081903</v>
       </c>
       <c r="E98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F98">
         <v>26</v>
@@ -3698,16 +3701,16 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C99" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D99">
         <v>9366541</v>
       </c>
       <c r="E99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F99">
         <v>25</v>
@@ -3730,16 +3733,16 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D100">
         <v>6435172</v>
       </c>
       <c r="E100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F100">
         <v>4</v>
@@ -3762,16 +3765,16 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D101">
         <v>7077736</v>
       </c>
       <c r="E101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -3794,16 +3797,16 @@
         <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D102">
         <v>7381125</v>
       </c>
       <c r="E102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F102">
         <v>35</v>
@@ -3826,16 +3829,16 @@
         <v>14</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D103">
         <v>2207663</v>
       </c>
       <c r="E103" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F103">
         <v>29</v>
@@ -3858,16 +3861,16 @@
         <v>14</v>
       </c>
       <c r="B104" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D104">
         <v>7397528</v>
       </c>
       <c r="E104" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F104">
         <v>26</v>
@@ -3890,16 +3893,16 @@
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D105">
         <v>5931712</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F105">
         <v>27</v>
@@ -3922,16 +3925,16 @@
         <v>14</v>
       </c>
       <c r="B106" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D106">
         <v>7325488</v>
       </c>
       <c r="E106" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F106">
         <v>36</v>
@@ -3954,16 +3957,16 @@
         <v>14</v>
       </c>
       <c r="B107" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D107">
         <v>3368175</v>
       </c>
       <c r="E107" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F107">
         <v>30</v>
@@ -3986,16 +3989,16 @@
         <v>14</v>
       </c>
       <c r="B108" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C108" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D108">
         <v>3864716</v>
       </c>
       <c r="E108" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F108">
         <v>54</v>
@@ -4018,16 +4021,16 @@
         <v>14</v>
       </c>
       <c r="B109" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C109" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D109">
         <v>3367403</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -4050,16 +4053,16 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C110" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D110">
         <v>7381124</v>
       </c>
       <c r="E110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F110">
         <v>37</v>
@@ -4082,16 +4085,16 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D111">
         <v>7079978</v>
       </c>
       <c r="E111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F111">
         <v>5</v>
@@ -4114,16 +4117,16 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D112">
         <v>3367739</v>
       </c>
       <c r="E112" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F112">
         <v>7</v>
@@ -4146,16 +4149,16 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D113">
         <v>7072286</v>
       </c>
       <c r="E113" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -4178,16 +4181,16 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D114">
         <v>3367743</v>
       </c>
       <c r="E114" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F114">
         <v>2</v>
@@ -4210,16 +4213,16 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D115">
         <v>4214024</v>
       </c>
       <c r="E115" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -4242,16 +4245,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C116" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D116">
         <v>7357843</v>
       </c>
       <c r="E116" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F116">
         <v>22</v>
@@ -4274,16 +4277,16 @@
         <v>14</v>
       </c>
       <c r="B117" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D117">
         <v>7077448</v>
       </c>
       <c r="E117" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F117">
         <v>2</v>
@@ -4306,16 +4309,16 @@
         <v>14</v>
       </c>
       <c r="B118" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118">
         <v>2278099</v>
       </c>
       <c r="E118" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F118">
         <v>24</v>
@@ -4338,16 +4341,16 @@
         <v>14</v>
       </c>
       <c r="B119" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D119">
         <v>7077738</v>
       </c>
       <c r="E119" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F119">
         <v>6</v>
@@ -4370,16 +4373,16 @@
         <v>14</v>
       </c>
       <c r="B120" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D120">
         <v>4493936</v>
       </c>
       <c r="E120" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F120">
         <v>6</v>
@@ -4402,16 +4405,16 @@
         <v>14</v>
       </c>
       <c r="B121" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D121">
         <v>5284531</v>
       </c>
       <c r="E121" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -4434,16 +4437,16 @@
         <v>14</v>
       </c>
       <c r="B122" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C122" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D122">
         <v>5954007</v>
       </c>
       <c r="E122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F122">
         <v>47</v>
@@ -4466,16 +4469,16 @@
         <v>14</v>
       </c>
       <c r="B123" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>7081903</v>
       </c>
       <c r="E123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F123">
         <v>20</v>
@@ -4498,16 +4501,16 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D124">
         <v>9366541</v>
       </c>
       <c r="E124" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F124">
         <v>24</v>
@@ -4530,16 +4533,16 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D125">
         <v>6435172</v>
       </c>
       <c r="E125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F125">
         <v>6</v>
@@ -4562,16 +4565,16 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C126" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D126">
         <v>7077736</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F126">
         <v>3</v>
@@ -4594,16 +4597,16 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C127" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D127">
         <v>7381125</v>
       </c>
       <c r="E127" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F127">
         <v>44</v>
@@ -4626,16 +4629,16 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C128" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D128">
         <v>2207663</v>
       </c>
       <c r="E128" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F128">
         <v>23</v>
@@ -4658,16 +4661,16 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C129" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D129">
         <v>7397528</v>
       </c>
       <c r="E129" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F129">
         <v>26</v>
@@ -4690,16 +4693,16 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C130" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D130">
         <v>5931712</v>
       </c>
       <c r="E130" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F130">
         <v>39</v>
@@ -4722,16 +4725,16 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C131" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D131">
         <v>7325488</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F131">
         <v>38</v>
@@ -4754,16 +4757,16 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C132" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D132">
         <v>3368175</v>
       </c>
       <c r="E132" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F132">
         <v>47</v>
@@ -4786,16 +4789,16 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C133" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D133">
         <v>3864716</v>
       </c>
       <c r="E133" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F133">
         <v>72</v>
@@ -4818,16 +4821,16 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C134" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D134">
         <v>3367403</v>
       </c>
       <c r="E134" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F134">
         <v>16</v>
@@ -4850,16 +4853,16 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D135">
         <v>7381124</v>
       </c>
       <c r="E135" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F135">
         <v>47</v>
@@ -4882,16 +4885,16 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D136">
         <v>7079978</v>
       </c>
       <c r="E136" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -4914,16 +4917,16 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D137">
         <v>3367739</v>
       </c>
       <c r="E137" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F137">
         <v>7</v>
@@ -4946,16 +4949,16 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C138" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D138">
         <v>7072286</v>
       </c>
       <c r="E138" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -4978,16 +4981,16 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C139" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D139">
         <v>3367743</v>
       </c>
       <c r="E139" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -5010,16 +5013,16 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C140" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D140">
         <v>4214024</v>
       </c>
       <c r="E140" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F140">
         <v>6</v>
@@ -5042,16 +5045,16 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D141">
         <v>7357843</v>
       </c>
       <c r="E141" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F141">
         <v>25</v>
@@ -5074,16 +5077,16 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C142" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D142">
         <v>7077448</v>
       </c>
       <c r="E142" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F142">
         <v>3</v>
@@ -5106,16 +5109,16 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D143">
         <v>2278099</v>
       </c>
       <c r="E143" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F143">
         <v>33</v>
@@ -5138,16 +5141,16 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D144">
         <v>7077738</v>
       </c>
       <c r="E144" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F144">
         <v>9</v>
@@ -5170,16 +5173,16 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D145">
         <v>4493936</v>
       </c>
       <c r="E145" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F145">
         <v>8</v>
@@ -5202,16 +5205,16 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C146" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D146">
         <v>5284531</v>
       </c>
       <c r="E146" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -5234,16 +5237,16 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>5954007</v>
       </c>
       <c r="E147" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F147">
         <v>78</v>
@@ -5266,16 +5269,16 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C148" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D148">
         <v>7081903</v>
       </c>
       <c r="E148" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F148">
         <v>29</v>
@@ -5298,16 +5301,16 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C149" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D149">
         <v>9366541</v>
       </c>
       <c r="E149" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F149">
         <v>18</v>
@@ -5330,16 +5333,16 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C150" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D150">
         <v>6435172</v>
       </c>
       <c r="E150" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F150">
         <v>20</v>
@@ -5362,16 +5365,16 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C151" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D151">
         <v>7077736</v>
       </c>
       <c r="E151" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F151">
         <v>4</v>
@@ -5394,16 +5397,16 @@
         <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C152" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D152">
         <v>7381125</v>
       </c>
       <c r="E152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F152">
         <v>76</v>
@@ -5426,16 +5429,16 @@
         <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C153" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D153">
         <v>2207663</v>
       </c>
       <c r="E153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F153">
         <v>30</v>
@@ -5458,16 +5461,16 @@
         <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C154" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D154">
         <v>7397528</v>
       </c>
       <c r="E154" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F154">
         <v>49</v>
@@ -5490,16 +5493,16 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C155" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D155">
         <v>5931712</v>
       </c>
       <c r="E155" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F155">
         <v>59</v>
@@ -5522,16 +5525,16 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C156" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D156">
         <v>7325488</v>
       </c>
       <c r="E156" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F156">
         <v>91</v>
@@ -5554,16 +5557,16 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C157" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D157">
         <v>3368175</v>
       </c>
       <c r="E157" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F157">
         <v>66</v>
@@ -5586,16 +5589,16 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C158" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D158">
         <v>3864716</v>
       </c>
       <c r="E158" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F158">
         <v>100</v>
@@ -5618,16 +5621,16 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C159" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D159">
         <v>3367403</v>
       </c>
       <c r="E159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F159">
         <v>23</v>
@@ -5650,16 +5653,16 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C160" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D160">
         <v>7381124</v>
       </c>
       <c r="E160" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F160">
         <v>60</v>
@@ -5682,16 +5685,16 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D161">
         <v>7079978</v>
       </c>
       <c r="E161" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F161">
         <v>14</v>
@@ -5714,16 +5717,16 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C162" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D162">
         <v>3367739</v>
       </c>
       <c r="E162" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F162">
         <v>9</v>
@@ -5746,16 +5749,16 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C163" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D163">
         <v>7072286</v>
       </c>
       <c r="E163" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -5778,16 +5781,16 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C164" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D164">
         <v>3367743</v>
       </c>
       <c r="E164" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F164">
         <v>5</v>
@@ -5810,16 +5813,16 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C165" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D165">
         <v>4214024</v>
       </c>
       <c r="E165" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F165">
         <v>13</v>
@@ -5842,16 +5845,16 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C166" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D166">
         <v>7357843</v>
       </c>
       <c r="E166" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F166">
         <v>31</v>
@@ -5874,16 +5877,16 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C167" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D167">
         <v>7077448</v>
       </c>
       <c r="E167" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F167">
         <v>5</v>
@@ -5906,16 +5909,16 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C168" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D168">
         <v>2278099</v>
       </c>
       <c r="E168" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F168">
         <v>39</v>
@@ -5938,16 +5941,16 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C169" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D169">
         <v>7077738</v>
       </c>
       <c r="E169" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F169">
         <v>9</v>
@@ -5970,16 +5973,16 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C170" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D170">
         <v>4493936</v>
       </c>
       <c r="E170" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F170">
         <v>12</v>
@@ -6002,16 +6005,16 @@
         <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C171" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D171">
         <v>5284531</v>
       </c>
       <c r="E171" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F171">
         <v>12</v>
@@ -6034,16 +6037,16 @@
         <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C172" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D172">
         <v>5954007</v>
       </c>
       <c r="E172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F172">
         <v>105</v>
@@ -6066,16 +6069,16 @@
         <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C173" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D173">
         <v>7081903</v>
       </c>
       <c r="E173" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F173">
         <v>39</v>
@@ -6098,16 +6101,16 @@
         <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C174" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D174">
         <v>9366541</v>
       </c>
       <c r="E174" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F174">
         <v>35</v>
@@ -6130,16 +6133,16 @@
         <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C175" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D175">
         <v>6435172</v>
       </c>
       <c r="E175" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F175">
         <v>30</v>
@@ -6162,16 +6165,16 @@
         <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C176" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D176">
         <v>7077736</v>
       </c>
       <c r="E176" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F176">
         <v>6</v>
@@ -6194,16 +6197,16 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D177">
         <v>7381125</v>
       </c>
       <c r="E177" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F177">
         <v>55</v>
@@ -6226,16 +6229,16 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C178" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D178">
         <v>2207663</v>
       </c>
       <c r="E178" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F178">
         <v>21</v>
@@ -6258,16 +6261,16 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C179" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D179">
         <v>7397528</v>
       </c>
       <c r="E179" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F179">
         <v>32</v>
@@ -6290,16 +6293,16 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C180" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D180">
         <v>5931712</v>
       </c>
       <c r="E180" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F180">
         <v>42</v>
@@ -6322,16 +6325,16 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C181" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D181">
         <v>7325488</v>
       </c>
       <c r="E181" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -6354,16 +6357,16 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C182" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D182">
         <v>3368175</v>
       </c>
       <c r="E182" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F182">
         <v>35</v>
@@ -6386,16 +6389,16 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C183" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D183">
         <v>3864716</v>
       </c>
       <c r="E183" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F183">
         <v>72</v>
@@ -6418,16 +6421,16 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C184" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D184">
         <v>3367403</v>
       </c>
       <c r="E184" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F184">
         <v>9</v>
@@ -6450,16 +6453,16 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C185" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D185">
         <v>7381124</v>
       </c>
       <c r="E185" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F185">
         <v>42</v>
@@ -6482,16 +6485,16 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C186" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D186">
         <v>7079978</v>
       </c>
       <c r="E186" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F186">
         <v>10</v>
@@ -6514,16 +6517,16 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C187" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D187">
         <v>3367739</v>
       </c>
       <c r="E187" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F187">
         <v>6</v>
@@ -6546,16 +6549,16 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C188" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D188">
         <v>7072286</v>
       </c>
       <c r="E188" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -6578,16 +6581,16 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C189" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D189">
         <v>3367743</v>
       </c>
       <c r="E189" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F189">
         <v>3</v>
@@ -6610,16 +6613,16 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C190" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D190">
         <v>4214024</v>
       </c>
       <c r="E190" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F190">
         <v>5</v>
@@ -6642,16 +6645,16 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D191">
         <v>7357843</v>
       </c>
       <c r="E191" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F191">
         <v>25</v>
@@ -6674,16 +6677,16 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C192" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D192">
         <v>7077448</v>
       </c>
       <c r="E192" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F192">
         <v>2</v>
@@ -6706,16 +6709,16 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C193" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D193">
         <v>2278099</v>
       </c>
       <c r="E193" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F193">
         <v>29</v>
@@ -6738,16 +6741,16 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C194" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D194">
         <v>7077738</v>
       </c>
       <c r="E194" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F194">
         <v>4</v>
@@ -6770,16 +6773,16 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C195" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D195">
         <v>4493936</v>
       </c>
       <c r="E195" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F195">
         <v>9</v>
@@ -6802,16 +6805,16 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C196" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D196">
         <v>5284531</v>
       </c>
       <c r="E196" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F196">
         <v>8</v>
@@ -6834,16 +6837,16 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C197" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D197">
         <v>5954007</v>
       </c>
       <c r="E197" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F197">
         <v>76</v>
@@ -6866,16 +6869,16 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C198" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D198">
         <v>7081903</v>
       </c>
       <c r="E198" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F198">
         <v>38</v>
@@ -6898,16 +6901,16 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C199" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D199">
         <v>9366541</v>
       </c>
       <c r="E199" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F199">
         <v>29</v>
@@ -6930,16 +6933,16 @@
         <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C200" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D200">
         <v>6435172</v>
       </c>
       <c r="E200" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -6962,16 +6965,16 @@
         <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C201" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D201">
         <v>7077736</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F201">
         <v>4</v>
@@ -6994,16 +6997,16 @@
         <v>18</v>
       </c>
       <c r="B202" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C202" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D202">
         <v>7381125</v>
       </c>
       <c r="E202" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F202">
         <v>50</v>
@@ -7026,16 +7029,16 @@
         <v>18</v>
       </c>
       <c r="B203" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C203" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D203">
         <v>2207663</v>
       </c>
       <c r="E203" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F203">
         <v>15</v>
@@ -7058,16 +7061,16 @@
         <v>18</v>
       </c>
       <c r="B204" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C204" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D204">
         <v>7397528</v>
       </c>
       <c r="E204" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F204">
         <v>39</v>
@@ -7090,16 +7093,16 @@
         <v>18</v>
       </c>
       <c r="B205" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C205" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D205">
         <v>5931712</v>
       </c>
       <c r="E205" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F205">
         <v>49</v>
@@ -7122,16 +7125,16 @@
         <v>18</v>
       </c>
       <c r="B206" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C206" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D206">
         <v>7325488</v>
       </c>
       <c r="E206" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F206">
         <v>84</v>
@@ -7154,16 +7157,16 @@
         <v>18</v>
       </c>
       <c r="B207" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C207" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D207">
         <v>3368175</v>
       </c>
       <c r="E207" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F207">
         <v>51</v>
@@ -7186,16 +7189,16 @@
         <v>18</v>
       </c>
       <c r="B208" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C208" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D208">
         <v>3864716</v>
       </c>
       <c r="E208" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F208">
         <v>99</v>
@@ -7218,16 +7221,16 @@
         <v>18</v>
       </c>
       <c r="B209" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C209" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D209">
         <v>3367403</v>
       </c>
       <c r="E209" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F209">
         <v>12</v>
@@ -7250,16 +7253,16 @@
         <v>18</v>
       </c>
       <c r="B210" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C210" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D210">
         <v>7381124</v>
       </c>
       <c r="E210" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F210">
         <v>65</v>
@@ -7282,16 +7285,16 @@
         <v>18</v>
       </c>
       <c r="B211" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C211" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D211">
         <v>7079978</v>
       </c>
       <c r="E211" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F211">
         <v>7</v>
@@ -7314,16 +7317,16 @@
         <v>18</v>
       </c>
       <c r="B212" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C212" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D212">
         <v>3367739</v>
       </c>
       <c r="E212" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F212">
         <v>7</v>
@@ -7346,16 +7349,16 @@
         <v>18</v>
       </c>
       <c r="B213" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C213" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D213">
         <v>7072286</v>
       </c>
       <c r="E213" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F213">
         <v>3</v>
@@ -7378,16 +7381,16 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D214">
         <v>3367743</v>
       </c>
       <c r="E214" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -7410,16 +7413,16 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C215" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D215">
         <v>4214024</v>
       </c>
       <c r="E215" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F215">
         <v>7</v>
@@ -7442,16 +7445,16 @@
         <v>18</v>
       </c>
       <c r="B216" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D216">
         <v>7357843</v>
       </c>
       <c r="E216" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F216">
         <v>24</v>
@@ -7474,16 +7477,16 @@
         <v>18</v>
       </c>
       <c r="B217" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C217" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D217">
         <v>7077448</v>
       </c>
       <c r="E217" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F217">
         <v>2</v>
@@ -7506,16 +7509,16 @@
         <v>18</v>
       </c>
       <c r="B218" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C218" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D218">
         <v>2278099</v>
       </c>
       <c r="E218" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F218">
         <v>27</v>
@@ -7538,16 +7541,16 @@
         <v>18</v>
       </c>
       <c r="B219" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C219" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D219">
         <v>7077738</v>
       </c>
       <c r="E219" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F219">
         <v>7</v>
@@ -7570,16 +7573,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C220" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D220">
         <v>4493936</v>
       </c>
       <c r="E220" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F220">
         <v>14</v>
@@ -7602,16 +7605,16 @@
         <v>18</v>
       </c>
       <c r="B221" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C221" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D221">
         <v>5284531</v>
       </c>
       <c r="E221" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F221">
         <v>4</v>
@@ -7634,16 +7637,16 @@
         <v>18</v>
       </c>
       <c r="B222" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C222" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D222">
         <v>5954007</v>
       </c>
       <c r="E222" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F222">
         <v>94</v>
@@ -7666,16 +7669,16 @@
         <v>18</v>
       </c>
       <c r="B223" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C223" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D223">
         <v>7081903</v>
       </c>
       <c r="E223" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F223">
         <v>53</v>
@@ -7698,16 +7701,16 @@
         <v>18</v>
       </c>
       <c r="B224" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C224" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D224">
         <v>9366541</v>
       </c>
       <c r="E224" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F224">
         <v>30</v>
@@ -7730,16 +7733,16 @@
         <v>18</v>
       </c>
       <c r="B225" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C225" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D225">
         <v>6435172</v>
       </c>
       <c r="E225" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -7762,16 +7765,16 @@
         <v>18</v>
       </c>
       <c r="B226" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C226" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D226">
         <v>7077736</v>
       </c>
       <c r="E226" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F226">
         <v>7</v>
@@ -7794,16 +7797,16 @@
         <v>19</v>
       </c>
       <c r="B227" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C227" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D227">
         <v>7381125</v>
       </c>
       <c r="E227" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F227">
         <v>46</v>
@@ -7826,16 +7829,16 @@
         <v>19</v>
       </c>
       <c r="B228" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C228" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D228">
         <v>2207663</v>
       </c>
       <c r="E228" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F228">
         <v>20</v>
@@ -7858,16 +7861,16 @@
         <v>19</v>
       </c>
       <c r="B229" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C229" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D229">
         <v>7397528</v>
       </c>
       <c r="E229" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F229">
         <v>31</v>
@@ -7890,16 +7893,16 @@
         <v>19</v>
       </c>
       <c r="B230" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C230" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D230">
         <v>5931712</v>
       </c>
       <c r="E230" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F230">
         <v>48</v>
@@ -7922,16 +7925,16 @@
         <v>19</v>
       </c>
       <c r="B231" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C231" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D231">
         <v>7325488</v>
       </c>
       <c r="E231" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F231">
         <v>88</v>
@@ -7954,16 +7957,16 @@
         <v>19</v>
       </c>
       <c r="B232" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C232" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D232">
         <v>3368175</v>
       </c>
       <c r="E232" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F232">
         <v>44</v>
@@ -7986,16 +7989,16 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C233" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D233">
         <v>3864716</v>
       </c>
       <c r="E233" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F233">
         <v>104</v>
@@ -8018,16 +8021,16 @@
         <v>19</v>
       </c>
       <c r="B234" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C234" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D234">
         <v>3367403</v>
       </c>
       <c r="E234" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F234">
         <v>13</v>
@@ -8050,16 +8053,16 @@
         <v>19</v>
       </c>
       <c r="B235" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C235" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D235">
         <v>7381124</v>
       </c>
       <c r="E235" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F235">
         <v>65</v>
@@ -8082,16 +8085,16 @@
         <v>19</v>
       </c>
       <c r="B236" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C236" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D236">
         <v>7079978</v>
       </c>
       <c r="E236" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -8114,16 +8117,16 @@
         <v>19</v>
       </c>
       <c r="B237" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C237" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D237">
         <v>3367739</v>
       </c>
       <c r="E237" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F237">
         <v>12</v>
@@ -8146,16 +8149,16 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C238" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D238">
         <v>7072286</v>
       </c>
       <c r="E238" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -8178,16 +8181,16 @@
         <v>19</v>
       </c>
       <c r="B239" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C239" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D239">
         <v>3367743</v>
       </c>
       <c r="E239" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -8210,16 +8213,16 @@
         <v>19</v>
       </c>
       <c r="B240" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C240" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D240">
         <v>4214024</v>
       </c>
       <c r="E240" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F240">
         <v>6</v>
@@ -8242,16 +8245,16 @@
         <v>19</v>
       </c>
       <c r="B241" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C241" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D241">
         <v>7357843</v>
       </c>
       <c r="E241" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F241">
         <v>41</v>
@@ -8274,16 +8277,16 @@
         <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C242" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D242">
         <v>7077448</v>
       </c>
       <c r="E242" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F242">
         <v>3</v>
@@ -8306,16 +8309,16 @@
         <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C243" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D243">
         <v>2278099</v>
       </c>
       <c r="E243" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F243">
         <v>30</v>
@@ -8338,16 +8341,16 @@
         <v>19</v>
       </c>
       <c r="B244" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C244" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D244">
         <v>7077738</v>
       </c>
       <c r="E244" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F244">
         <v>9</v>
@@ -8370,16 +8373,16 @@
         <v>19</v>
       </c>
       <c r="B245" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C245" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D245">
         <v>4493936</v>
       </c>
       <c r="E245" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -8402,16 +8405,16 @@
         <v>19</v>
       </c>
       <c r="B246" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C246" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D246">
         <v>5284531</v>
       </c>
       <c r="E246" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -8434,16 +8437,16 @@
         <v>19</v>
       </c>
       <c r="B247" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C247" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D247">
         <v>5954007</v>
       </c>
       <c r="E247" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F247">
         <v>108</v>
@@ -8466,16 +8469,16 @@
         <v>19</v>
       </c>
       <c r="B248" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C248" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D248">
         <v>7081903</v>
       </c>
       <c r="E248" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F248">
         <v>57</v>
@@ -8498,16 +8501,16 @@
         <v>19</v>
       </c>
       <c r="B249" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C249" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D249">
         <v>9366541</v>
       </c>
       <c r="E249" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F249">
         <v>38</v>
@@ -8530,16 +8533,16 @@
         <v>19</v>
       </c>
       <c r="B250" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C250" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D250">
         <v>6435172</v>
       </c>
       <c r="E250" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F250">
         <v>19</v>
@@ -8562,16 +8565,16 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C251" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D251">
         <v>7077736</v>
       </c>
       <c r="E251" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F251">
         <v>7</v>
@@ -8594,16 +8597,16 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C252" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D252">
         <v>7381125</v>
       </c>
       <c r="E252" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F252">
         <v>40</v>
@@ -8626,16 +8629,16 @@
         <v>20</v>
       </c>
       <c r="B253" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C253" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D253">
         <v>2207663</v>
       </c>
       <c r="E253" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F253">
         <v>22</v>
@@ -8658,16 +8661,16 @@
         <v>20</v>
       </c>
       <c r="B254" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C254" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D254">
         <v>7397528</v>
       </c>
       <c r="E254" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F254">
         <v>36</v>
@@ -8690,16 +8693,16 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C255" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D255">
         <v>5931712</v>
       </c>
       <c r="E255" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F255">
         <v>44</v>
@@ -8722,16 +8725,16 @@
         <v>20</v>
       </c>
       <c r="B256" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C256" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D256">
         <v>7325488</v>
       </c>
       <c r="E256" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F256">
         <v>92</v>
@@ -8754,16 +8757,16 @@
         <v>20</v>
       </c>
       <c r="B257" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D257">
         <v>3368175</v>
       </c>
       <c r="E257" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F257">
         <v>37</v>
@@ -8786,16 +8789,16 @@
         <v>20</v>
       </c>
       <c r="B258" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C258" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D258">
         <v>3864716</v>
       </c>
       <c r="E258" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F258">
         <v>75</v>
@@ -8818,16 +8821,16 @@
         <v>20</v>
       </c>
       <c r="B259" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C259" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D259">
         <v>3367403</v>
       </c>
       <c r="E259" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F259">
         <v>8</v>
@@ -8850,16 +8853,16 @@
         <v>20</v>
       </c>
       <c r="B260" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C260" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D260">
         <v>7381124</v>
       </c>
       <c r="E260" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F260">
         <v>62</v>
@@ -8882,16 +8885,16 @@
         <v>20</v>
       </c>
       <c r="B261" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C261" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D261">
         <v>7079978</v>
       </c>
       <c r="E261" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -8914,16 +8917,16 @@
         <v>20</v>
       </c>
       <c r="B262" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C262" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D262">
         <v>3367739</v>
       </c>
       <c r="E262" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F262">
         <v>9</v>
@@ -8946,16 +8949,16 @@
         <v>20</v>
       </c>
       <c r="B263" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C263" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D263">
         <v>7072286</v>
       </c>
       <c r="E263" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -8978,16 +8981,16 @@
         <v>20</v>
       </c>
       <c r="B264" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C264" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D264">
         <v>3367743</v>
       </c>
       <c r="E264" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F264">
         <v>3</v>
@@ -9010,16 +9013,16 @@
         <v>20</v>
       </c>
       <c r="B265" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C265" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D265">
         <v>4214024</v>
       </c>
       <c r="E265" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F265">
         <v>4</v>
@@ -9042,16 +9045,16 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C266" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D266">
         <v>7357843</v>
       </c>
       <c r="E266" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F266">
         <v>46</v>
@@ -9074,16 +9077,16 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C267" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D267">
         <v>7077448</v>
       </c>
       <c r="E267" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F267">
         <v>3</v>
@@ -9106,16 +9109,16 @@
         <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C268" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D268">
         <v>2278099</v>
       </c>
       <c r="E268" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F268">
         <v>38</v>
@@ -9138,16 +9141,16 @@
         <v>20</v>
       </c>
       <c r="B269" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C269" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D269">
         <v>7077738</v>
       </c>
       <c r="E269" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F269">
         <v>14</v>
@@ -9170,16 +9173,16 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C270" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D270">
         <v>4493936</v>
       </c>
       <c r="E270" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F270">
         <v>17</v>
@@ -9202,16 +9205,16 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C271" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D271">
         <v>5284531</v>
       </c>
       <c r="E271" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F271">
         <v>7</v>
@@ -9234,16 +9237,16 @@
         <v>20</v>
       </c>
       <c r="B272" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C272" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D272">
         <v>5954007</v>
       </c>
       <c r="E272" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F272">
         <v>116</v>
@@ -9266,16 +9269,16 @@
         <v>20</v>
       </c>
       <c r="B273" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C273" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D273">
         <v>7081903</v>
       </c>
       <c r="E273" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F273">
         <v>58</v>
@@ -9298,16 +9301,16 @@
         <v>20</v>
       </c>
       <c r="B274" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C274" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D274">
         <v>9366541</v>
       </c>
       <c r="E274" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F274">
         <v>43</v>
@@ -9330,16 +9333,16 @@
         <v>20</v>
       </c>
       <c r="B275" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C275" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D275">
         <v>6435172</v>
       </c>
       <c r="E275" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F275">
         <v>12</v>
@@ -9362,16 +9365,16 @@
         <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C276" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D276">
         <v>7077736</v>
       </c>
       <c r="E276" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F276">
         <v>5</v>
@@ -9394,16 +9397,16 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C277" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D277">
         <v>7381125</v>
       </c>
       <c r="E277" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F277">
         <v>45</v>
@@ -9426,16 +9429,16 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C278" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D278">
         <v>2207663</v>
       </c>
       <c r="E278" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F278">
         <v>20</v>
@@ -9458,16 +9461,16 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C279" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D279">
         <v>7397528</v>
       </c>
       <c r="E279" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F279">
         <v>38</v>
@@ -9490,16 +9493,16 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C280" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D280">
         <v>5931712</v>
       </c>
       <c r="E280" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F280">
         <v>43</v>
@@ -9522,16 +9525,16 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C281" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D281">
         <v>7325488</v>
       </c>
       <c r="E281" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F281">
         <v>90</v>
@@ -9554,16 +9557,16 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C282" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D282">
         <v>3368175</v>
       </c>
       <c r="E282" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F282">
         <v>34</v>
@@ -9586,16 +9589,16 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C283" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D283">
         <v>3864716</v>
       </c>
       <c r="E283" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F283">
         <v>103</v>
@@ -9618,16 +9621,16 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C284" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D284">
         <v>3367403</v>
       </c>
       <c r="E284" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -9650,16 +9653,16 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C285" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D285">
         <v>7381124</v>
       </c>
       <c r="E285" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F285">
         <v>69</v>
@@ -9682,16 +9685,16 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C286" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D286">
         <v>7079978</v>
       </c>
       <c r="E286" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F286">
         <v>9</v>
@@ -9714,16 +9717,16 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C287" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D287">
         <v>3367739</v>
       </c>
       <c r="E287" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F287">
         <v>16</v>
@@ -9746,16 +9749,16 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C288" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D288">
         <v>7072286</v>
       </c>
       <c r="E288" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F288">
         <v>2</v>
@@ -9778,16 +9781,16 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C289" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D289">
         <v>3367743</v>
       </c>
       <c r="E289" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F289">
         <v>2</v>
@@ -9810,16 +9813,16 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C290" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D290">
         <v>4214024</v>
       </c>
       <c r="E290" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F290">
         <v>3</v>
@@ -9842,16 +9845,16 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C291" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D291">
         <v>7357843</v>
       </c>
       <c r="E291" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F291">
         <v>51</v>
@@ -9874,16 +9877,16 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C292" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D292">
         <v>7077448</v>
       </c>
       <c r="E292" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F292">
         <v>3</v>
@@ -9906,16 +9909,16 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C293" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D293">
         <v>2278099</v>
       </c>
       <c r="E293" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F293">
         <v>44</v>
@@ -9938,16 +9941,16 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C294" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D294">
         <v>7077738</v>
       </c>
       <c r="E294" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F294">
         <v>11</v>
@@ -9970,16 +9973,16 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C295" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D295">
         <v>4493936</v>
       </c>
       <c r="E295" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F295">
         <v>20</v>
@@ -10002,16 +10005,16 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C296" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D296">
         <v>5284531</v>
       </c>
       <c r="E296" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F296">
         <v>9</v>
@@ -10034,16 +10037,16 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C297" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D297">
         <v>5954007</v>
       </c>
       <c r="E297" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F297">
         <v>117</v>
@@ -10066,16 +10069,16 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C298" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D298">
         <v>7081903</v>
       </c>
       <c r="E298" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F298">
         <v>59</v>
@@ -10098,16 +10101,16 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C299" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D299">
         <v>9366541</v>
       </c>
       <c r="E299" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F299">
         <v>40</v>
@@ -10130,16 +10133,16 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C300" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D300">
         <v>6435172</v>
       </c>
       <c r="E300" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F300">
         <v>10</v>
@@ -10162,16 +10165,16 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C301" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D301">
         <v>7077736</v>
       </c>
       <c r="E301" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F301">
         <v>9</v>
@@ -10194,16 +10197,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C302" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D302">
         <v>7381125</v>
       </c>
       <c r="E302" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F302">
         <v>44</v>
@@ -10226,16 +10229,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C303" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D303">
         <v>2207663</v>
       </c>
       <c r="E303" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F303">
         <v>20</v>
@@ -10258,16 +10261,16 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C304" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D304">
         <v>7397528</v>
       </c>
       <c r="E304" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F304">
         <v>28</v>
@@ -10290,16 +10293,16 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C305" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D305">
         <v>5931712</v>
       </c>
       <c r="E305" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F305">
         <v>24</v>
@@ -10322,16 +10325,16 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C306" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D306">
         <v>7325488</v>
       </c>
       <c r="E306" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F306">
         <v>83</v>
@@ -10354,16 +10357,16 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C307" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D307">
         <v>3368175</v>
       </c>
       <c r="E307" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F307">
         <v>43</v>
@@ -10386,16 +10389,16 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C308" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D308">
         <v>3864716</v>
       </c>
       <c r="E308" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F308">
         <v>89</v>
@@ -10418,16 +10421,16 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C309" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D309">
         <v>3367403</v>
       </c>
       <c r="E309" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F309">
         <v>13</v>
@@ -10450,16 +10453,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C310" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D310">
         <v>7381124</v>
       </c>
       <c r="E310" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F310">
         <v>43</v>
@@ -10482,16 +10485,16 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C311" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D311">
         <v>7079978</v>
       </c>
       <c r="E311" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F311">
         <v>10</v>
@@ -10514,16 +10517,16 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C312" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D312">
         <v>3367739</v>
       </c>
       <c r="E312" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F312">
         <v>7</v>
@@ -10546,16 +10549,16 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C313" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D313">
         <v>7072286</v>
       </c>
       <c r="E313" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F313">
         <v>3</v>
@@ -10578,16 +10581,16 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C314" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D314">
         <v>3367743</v>
       </c>
       <c r="E314" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -10610,16 +10613,16 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C315" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D315">
         <v>4214024</v>
       </c>
       <c r="E315" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -10642,16 +10645,16 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C316" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D316">
         <v>7357843</v>
       </c>
       <c r="E316" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F316">
         <v>62</v>
@@ -10674,16 +10677,16 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C317" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D317">
         <v>7077448</v>
       </c>
       <c r="E317" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F317">
         <v>3</v>
@@ -10706,16 +10709,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C318" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D318">
         <v>2278099</v>
       </c>
       <c r="E318" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F318">
         <v>40</v>
@@ -10738,16 +10741,16 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C319" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D319">
         <v>7077738</v>
       </c>
       <c r="E319" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F319">
         <v>8</v>
@@ -10770,16 +10773,16 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C320" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D320">
         <v>4493936</v>
       </c>
       <c r="E320" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F320">
         <v>14</v>
@@ -10802,16 +10805,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C321" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D321">
         <v>5284531</v>
       </c>
       <c r="E321" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F321">
         <v>7</v>
@@ -10834,16 +10837,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C322" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D322">
         <v>5954007</v>
       </c>
       <c r="E322" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F322">
         <v>132</v>
@@ -10866,16 +10869,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C323" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D323">
         <v>7081903</v>
       </c>
       <c r="E323" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F323">
         <v>43</v>
@@ -10898,16 +10901,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C324" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D324">
         <v>9366541</v>
       </c>
       <c r="E324" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F324">
         <v>48</v>
@@ -10930,16 +10933,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C325" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D325">
         <v>6435172</v>
       </c>
       <c r="E325" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F325">
         <v>17</v>
@@ -10962,16 +10965,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C326" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D326">
         <v>7077736</v>
       </c>
       <c r="E326" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F326">
         <v>8</v>
@@ -10994,16 +10997,16 @@
         <v>23</v>
       </c>
       <c r="B327" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C327" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D327">
         <v>7381125</v>
       </c>
       <c r="E327" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327">
         <v>56</v>
@@ -11026,16 +11029,16 @@
         <v>23</v>
       </c>
       <c r="B328" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C328" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D328">
         <v>2207663</v>
       </c>
       <c r="E328" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F328">
         <v>26</v>
@@ -11058,16 +11061,16 @@
         <v>23</v>
       </c>
       <c r="B329" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C329" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D329">
         <v>7397528</v>
       </c>
       <c r="E329" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F329">
         <v>40</v>
@@ -11090,16 +11093,16 @@
         <v>23</v>
       </c>
       <c r="B330" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C330" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D330">
         <v>5931712</v>
       </c>
       <c r="E330" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F330">
         <v>34</v>
@@ -11122,16 +11125,16 @@
         <v>23</v>
       </c>
       <c r="B331" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C331" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D331">
         <v>7325488</v>
       </c>
       <c r="E331" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F331">
         <v>99</v>
@@ -11154,16 +11157,16 @@
         <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C332" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D332">
         <v>3368175</v>
       </c>
       <c r="E332" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F332">
         <v>51</v>
@@ -11186,16 +11189,16 @@
         <v>23</v>
       </c>
       <c r="B333" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C333" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D333">
         <v>3864716</v>
       </c>
       <c r="E333" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F333">
         <v>104</v>
@@ -11218,16 +11221,16 @@
         <v>23</v>
       </c>
       <c r="B334" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C334" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D334">
         <v>3367403</v>
       </c>
       <c r="E334" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F334">
         <v>14</v>
@@ -11250,16 +11253,16 @@
         <v>23</v>
       </c>
       <c r="B335" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C335" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D335">
         <v>7381124</v>
       </c>
       <c r="E335" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F335">
         <v>49</v>
@@ -11282,16 +11285,16 @@
         <v>23</v>
       </c>
       <c r="B336" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C336" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D336">
         <v>7079978</v>
       </c>
       <c r="E336" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F336">
         <v>20</v>
@@ -11314,16 +11317,16 @@
         <v>23</v>
       </c>
       <c r="B337" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C337" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D337">
         <v>3367739</v>
       </c>
       <c r="E337" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F337">
         <v>8</v>
@@ -11346,16 +11349,16 @@
         <v>23</v>
       </c>
       <c r="B338" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C338" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D338">
         <v>7072286</v>
       </c>
       <c r="E338" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F338">
         <v>3</v>
@@ -11378,16 +11381,16 @@
         <v>23</v>
       </c>
       <c r="B339" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C339" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D339">
         <v>3367743</v>
       </c>
       <c r="E339" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F339">
         <v>8</v>
@@ -11410,16 +11413,16 @@
         <v>23</v>
       </c>
       <c r="B340" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C340" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D340">
         <v>4214024</v>
       </c>
       <c r="E340" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F340">
         <v>8</v>
@@ -11442,16 +11445,16 @@
         <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C341" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D341">
         <v>7357843</v>
       </c>
       <c r="E341" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F341">
         <v>68</v>
@@ -11474,16 +11477,16 @@
         <v>23</v>
       </c>
       <c r="B342" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C342" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D342">
         <v>7077448</v>
       </c>
       <c r="E342" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F342">
         <v>3</v>
@@ -11506,16 +11509,16 @@
         <v>23</v>
       </c>
       <c r="B343" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C343" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D343">
         <v>2278099</v>
       </c>
       <c r="E343" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F343">
         <v>48</v>
@@ -11538,16 +11541,16 @@
         <v>23</v>
       </c>
       <c r="B344" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C344" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D344">
         <v>7077738</v>
       </c>
       <c r="E344" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F344">
         <v>8</v>
@@ -11570,16 +11573,16 @@
         <v>23</v>
       </c>
       <c r="B345" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C345" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D345">
         <v>4493936</v>
       </c>
       <c r="E345" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F345">
         <v>14</v>
@@ -11602,16 +11605,16 @@
         <v>23</v>
       </c>
       <c r="B346" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C346" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D346">
         <v>5284531</v>
       </c>
       <c r="E346" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F346">
         <v>7</v>
@@ -11634,16 +11637,16 @@
         <v>23</v>
       </c>
       <c r="B347" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C347" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D347">
         <v>5954007</v>
       </c>
       <c r="E347" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F347">
         <v>123</v>
@@ -11666,16 +11669,16 @@
         <v>23</v>
       </c>
       <c r="B348" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C348" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D348">
         <v>7081903</v>
       </c>
       <c r="E348" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F348">
         <v>50</v>
@@ -11698,16 +11701,16 @@
         <v>23</v>
       </c>
       <c r="B349" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C349" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D349">
         <v>9366541</v>
       </c>
       <c r="E349" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F349">
         <v>49</v>
@@ -11730,16 +11733,16 @@
         <v>23</v>
       </c>
       <c r="B350" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C350" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D350">
         <v>6435172</v>
       </c>
       <c r="E350" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F350">
         <v>17</v>
@@ -11762,16 +11765,16 @@
         <v>23</v>
       </c>
       <c r="B351" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C351" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D351">
         <v>7077736</v>
       </c>
       <c r="E351" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F351">
         <v>8</v>
@@ -11794,16 +11797,16 @@
         <v>24</v>
       </c>
       <c r="B352" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C352" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D352">
         <v>7381125</v>
       </c>
       <c r="E352" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F352">
         <v>33</v>
@@ -11826,16 +11829,16 @@
         <v>24</v>
       </c>
       <c r="B353" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C353" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D353">
         <v>2207663</v>
       </c>
       <c r="E353" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F353">
         <v>21</v>
@@ -11858,16 +11861,16 @@
         <v>24</v>
       </c>
       <c r="B354" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C354" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D354">
         <v>7397528</v>
       </c>
       <c r="E354" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F354">
         <v>27</v>
@@ -11890,16 +11893,16 @@
         <v>24</v>
       </c>
       <c r="B355" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C355" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D355">
         <v>5931712</v>
       </c>
       <c r="E355" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F355">
         <v>23</v>
@@ -11922,16 +11925,16 @@
         <v>24</v>
       </c>
       <c r="B356" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C356" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D356">
         <v>7325488</v>
       </c>
       <c r="E356" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F356">
         <v>69</v>
@@ -11954,16 +11957,16 @@
         <v>24</v>
       </c>
       <c r="B357" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C357" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D357">
         <v>3368175</v>
       </c>
       <c r="E357" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F357">
         <v>21</v>
@@ -11986,16 +11989,16 @@
         <v>24</v>
       </c>
       <c r="B358" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C358" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D358">
         <v>3864716</v>
       </c>
       <c r="E358" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F358">
         <v>72</v>
@@ -12018,16 +12021,16 @@
         <v>24</v>
       </c>
       <c r="B359" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C359" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D359">
         <v>3367403</v>
       </c>
       <c r="E359" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F359">
         <v>6</v>
@@ -12050,16 +12053,16 @@
         <v>24</v>
       </c>
       <c r="B360" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C360" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D360">
         <v>7381124</v>
       </c>
       <c r="E360" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F360">
         <v>28</v>
@@ -12082,16 +12085,16 @@
         <v>24</v>
       </c>
       <c r="B361" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C361" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D361">
         <v>7079978</v>
       </c>
       <c r="E361" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F361">
         <v>10</v>
@@ -12114,16 +12117,16 @@
         <v>24</v>
       </c>
       <c r="B362" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C362" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D362">
         <v>3367739</v>
       </c>
       <c r="E362" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F362">
         <v>3</v>
@@ -12146,16 +12149,16 @@
         <v>24</v>
       </c>
       <c r="B363" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C363" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D363">
         <v>7072286</v>
       </c>
       <c r="E363" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F363">
         <v>3</v>
@@ -12178,16 +12181,16 @@
         <v>24</v>
       </c>
       <c r="B364" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C364" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D364">
         <v>3367743</v>
       </c>
       <c r="E364" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F364">
         <v>6</v>
@@ -12210,16 +12213,16 @@
         <v>24</v>
       </c>
       <c r="B365" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C365" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D365">
         <v>4214024</v>
       </c>
       <c r="E365" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F365">
         <v>4</v>
@@ -12242,16 +12245,16 @@
         <v>24</v>
       </c>
       <c r="B366" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C366" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D366">
         <v>7357843</v>
       </c>
       <c r="E366" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F366">
         <v>50</v>
@@ -12274,16 +12277,16 @@
         <v>24</v>
       </c>
       <c r="B367" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C367" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D367">
         <v>7077448</v>
       </c>
       <c r="E367" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F367">
         <v>2</v>
@@ -12306,16 +12309,16 @@
         <v>24</v>
       </c>
       <c r="B368" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C368" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D368">
         <v>2278099</v>
       </c>
       <c r="E368" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F368">
         <v>26</v>
@@ -12338,16 +12341,16 @@
         <v>24</v>
       </c>
       <c r="B369" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C369" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D369">
         <v>7077738</v>
       </c>
       <c r="E369" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F369">
         <v>6</v>
@@ -12370,16 +12373,16 @@
         <v>24</v>
       </c>
       <c r="B370" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C370" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D370">
         <v>4493936</v>
       </c>
       <c r="E370" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F370">
         <v>10</v>
@@ -12402,16 +12405,16 @@
         <v>24</v>
       </c>
       <c r="B371" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C371" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D371">
         <v>5284531</v>
       </c>
       <c r="E371" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F371">
         <v>3</v>
@@ -12434,16 +12437,16 @@
         <v>24</v>
       </c>
       <c r="B372" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C372" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D372">
         <v>5954007</v>
       </c>
       <c r="E372" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F372">
         <v>91</v>
@@ -12466,16 +12469,16 @@
         <v>24</v>
       </c>
       <c r="B373" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C373" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D373">
         <v>7081903</v>
       </c>
       <c r="E373" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F373">
         <v>35</v>
@@ -12498,16 +12501,16 @@
         <v>24</v>
       </c>
       <c r="B374" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C374" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D374">
         <v>9366541</v>
       </c>
       <c r="E374" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F374">
         <v>33</v>
@@ -12530,16 +12533,16 @@
         <v>24</v>
       </c>
       <c r="B375" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C375" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D375">
         <v>6435172</v>
       </c>
       <c r="E375" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F375">
         <v>10</v>
@@ -12562,16 +12565,16 @@
         <v>24</v>
       </c>
       <c r="B376" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C376" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D376">
         <v>7077736</v>
       </c>
       <c r="E376" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F376">
         <v>3</v>
@@ -12594,16 +12597,16 @@
         <v>25</v>
       </c>
       <c r="B377" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C377" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D377">
         <v>7381125</v>
       </c>
       <c r="E377" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F377">
         <v>32</v>
@@ -12626,16 +12629,16 @@
         <v>25</v>
       </c>
       <c r="B378" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C378" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D378">
         <v>2207663</v>
       </c>
       <c r="E378" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F378">
         <v>18</v>
@@ -12658,16 +12661,16 @@
         <v>25</v>
       </c>
       <c r="B379" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C379" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D379">
         <v>7397528</v>
       </c>
       <c r="E379" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F379">
         <v>28</v>
@@ -12690,16 +12693,16 @@
         <v>25</v>
       </c>
       <c r="B380" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C380" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D380">
         <v>5931712</v>
       </c>
       <c r="E380" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F380">
         <v>22</v>
@@ -12722,16 +12725,16 @@
         <v>25</v>
       </c>
       <c r="B381" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C381" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D381">
         <v>7325488</v>
       </c>
       <c r="E381" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F381">
         <v>62</v>
@@ -12754,16 +12757,16 @@
         <v>25</v>
       </c>
       <c r="B382" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C382" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D382">
         <v>3368175</v>
       </c>
       <c r="E382" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F382">
         <v>26</v>
@@ -12786,16 +12789,16 @@
         <v>25</v>
       </c>
       <c r="B383" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C383" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D383">
         <v>3864716</v>
       </c>
       <c r="E383" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F383">
         <v>44</v>
@@ -12818,16 +12821,16 @@
         <v>25</v>
       </c>
       <c r="B384" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C384" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D384">
         <v>3367403</v>
       </c>
       <c r="E384" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F384">
         <v>4</v>
@@ -12850,16 +12853,16 @@
         <v>25</v>
       </c>
       <c r="B385" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C385" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D385">
         <v>7381124</v>
       </c>
       <c r="E385" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F385">
         <v>27</v>
@@ -12882,16 +12885,16 @@
         <v>25</v>
       </c>
       <c r="B386" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C386" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D386">
         <v>7079978</v>
       </c>
       <c r="E386" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F386">
         <v>7</v>
@@ -12914,16 +12917,16 @@
         <v>25</v>
       </c>
       <c r="B387" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C387" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D387">
         <v>3367739</v>
       </c>
       <c r="E387" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F387">
         <v>2</v>
@@ -12946,16 +12949,16 @@
         <v>25</v>
       </c>
       <c r="B388" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C388" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D388">
         <v>7072286</v>
       </c>
       <c r="E388" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F388">
         <v>4</v>
@@ -12978,16 +12981,16 @@
         <v>25</v>
       </c>
       <c r="B389" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C389" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D389">
         <v>3367743</v>
       </c>
       <c r="E389" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F389">
         <v>6</v>
@@ -13010,16 +13013,16 @@
         <v>25</v>
       </c>
       <c r="B390" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C390" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D390">
         <v>4214024</v>
       </c>
       <c r="E390" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F390">
         <v>2</v>
@@ -13042,16 +13045,16 @@
         <v>25</v>
       </c>
       <c r="B391" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C391" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D391">
         <v>7357843</v>
       </c>
       <c r="E391" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F391">
         <v>46</v>
@@ -13074,16 +13077,16 @@
         <v>25</v>
       </c>
       <c r="B392" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C392" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D392">
         <v>7077448</v>
       </c>
       <c r="E392" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F392">
         <v>4</v>
@@ -13106,16 +13109,16 @@
         <v>25</v>
       </c>
       <c r="B393" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C393" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D393">
         <v>2278099</v>
       </c>
       <c r="E393" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F393">
         <v>33</v>
@@ -13138,16 +13141,16 @@
         <v>25</v>
       </c>
       <c r="B394" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C394" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D394">
         <v>7077738</v>
       </c>
       <c r="E394" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F394">
         <v>6</v>
@@ -13170,16 +13173,16 @@
         <v>25</v>
       </c>
       <c r="B395" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C395" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D395">
         <v>4493936</v>
       </c>
       <c r="E395" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F395">
         <v>8</v>
@@ -13202,16 +13205,16 @@
         <v>25</v>
       </c>
       <c r="B396" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C396" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D396">
         <v>5284531</v>
       </c>
       <c r="E396" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F396">
         <v>4</v>
@@ -13234,16 +13237,16 @@
         <v>25</v>
       </c>
       <c r="B397" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C397" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D397">
         <v>5954007</v>
       </c>
       <c r="E397" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F397">
         <v>75</v>
@@ -13266,16 +13269,16 @@
         <v>25</v>
       </c>
       <c r="B398" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C398" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D398">
         <v>7081903</v>
       </c>
       <c r="E398" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F398">
         <v>37</v>
@@ -13298,16 +13301,16 @@
         <v>25</v>
       </c>
       <c r="B399" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C399" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D399">
         <v>9366541</v>
       </c>
       <c r="E399" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F399">
         <v>34</v>
@@ -13330,16 +13333,16 @@
         <v>25</v>
       </c>
       <c r="B400" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C400" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D400">
         <v>6435172</v>
       </c>
       <c r="E400" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F400">
         <v>8</v>
@@ -13362,16 +13365,16 @@
         <v>25</v>
       </c>
       <c r="B401" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C401" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D401">
         <v>7077736</v>
       </c>
       <c r="E401" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F401">
         <v>6</v>
@@ -13394,16 +13397,16 @@
         <v>26</v>
       </c>
       <c r="B402" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C402" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D402">
         <v>7381125</v>
       </c>
       <c r="E402" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F402">
         <v>32</v>
@@ -13426,16 +13429,16 @@
         <v>26</v>
       </c>
       <c r="B403" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C403" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D403">
         <v>2207663</v>
       </c>
       <c r="E403" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F403">
         <v>15</v>
@@ -13458,16 +13461,16 @@
         <v>26</v>
       </c>
       <c r="B404" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C404" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D404">
         <v>7397528</v>
       </c>
       <c r="E404" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F404">
         <v>29</v>
@@ -13490,16 +13493,16 @@
         <v>26</v>
       </c>
       <c r="B405" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C405" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D405">
         <v>5931712</v>
       </c>
       <c r="E405" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F405">
         <v>15</v>
@@ -13522,16 +13525,16 @@
         <v>26</v>
       </c>
       <c r="B406" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C406" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D406">
         <v>7325488</v>
       </c>
       <c r="E406" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F406">
         <v>70</v>
@@ -13554,16 +13557,16 @@
         <v>26</v>
       </c>
       <c r="B407" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C407" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D407">
         <v>3368175</v>
       </c>
       <c r="E407" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F407">
         <v>28</v>
@@ -13586,16 +13589,16 @@
         <v>26</v>
       </c>
       <c r="B408" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C408" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D408">
         <v>3864716</v>
       </c>
       <c r="E408" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F408">
         <v>50</v>
@@ -13618,16 +13621,16 @@
         <v>26</v>
       </c>
       <c r="B409" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C409" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D409">
         <v>3367403</v>
       </c>
       <c r="E409" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F409">
         <v>4</v>
@@ -13650,16 +13653,16 @@
         <v>26</v>
       </c>
       <c r="B410" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C410" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D410">
         <v>7381124</v>
       </c>
       <c r="E410" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F410">
         <v>29</v>
@@ -13682,16 +13685,16 @@
         <v>26</v>
       </c>
       <c r="B411" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C411" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D411">
         <v>7079978</v>
       </c>
       <c r="E411" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F411">
         <v>10</v>
@@ -13714,16 +13717,16 @@
         <v>26</v>
       </c>
       <c r="B412" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C412" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D412">
         <v>3367739</v>
       </c>
       <c r="E412" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F412">
         <v>1</v>
@@ -13746,16 +13749,16 @@
         <v>26</v>
       </c>
       <c r="B413" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C413" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D413">
         <v>7072286</v>
       </c>
       <c r="E413" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F413">
         <v>3</v>
@@ -13778,16 +13781,16 @@
         <v>26</v>
       </c>
       <c r="B414" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C414" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D414">
         <v>3367743</v>
       </c>
       <c r="E414" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F414">
         <v>4</v>
@@ -13810,16 +13813,16 @@
         <v>26</v>
       </c>
       <c r="B415" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C415" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D415">
         <v>4214024</v>
       </c>
       <c r="E415" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F415">
         <v>6</v>
@@ -13842,16 +13845,16 @@
         <v>26</v>
       </c>
       <c r="B416" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C416" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D416">
         <v>7357843</v>
       </c>
       <c r="E416" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F416">
         <v>43</v>
@@ -13874,16 +13877,16 @@
         <v>26</v>
       </c>
       <c r="B417" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C417" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D417">
         <v>7077448</v>
       </c>
       <c r="E417" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F417">
         <v>8</v>
@@ -13906,16 +13909,16 @@
         <v>26</v>
       </c>
       <c r="B418" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C418" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D418">
         <v>2278099</v>
       </c>
       <c r="E418" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F418">
         <v>36</v>
@@ -13938,16 +13941,16 @@
         <v>26</v>
       </c>
       <c r="B419" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C419" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D419">
         <v>7077738</v>
       </c>
       <c r="E419" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F419">
         <v>6</v>
@@ -13970,16 +13973,16 @@
         <v>26</v>
       </c>
       <c r="B420" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C420" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D420">
         <v>4493936</v>
       </c>
       <c r="E420" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F420">
         <v>8</v>
@@ -14002,16 +14005,16 @@
         <v>26</v>
       </c>
       <c r="B421" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C421" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D421">
         <v>5284531</v>
       </c>
       <c r="E421" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F421">
         <v>5</v>
@@ -14034,16 +14037,16 @@
         <v>26</v>
       </c>
       <c r="B422" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C422" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D422">
         <v>5954007</v>
       </c>
       <c r="E422" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F422">
         <v>65</v>
@@ -14066,16 +14069,16 @@
         <v>26</v>
       </c>
       <c r="B423" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C423" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D423">
         <v>7081903</v>
       </c>
       <c r="E423" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F423">
         <v>30</v>
@@ -14098,16 +14101,16 @@
         <v>26</v>
       </c>
       <c r="B424" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C424" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D424">
         <v>9366541</v>
       </c>
       <c r="E424" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F424">
         <v>33</v>
@@ -14130,16 +14133,16 @@
         <v>26</v>
       </c>
       <c r="B425" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C425" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D425">
         <v>6435172</v>
       </c>
       <c r="E425" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F425">
         <v>9</v>
@@ -14162,16 +14165,16 @@
         <v>26</v>
       </c>
       <c r="B426" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C426" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D426">
         <v>7077736</v>
       </c>
       <c r="E426" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F426">
         <v>6</v>
@@ -14187,6 +14190,806 @@
       </c>
       <c r="J426">
         <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10">
+      <c r="A427" t="s">
+        <v>27</v>
+      </c>
+      <c r="B427" t="s">
+        <v>28</v>
+      </c>
+      <c r="C427" t="s">
+        <v>28</v>
+      </c>
+      <c r="D427">
+        <v>7381125</v>
+      </c>
+      <c r="E427" t="s">
+        <v>37</v>
+      </c>
+      <c r="F427">
+        <v>27</v>
+      </c>
+      <c r="G427">
+        <v>13</v>
+      </c>
+      <c r="H427">
+        <v>7</v>
+      </c>
+      <c r="I427">
+        <v>22</v>
+      </c>
+      <c r="J427">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
+      <c r="A428" t="s">
+        <v>27</v>
+      </c>
+      <c r="B428" t="s">
+        <v>28</v>
+      </c>
+      <c r="C428" t="s">
+        <v>28</v>
+      </c>
+      <c r="D428">
+        <v>2207663</v>
+      </c>
+      <c r="E428" t="s">
+        <v>38</v>
+      </c>
+      <c r="F428">
+        <v>16</v>
+      </c>
+      <c r="G428">
+        <v>5</v>
+      </c>
+      <c r="H428">
+        <v>4</v>
+      </c>
+      <c r="I428">
+        <v>14</v>
+      </c>
+      <c r="J428">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10">
+      <c r="A429" t="s">
+        <v>27</v>
+      </c>
+      <c r="B429" t="s">
+        <v>28</v>
+      </c>
+      <c r="C429" t="s">
+        <v>28</v>
+      </c>
+      <c r="D429">
+        <v>7397528</v>
+      </c>
+      <c r="E429" t="s">
+        <v>39</v>
+      </c>
+      <c r="F429">
+        <v>26</v>
+      </c>
+      <c r="G429">
+        <v>13</v>
+      </c>
+      <c r="H429">
+        <v>3</v>
+      </c>
+      <c r="I429">
+        <v>21</v>
+      </c>
+      <c r="J429">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
+      <c r="A430" t="s">
+        <v>27</v>
+      </c>
+      <c r="B430" t="s">
+        <v>28</v>
+      </c>
+      <c r="C430" t="s">
+        <v>28</v>
+      </c>
+      <c r="D430">
+        <v>5931712</v>
+      </c>
+      <c r="E430" t="s">
+        <v>40</v>
+      </c>
+      <c r="F430">
+        <v>20</v>
+      </c>
+      <c r="G430">
+        <v>10</v>
+      </c>
+      <c r="H430">
+        <v>4</v>
+      </c>
+      <c r="I430">
+        <v>16</v>
+      </c>
+      <c r="J430">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
+      <c r="A431" t="s">
+        <v>27</v>
+      </c>
+      <c r="B431" t="s">
+        <v>28</v>
+      </c>
+      <c r="C431" t="s">
+        <v>28</v>
+      </c>
+      <c r="D431">
+        <v>7325488</v>
+      </c>
+      <c r="E431" t="s">
+        <v>41</v>
+      </c>
+      <c r="F431">
+        <v>65</v>
+      </c>
+      <c r="G431">
+        <v>23</v>
+      </c>
+      <c r="H431">
+        <v>13</v>
+      </c>
+      <c r="I431">
+        <v>23</v>
+      </c>
+      <c r="J431">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10">
+      <c r="A432" t="s">
+        <v>27</v>
+      </c>
+      <c r="B432" t="s">
+        <v>28</v>
+      </c>
+      <c r="C432" t="s">
+        <v>28</v>
+      </c>
+      <c r="D432">
+        <v>3368175</v>
+      </c>
+      <c r="E432" t="s">
+        <v>42</v>
+      </c>
+      <c r="F432">
+        <v>28</v>
+      </c>
+      <c r="G432">
+        <v>21</v>
+      </c>
+      <c r="H432">
+        <v>11</v>
+      </c>
+      <c r="I432">
+        <v>18</v>
+      </c>
+      <c r="J432">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10">
+      <c r="A433" t="s">
+        <v>27</v>
+      </c>
+      <c r="B433" t="s">
+        <v>28</v>
+      </c>
+      <c r="C433" t="s">
+        <v>28</v>
+      </c>
+      <c r="D433">
+        <v>3864716</v>
+      </c>
+      <c r="E433" t="s">
+        <v>43</v>
+      </c>
+      <c r="F433">
+        <v>35</v>
+      </c>
+      <c r="G433">
+        <v>22</v>
+      </c>
+      <c r="H433">
+        <v>8</v>
+      </c>
+      <c r="I433">
+        <v>33</v>
+      </c>
+      <c r="J433">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10">
+      <c r="A434" t="s">
+        <v>27</v>
+      </c>
+      <c r="B434" t="s">
+        <v>28</v>
+      </c>
+      <c r="C434" t="s">
+        <v>28</v>
+      </c>
+      <c r="D434">
+        <v>3367403</v>
+      </c>
+      <c r="E434" t="s">
+        <v>44</v>
+      </c>
+      <c r="F434">
+        <v>6</v>
+      </c>
+      <c r="G434">
+        <v>5</v>
+      </c>
+      <c r="H434">
+        <v>2</v>
+      </c>
+      <c r="I434">
+        <v>4</v>
+      </c>
+      <c r="J434">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10">
+      <c r="A435" t="s">
+        <v>27</v>
+      </c>
+      <c r="B435" t="s">
+        <v>28</v>
+      </c>
+      <c r="C435" t="s">
+        <v>28</v>
+      </c>
+      <c r="D435">
+        <v>7381124</v>
+      </c>
+      <c r="E435" t="s">
+        <v>45</v>
+      </c>
+      <c r="F435">
+        <v>31</v>
+      </c>
+      <c r="G435">
+        <v>13</v>
+      </c>
+      <c r="H435">
+        <v>5</v>
+      </c>
+      <c r="I435">
+        <v>18</v>
+      </c>
+      <c r="J435">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="A436" t="s">
+        <v>27</v>
+      </c>
+      <c r="B436" t="s">
+        <v>28</v>
+      </c>
+      <c r="C436" t="s">
+        <v>29</v>
+      </c>
+      <c r="D436">
+        <v>7079978</v>
+      </c>
+      <c r="E436" t="s">
+        <v>46</v>
+      </c>
+      <c r="F436">
+        <v>9</v>
+      </c>
+      <c r="G436">
+        <v>5</v>
+      </c>
+      <c r="H436">
+        <v>1</v>
+      </c>
+      <c r="I436">
+        <v>9</v>
+      </c>
+      <c r="J436">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="A437" t="s">
+        <v>27</v>
+      </c>
+      <c r="B437" t="s">
+        <v>28</v>
+      </c>
+      <c r="C437" t="s">
+        <v>29</v>
+      </c>
+      <c r="D437">
+        <v>3367739</v>
+      </c>
+      <c r="E437" t="s">
+        <v>47</v>
+      </c>
+      <c r="F437">
+        <v>1</v>
+      </c>
+      <c r="G437">
+        <v>5</v>
+      </c>
+      <c r="H437">
+        <v>0</v>
+      </c>
+      <c r="I437">
+        <v>3</v>
+      </c>
+      <c r="J437">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10">
+      <c r="A438" t="s">
+        <v>27</v>
+      </c>
+      <c r="B438" t="s">
+        <v>28</v>
+      </c>
+      <c r="C438" t="s">
+        <v>30</v>
+      </c>
+      <c r="D438">
+        <v>7072286</v>
+      </c>
+      <c r="E438" t="s">
+        <v>48</v>
+      </c>
+      <c r="F438">
+        <v>11</v>
+      </c>
+      <c r="G438">
+        <v>2</v>
+      </c>
+      <c r="H438">
+        <v>0</v>
+      </c>
+      <c r="I438">
+        <v>1</v>
+      </c>
+      <c r="J438">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10">
+      <c r="A439" t="s">
+        <v>27</v>
+      </c>
+      <c r="B439" t="s">
+        <v>28</v>
+      </c>
+      <c r="C439" t="s">
+        <v>31</v>
+      </c>
+      <c r="D439">
+        <v>3367743</v>
+      </c>
+      <c r="E439" t="s">
+        <v>49</v>
+      </c>
+      <c r="F439">
+        <v>3</v>
+      </c>
+      <c r="G439">
+        <v>2</v>
+      </c>
+      <c r="H439">
+        <v>3</v>
+      </c>
+      <c r="I439">
+        <v>0</v>
+      </c>
+      <c r="J439">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
+      <c r="A440" t="s">
+        <v>27</v>
+      </c>
+      <c r="B440" t="s">
+        <v>28</v>
+      </c>
+      <c r="C440" t="s">
+        <v>30</v>
+      </c>
+      <c r="D440">
+        <v>4214024</v>
+      </c>
+      <c r="E440" t="s">
+        <v>50</v>
+      </c>
+      <c r="F440">
+        <v>3</v>
+      </c>
+      <c r="G440">
+        <v>8</v>
+      </c>
+      <c r="H440">
+        <v>2</v>
+      </c>
+      <c r="I440">
+        <v>5</v>
+      </c>
+      <c r="J440">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10">
+      <c r="A441" t="s">
+        <v>27</v>
+      </c>
+      <c r="B441" t="s">
+        <v>28</v>
+      </c>
+      <c r="C441" t="s">
+        <v>31</v>
+      </c>
+      <c r="D441">
+        <v>7357843</v>
+      </c>
+      <c r="E441" t="s">
+        <v>51</v>
+      </c>
+      <c r="F441">
+        <v>30</v>
+      </c>
+      <c r="G441">
+        <v>6</v>
+      </c>
+      <c r="H441">
+        <v>2</v>
+      </c>
+      <c r="I441">
+        <v>21</v>
+      </c>
+      <c r="J441">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10">
+      <c r="A442" t="s">
+        <v>27</v>
+      </c>
+      <c r="B442" t="s">
+        <v>28</v>
+      </c>
+      <c r="C442" t="s">
+        <v>31</v>
+      </c>
+      <c r="D442">
+        <v>7077448</v>
+      </c>
+      <c r="E442" t="s">
+        <v>52</v>
+      </c>
+      <c r="F442">
+        <v>8</v>
+      </c>
+      <c r="G442">
+        <v>2</v>
+      </c>
+      <c r="H442">
+        <v>0</v>
+      </c>
+      <c r="I442">
+        <v>1</v>
+      </c>
+      <c r="J442">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10">
+      <c r="A443" t="s">
+        <v>27</v>
+      </c>
+      <c r="B443" t="s">
+        <v>28</v>
+      </c>
+      <c r="C443" t="s">
+        <v>32</v>
+      </c>
+      <c r="D443">
+        <v>2278099</v>
+      </c>
+      <c r="E443" t="s">
+        <v>53</v>
+      </c>
+      <c r="F443">
+        <v>31</v>
+      </c>
+      <c r="G443">
+        <v>14</v>
+      </c>
+      <c r="H443">
+        <v>8</v>
+      </c>
+      <c r="I443">
+        <v>31</v>
+      </c>
+      <c r="J443">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10">
+      <c r="A444" t="s">
+        <v>27</v>
+      </c>
+      <c r="B444" t="s">
+        <v>28</v>
+      </c>
+      <c r="C444" t="s">
+        <v>32</v>
+      </c>
+      <c r="D444">
+        <v>7077738</v>
+      </c>
+      <c r="E444" t="s">
+        <v>54</v>
+      </c>
+      <c r="F444">
+        <v>7</v>
+      </c>
+      <c r="G444">
+        <v>2</v>
+      </c>
+      <c r="H444">
+        <v>1</v>
+      </c>
+      <c r="I444">
+        <v>3</v>
+      </c>
+      <c r="J444">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10">
+      <c r="A445" t="s">
+        <v>27</v>
+      </c>
+      <c r="B445" t="s">
+        <v>28</v>
+      </c>
+      <c r="C445" t="s">
+        <v>32</v>
+      </c>
+      <c r="D445">
+        <v>4493936</v>
+      </c>
+      <c r="E445" t="s">
+        <v>55</v>
+      </c>
+      <c r="F445">
+        <v>9</v>
+      </c>
+      <c r="G445">
+        <v>0</v>
+      </c>
+      <c r="H445">
+        <v>0</v>
+      </c>
+      <c r="I445">
+        <v>1</v>
+      </c>
+      <c r="J445">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10">
+      <c r="A446" t="s">
+        <v>27</v>
+      </c>
+      <c r="B446" t="s">
+        <v>28</v>
+      </c>
+      <c r="C446" t="s">
+        <v>32</v>
+      </c>
+      <c r="D446">
+        <v>5284531</v>
+      </c>
+      <c r="E446" t="s">
+        <v>56</v>
+      </c>
+      <c r="F446">
+        <v>8</v>
+      </c>
+      <c r="G446">
+        <v>3</v>
+      </c>
+      <c r="H446">
+        <v>0</v>
+      </c>
+      <c r="I446">
+        <v>1</v>
+      </c>
+      <c r="J446">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10">
+      <c r="A447" t="s">
+        <v>27</v>
+      </c>
+      <c r="B447" t="s">
+        <v>28</v>
+      </c>
+      <c r="C447" t="s">
+        <v>33</v>
+      </c>
+      <c r="D447">
+        <v>5954007</v>
+      </c>
+      <c r="E447" t="s">
+        <v>57</v>
+      </c>
+      <c r="F447">
+        <v>50</v>
+      </c>
+      <c r="G447">
+        <v>35</v>
+      </c>
+      <c r="H447">
+        <v>6</v>
+      </c>
+      <c r="I447">
+        <v>28</v>
+      </c>
+      <c r="J447">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10">
+      <c r="A448" t="s">
+        <v>27</v>
+      </c>
+      <c r="B448" t="s">
+        <v>28</v>
+      </c>
+      <c r="C448" t="s">
+        <v>33</v>
+      </c>
+      <c r="D448">
+        <v>7081903</v>
+      </c>
+      <c r="E448" t="s">
+        <v>58</v>
+      </c>
+      <c r="F448">
+        <v>27</v>
+      </c>
+      <c r="G448">
+        <v>12</v>
+      </c>
+      <c r="H448">
+        <v>2</v>
+      </c>
+      <c r="I448">
+        <v>20</v>
+      </c>
+      <c r="J448">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10">
+      <c r="A449" t="s">
+        <v>27</v>
+      </c>
+      <c r="B449" t="s">
+        <v>28</v>
+      </c>
+      <c r="C449" t="s">
+        <v>34</v>
+      </c>
+      <c r="D449">
+        <v>9366541</v>
+      </c>
+      <c r="E449" t="s">
+        <v>59</v>
+      </c>
+      <c r="F449">
+        <v>25</v>
+      </c>
+      <c r="G449">
+        <v>16</v>
+      </c>
+      <c r="H449">
+        <v>3</v>
+      </c>
+      <c r="I449">
+        <v>16</v>
+      </c>
+      <c r="J449">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10">
+      <c r="A450" t="s">
+        <v>27</v>
+      </c>
+      <c r="B450" t="s">
+        <v>28</v>
+      </c>
+      <c r="C450" t="s">
+        <v>35</v>
+      </c>
+      <c r="D450">
+        <v>6435172</v>
+      </c>
+      <c r="E450" t="s">
+        <v>60</v>
+      </c>
+      <c r="F450">
+        <v>8</v>
+      </c>
+      <c r="G450">
+        <v>2</v>
+      </c>
+      <c r="H450">
+        <v>2</v>
+      </c>
+      <c r="I450">
+        <v>8</v>
+      </c>
+      <c r="J450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10">
+      <c r="A451" t="s">
+        <v>27</v>
+      </c>
+      <c r="B451" t="s">
+        <v>28</v>
+      </c>
+      <c r="C451" t="s">
+        <v>36</v>
+      </c>
+      <c r="D451">
+        <v>7077736</v>
+      </c>
+      <c r="E451" t="s">
+        <v>61</v>
+      </c>
+      <c r="F451">
+        <v>4</v>
+      </c>
+      <c r="G451">
+        <v>1</v>
+      </c>
+      <c r="H451">
+        <v>0</v>
+      </c>
+      <c r="I451">
+        <v>4</v>
+      </c>
+      <c r="J451">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
